--- a/docs/sdd/Desk2.0_Plan_Fases_y_Tandas_Revision_MoL_R01.3.xlsx
+++ b/docs/sdd/Desk2.0_Plan_Fases_y_Tandas_Revision_MoL_R01.3.xlsx
@@ -181,7 +181,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -302,6 +302,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -926,41 +929,41 @@
       </c>
     </row>
     <row r="2" ht="39" customHeight="1" s="20">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>F0</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="33" t="inlineStr">
         <is>
           <t>Cimientos SDD</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="C2" s="33" t="inlineStr">
         <is>
           <t>S37 (07–09/09/2026) · ejecutada</t>
         </is>
       </c>
-      <c r="D2" s="26" t="inlineStr">
+      <c r="D2" s="33" t="inlineStr">
         <is>
           <t>1,5 semanas previstas · 3 días reales</t>
         </is>
       </c>
-      <c r="E2" s="26" t="inlineStr">
+      <c r="E2" s="33" t="inlineStr">
         <is>
           <t>Traducir el as-built a specs OpenSpec; CLAUDE.md; Engram; pruebas del motor; staging y CI.</t>
         </is>
       </c>
-      <c r="F2" s="26" t="inlineStr">
+      <c r="F2" s="33" t="inlineStr">
         <is>
           <t>Ninguna decisión pendiente</t>
         </is>
       </c>
-      <c r="G2" s="27" t="n"/>
-      <c r="H2" s="27" t="n"/>
-      <c r="I2" s="27" t="n"/>
-      <c r="J2" s="27" t="n"/>
-      <c r="K2" s="27" t="n"/>
+      <c r="G2" s="34" t="n"/>
+      <c r="H2" s="34" t="n"/>
+      <c r="I2" s="34" t="n"/>
+      <c r="J2" s="34" t="n"/>
+      <c r="K2" s="34" t="n"/>
     </row>
     <row r="3" ht="51" customHeight="1" s="20">
       <c r="A3" s="28" t="inlineStr">
@@ -968,36 +971,36 @@
           <t>F1</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>Réplica del Desk 1.0 + diagnóstico protocolizado + informes (MVP)</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="33" t="inlineStr">
         <is>
           <t>S38–S53 (14/09–31/12/2026)</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="33" t="inlineStr">
         <is>
           <t>15 semanas</t>
         </is>
       </c>
-      <c r="E3" s="26" t="inlineStr">
+      <c r="E3" s="33" t="inlineStr">
         <is>
           <t>Paridad con Zoho Desk; correcciones C1–C12; decisiones del 10/09 (P21, P52, subOV, vista «Todos», fechas del servidor, mapa generado); motor de checklist dinámico con catálogo importado; módulo de informes; puesta en producción.</t>
         </is>
       </c>
-      <c r="F3" s="26" t="inlineStr">
+      <c r="F3" s="33" t="inlineStr">
         <is>
           <t>Gates de §4.5 del plan (sesiones de los viernes)</t>
         </is>
       </c>
-      <c r="G3" s="27" t="n"/>
-      <c r="H3" s="27" t="n"/>
-      <c r="I3" s="27" t="n"/>
-      <c r="J3" s="27" t="n"/>
-      <c r="K3" s="27" t="n"/>
+      <c r="G3" s="34" t="n"/>
+      <c r="H3" s="34" t="n"/>
+      <c r="I3" s="34" t="n"/>
+      <c r="J3" s="34" t="n"/>
+      <c r="K3" s="34" t="n"/>
     </row>
     <row r="4" ht="27" customHeight="1" s="20">
       <c r="A4" s="29" t="inlineStr">
@@ -1005,36 +1008,36 @@
           <t>F2</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>Operación interna completa</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t>2027 · T1</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>Kanban y KPIs (OTD, bodegajes), descuento de repuestos, comentarios predefinidos, app móvil responsive sin offline, migración documental.</t>
         </is>
       </c>
-      <c r="F4" s="26" t="inlineStr">
+      <c r="F4" s="33" t="inlineStr">
         <is>
           <t>Datos limpios de la F1</t>
         </is>
       </c>
-      <c r="G4" s="27" t="n"/>
-      <c r="H4" s="27" t="n"/>
-      <c r="I4" s="27" t="n"/>
-      <c r="J4" s="27" t="n"/>
-      <c r="K4" s="27" t="n"/>
+      <c r="G4" s="34" t="n"/>
+      <c r="H4" s="34" t="n"/>
+      <c r="I4" s="34" t="n"/>
+      <c r="J4" s="34" t="n"/>
+      <c r="K4" s="34" t="n"/>
     </row>
     <row r="5" ht="27" customHeight="1" s="20">
       <c r="A5" s="30" t="inlineStr">
@@ -1042,36 +1045,36 @@
           <t>F3</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Área de cliente nivel básico y seguridad</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>2027 · T2</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>C8, ítem 26 (hoja de vida reducida y aprobación en un clic), identidad registrada, nueve puntos de seguridad.</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>Etapa independiente (27/08)</t>
         </is>
       </c>
-      <c r="G5" s="27" t="n"/>
-      <c r="H5" s="27" t="n"/>
-      <c r="I5" s="27" t="n"/>
-      <c r="J5" s="27" t="n"/>
-      <c r="K5" s="27" t="n"/>
+      <c r="G5" s="34" t="n"/>
+      <c r="H5" s="34" t="n"/>
+      <c r="I5" s="34" t="n"/>
+      <c r="J5" s="34" t="n"/>
+      <c r="K5" s="34" t="n"/>
     </row>
     <row r="6" ht="27" customHeight="1" s="20">
       <c r="A6" s="31" t="inlineStr">
@@ -1079,36 +1082,36 @@
           <t>F4</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Eficiencia, capacidad y conocimiento</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>2027 · S2</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>Inventario transaccional, parámetro de carga y citas, dashboards por rol, capa RAG/KB, firmware, offline, QR/NFC.</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>Parámetro de carga antes que agendamiento</t>
         </is>
       </c>
-      <c r="G6" s="27" t="n"/>
-      <c r="H6" s="27" t="n"/>
-      <c r="I6" s="27" t="n"/>
-      <c r="J6" s="27" t="n"/>
-      <c r="K6" s="27" t="n"/>
+      <c r="G6" s="34" t="n"/>
+      <c r="H6" s="34" t="n"/>
+      <c r="I6" s="34" t="n"/>
+      <c r="J6" s="34" t="n"/>
+      <c r="K6" s="34" t="n"/>
     </row>
     <row r="7" ht="27" customHeight="1" s="20">
       <c r="A7" s="31" t="inlineStr">
@@ -1116,36 +1119,36 @@
           <t>F5</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Promesa, predicción y ecosistema</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>CTP, predicción de carga, agente conversacional, IoT, servicio premium, sustitución total de Zoho Desk.</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F7" s="33" t="inlineStr">
         <is>
           <t>MVP con dato estructurado</t>
         </is>
       </c>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="34" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G7">
@@ -1258,40 +1261,40 @@
       </c>
     </row>
     <row r="2" ht="39" customHeight="1" s="20">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>F0</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="33" t="inlineStr">
         <is>
           <t>F0</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="C2" s="33" t="inlineStr">
         <is>
           <t>Cimientos SDD</t>
         </is>
       </c>
-      <c r="D2" s="26" t="inlineStr">
+      <c r="D2" s="33" t="inlineStr">
         <is>
           <t>S37 (ejecutada 07–09/09)</t>
         </is>
       </c>
-      <c r="E2" s="26" t="inlineStr">
+      <c r="E2" s="33" t="inlineStr">
         <is>
           <t>Auditoría del as-built, specs as-built, Engram, pruebas, staging</t>
         </is>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="33">
         <f>COUNTIF(Tandas!$B:$B,B2)</f>
         <v/>
       </c>
-      <c r="G2" s="27" t="n"/>
-      <c r="H2" s="27" t="n"/>
-      <c r="I2" s="27" t="n"/>
-      <c r="J2" s="27" t="n"/>
-      <c r="K2" s="27" t="n"/>
+      <c r="G2" s="34" t="n"/>
+      <c r="H2" s="34" t="n"/>
+      <c r="I2" s="34" t="n"/>
+      <c r="J2" s="34" t="n"/>
+      <c r="K2" s="34" t="n"/>
     </row>
     <row r="3" ht="39" customHeight="1" s="20">
       <c r="A3" s="28" t="inlineStr">
@@ -1299,35 +1302,35 @@
           <t>F1</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>F1A</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="33" t="inlineStr">
         <is>
           <t>Correcciones sin decisión pendiente</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="33" t="inlineStr">
         <is>
           <t>S37–S38</t>
         </is>
       </c>
-      <c r="E3" s="26" t="inlineStr">
+      <c r="E3" s="33" t="inlineStr">
         <is>
           <t>Cerradas el 09/09: C1, C11, C9 (parte técnica) y la auditoría. Pendientes: C12 (recuperación as-is), generador del mapa, IV-2 fechas del servidor, IV-4 tercera puerta OV, barrido de citas R08.2</t>
         </is>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="33">
         <f>COUNTIF(Tandas!$B:$B,B3)</f>
         <v/>
       </c>
-      <c r="G3" s="27" t="n"/>
-      <c r="H3" s="27" t="n"/>
-      <c r="I3" s="27" t="n"/>
-      <c r="J3" s="27" t="n"/>
-      <c r="K3" s="27" t="n"/>
+      <c r="G3" s="34" t="n"/>
+      <c r="H3" s="34" t="n"/>
+      <c r="I3" s="34" t="n"/>
+      <c r="J3" s="34" t="n"/>
+      <c r="K3" s="34" t="n"/>
     </row>
     <row r="4" ht="39" customHeight="1" s="20">
       <c r="A4" s="28" t="inlineStr">
@@ -1335,35 +1338,35 @@
           <t>F1</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>F1B</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t>Paridad funcional con el Desk 1.0</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>S39–S44</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>Ítems 1, 2, 4–10, 17, 19, 20, 22; flujos equipo nuevo y soporte remoto; orden único de guardas; asociación OV ↔ ticket 1 : N y subOV de lote</t>
         </is>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="33">
         <f>COUNTIF(Tandas!$B:$B,B4)</f>
         <v/>
       </c>
-      <c r="G4" s="27" t="n"/>
-      <c r="H4" s="27" t="n"/>
-      <c r="I4" s="27" t="n"/>
-      <c r="J4" s="27" t="n"/>
-      <c r="K4" s="27" t="n"/>
+      <c r="G4" s="34" t="n"/>
+      <c r="H4" s="34" t="n"/>
+      <c r="I4" s="34" t="n"/>
+      <c r="J4" s="34" t="n"/>
+      <c r="K4" s="34" t="n"/>
     </row>
     <row r="5" ht="39" customHeight="1" s="20">
       <c r="A5" s="28" t="inlineStr">
@@ -1371,35 +1374,35 @@
           <t>F1</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>F1C</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>Correcciones que cambian el proceso</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>S40–S48 (según decisiones)</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>C2, C3, C4, C5, C6, C7+C9, C10, rutas abreviadas</t>
         </is>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="33">
         <f>COUNTIF(Tandas!$B:$B,B5)</f>
         <v/>
       </c>
-      <c r="G5" s="27" t="n"/>
-      <c r="H5" s="27" t="n"/>
-      <c r="I5" s="27" t="n"/>
-      <c r="J5" s="27" t="n"/>
-      <c r="K5" s="27" t="n"/>
+      <c r="G5" s="34" t="n"/>
+      <c r="H5" s="34" t="n"/>
+      <c r="I5" s="34" t="n"/>
+      <c r="J5" s="34" t="n"/>
+      <c r="K5" s="34" t="n"/>
     </row>
     <row r="6" ht="39" customHeight="1" s="20">
       <c r="A6" s="28" t="inlineStr">
@@ -1407,35 +1410,35 @@
           <t>F1</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>F1D</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>Diagnóstico protocolizado con checklist dinámico</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>S42–S47</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>Modelo del catálogo, importador Excel, macro-fases, validación por macro, encadenamiento No OK, criterio de falla, falla nueva, Horiba</t>
         </is>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="33">
         <f>COUNTIF(Tandas!$B:$B,B6)</f>
         <v/>
       </c>
-      <c r="G6" s="27" t="n"/>
-      <c r="H6" s="27" t="n"/>
-      <c r="I6" s="27" t="n"/>
-      <c r="J6" s="27" t="n"/>
-      <c r="K6" s="27" t="n"/>
+      <c r="G6" s="34" t="n"/>
+      <c r="H6" s="34" t="n"/>
+      <c r="I6" s="34" t="n"/>
+      <c r="J6" s="34" t="n"/>
+      <c r="K6" s="34" t="n"/>
     </row>
     <row r="7" ht="39" customHeight="1" s="20">
       <c r="A7" s="28" t="inlineStr">
@@ -1443,35 +1446,35 @@
           <t>F1</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>F1E</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>Módulo de informes</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>S46–S50</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>Informe de diagnóstico y de salida derivados del checklist; validación por dos personas</t>
         </is>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="33">
         <f>COUNTIF(Tandas!$B:$B,B7)</f>
         <v/>
       </c>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="34" t="n"/>
     </row>
     <row r="8" ht="39" customHeight="1" s="20">
       <c r="A8" s="28" t="inlineStr">
@@ -1479,35 +1482,35 @@
           <t>F1</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>F1F</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>Puesta en producción</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>S50–S53</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>Migración de tickets abiertos, respaldo, aceptación, formación, Zoho a solo lectura</t>
         </is>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="33">
         <f>COUNTIF(Tandas!$B:$B,B8)</f>
         <v/>
       </c>
-      <c r="G8" s="27" t="n"/>
-      <c r="H8" s="27" t="n"/>
-      <c r="I8" s="27" t="n"/>
-      <c r="J8" s="27" t="n"/>
-      <c r="K8" s="27" t="n"/>
+      <c r="G8" s="34" t="n"/>
+      <c r="H8" s="34" t="n"/>
+      <c r="I8" s="34" t="n"/>
+      <c r="J8" s="34" t="n"/>
+      <c r="K8" s="34" t="n"/>
     </row>
     <row r="9" ht="39" customHeight="1" s="20">
       <c r="A9" s="29" t="inlineStr">
@@ -1515,35 +1518,35 @@
           <t>F2</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>Operación interna completa</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>2027 T1</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>Ítems 13, 14, 15, 18 (sin offline), 30, 32, 37; comentarios predefinidos; P8/P54</t>
         </is>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="33">
         <f>COUNTIF(Tandas!$B:$B,B9)</f>
         <v/>
       </c>
-      <c r="G9" s="27" t="n"/>
-      <c r="H9" s="27" t="n"/>
-      <c r="I9" s="27" t="n"/>
-      <c r="J9" s="27" t="n"/>
-      <c r="K9" s="27" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
+      <c r="J9" s="34" t="n"/>
+      <c r="K9" s="34" t="n"/>
     </row>
     <row r="10" ht="39" customHeight="1" s="20">
       <c r="A10" s="30" t="inlineStr">
@@ -1551,35 +1554,35 @@
           <t>F3</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>Área de cliente y seguridad</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>2027 T2</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>C8, 26, 29, 52; seguridad</t>
         </is>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="33">
         <f>COUNTIF(Tandas!$B:$B,B10)</f>
         <v/>
       </c>
-      <c r="G10" s="27" t="n"/>
-      <c r="H10" s="27" t="n"/>
-      <c r="I10" s="27" t="n"/>
-      <c r="J10" s="27" t="n"/>
-      <c r="K10" s="27" t="n"/>
+      <c r="G10" s="34" t="n"/>
+      <c r="H10" s="34" t="n"/>
+      <c r="I10" s="34" t="n"/>
+      <c r="J10" s="34" t="n"/>
+      <c r="K10" s="34" t="n"/>
     </row>
     <row r="11" ht="39" customHeight="1" s="20">
       <c r="A11" s="31" t="inlineStr">
@@ -1587,35 +1590,35 @@
           <t>F4</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>Eficiencia, capacidad y conocimiento</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>2027 S2</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>Ítems 27, 28, 31–60 reordenados</t>
         </is>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="33">
         <f>COUNTIF(Tandas!$B:$B,B11)</f>
         <v/>
       </c>
-      <c r="G11" s="27" t="n"/>
-      <c r="H11" s="27" t="n"/>
-      <c r="I11" s="27" t="n"/>
-      <c r="J11" s="27" t="n"/>
-      <c r="K11" s="27" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
+      <c r="J11" s="34" t="n"/>
+      <c r="K11" s="34" t="n"/>
     </row>
     <row r="12" ht="39" customHeight="1" s="20">
       <c r="A12" s="31" t="inlineStr">
@@ -1623,35 +1626,35 @@
           <t>F5</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>F5</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>Promesa, predicción y ecosistema</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>Ítems 61–76</t>
         </is>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="33">
         <f>COUNTIF(Tandas!$B:$B,B12)</f>
         <v/>
       </c>
-      <c r="G12" s="27" t="n"/>
-      <c r="H12" s="27" t="n"/>
-      <c r="I12" s="27" t="n"/>
-      <c r="J12" s="27" t="n"/>
-      <c r="K12" s="27" t="n"/>
+      <c r="G12" s="34" t="n"/>
+      <c r="H12" s="34" t="n"/>
+      <c r="I12" s="34" t="n"/>
+      <c r="J12" s="34" t="n"/>
+      <c r="K12" s="34" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G12">
@@ -1690,7 +1693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="19" min="1" max="1"/>
@@ -1710,6 +1713,7 @@
     <col width="12" customWidth="1" style="19" min="16" max="16"/>
     <col width="22" customWidth="1" style="19" min="17" max="17"/>
     <col width="44" customWidth="1" style="19" min="18" max="18"/>
+    <col width="78" customWidth="1" style="20" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1" s="20">
@@ -1813,344 +1817,374 @@
           <t>Cambio en R01.3</t>
         </is>
       </c>
+      <c r="U1" s="24" t="inlineStr">
+        <is>
+          <t>Qué se podrá ver en la app al cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="75" customHeight="1" s="20">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>F0</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="33" t="inlineStr">
         <is>
           <t>F0</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="C2" s="33" t="inlineStr">
         <is>
           <t>F0-00</t>
         </is>
       </c>
-      <c r="D2" s="26" t="inlineStr">
+      <c r="D2" s="33" t="inlineStr">
         <is>
           <t>Auditoría del as-built</t>
         </is>
       </c>
-      <c r="E2" s="26" t="inlineStr">
+      <c r="E2" s="33" t="inlineStr">
         <is>
           <t>Tanda sin código. sdd-explore con un sub-agente por frente: motor de flujo (34 transiciones/21 estados, hallazgos R04), esquema de datos vs Anexo G y diseños de docs/superpowers, sincronización Zoho, UI (qué replica ya Zoho Desk), pruebas y build (96 ficheros vitest, typecheck, lint), deuda (reclasificar debt.md). Veredicto conservar / refactorizar / rehacer por frente; baseline a Engram.</t>
         </is>
       </c>
-      <c r="F2" s="26" t="inlineStr">
+      <c r="F2" s="33" t="inlineStr">
         <is>
           <t>todas las as-built</t>
         </is>
       </c>
-      <c r="G2" s="26" t="inlineStr">
+      <c r="G2" s="33" t="inlineStr">
         <is>
           <t>Anexo H · debt.md · docs/superpowers</t>
         </is>
       </c>
-      <c r="H2" s="26" t="inlineStr">
+      <c r="H2" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I2" s="26" t="inlineStr">
+      <c r="I2" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J2" s="26" t="inlineStr">
+      <c r="J2" s="33" t="inlineStr">
         <is>
           <t>S37</t>
         </is>
       </c>
-      <c r="K2" s="27" t="n"/>
-      <c r="L2" s="27" t="n"/>
-      <c r="M2" s="27" t="n"/>
-      <c r="N2" s="27" t="n"/>
-      <c r="O2" s="27" t="n"/>
-      <c r="P2" s="27" t="n"/>
-      <c r="Q2" s="26" t="inlineStr">
+      <c r="K2" s="34" t="n"/>
+      <c r="L2" s="34" t="n"/>
+      <c r="M2" s="34" t="n"/>
+      <c r="N2" s="34" t="n"/>
+      <c r="O2" s="34" t="n"/>
+      <c r="P2" s="34" t="n"/>
+      <c r="Q2" s="33" t="inlineStr">
         <is>
           <t>Cerrada (0e8f581)</t>
         </is>
       </c>
-      <c r="R2" s="26" t="inlineStr">
+      <c r="R2" s="33" t="inlineStr">
         <is>
           <t>Estado. Seis frentes conservar, uno refactorizar.</t>
         </is>
       </c>
+      <c r="U2" s="41" t="inlineStr">
+        <is>
+          <t>Nada en la aplicación: tanda sin código. Lo que queda como evidencia es el baseline verificado —docs/sdd/F0-00_Baseline_as-built.md— con el veredicto conservar / refactorizar / rehacer de los seis frentes, y ocho claves baseline/* en Engram. Se comprueba leyendo el documento, no abriendo la app.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="51" customHeight="1" s="20">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>F0</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>F0</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="33" t="inlineStr">
         <is>
           <t>F0-01</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="33" t="inlineStr">
         <is>
           <t>Init SDD, config, CLAUDE.md y export .md del documento maestro</t>
         </is>
       </c>
-      <c r="E3" s="26" t="inlineStr">
+      <c r="E3" s="33" t="inlineStr">
         <is>
           <t>sdd-init sobre el repo; openspec/config.yaml (contexto, strict_tdd: true, reglas por fase); CLAUDE.md con las 12 reglas invariables y el mapa documental (§4.7); exportación docs/Manifesto/…_R08.1.md; decidir qué skills de .claude/.agent se conservan.</t>
         </is>
       </c>
-      <c r="F3" s="26" t="inlineStr">
+      <c r="F3" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" s="26" t="inlineStr">
+      <c r="G3" s="33" t="inlineStr">
         <is>
           <t>Plan §4.4, §4.7</t>
         </is>
       </c>
-      <c r="H3" s="26" t="inlineStr">
+      <c r="H3" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I3" s="26" t="inlineStr">
+      <c r="I3" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J3" s="26" t="inlineStr">
+      <c r="J3" s="33" t="inlineStr">
         <is>
           <t>S37</t>
         </is>
       </c>
-      <c r="K3" s="27" t="n"/>
-      <c r="L3" s="27" t="n"/>
-      <c r="M3" s="27" t="n"/>
-      <c r="N3" s="27" t="n"/>
-      <c r="O3" s="27" t="n"/>
-      <c r="P3" s="27" t="n"/>
-      <c r="Q3" s="26" t="inlineStr">
+      <c r="K3" s="34" t="n"/>
+      <c r="L3" s="34" t="n"/>
+      <c r="M3" s="34" t="n"/>
+      <c r="N3" s="34" t="n"/>
+      <c r="O3" s="34" t="n"/>
+      <c r="P3" s="34" t="n"/>
+      <c r="Q3" s="33" t="inlineStr">
         <is>
           <t>Cerrada (3d44e1e)</t>
         </is>
       </c>
-      <c r="R3" s="26" t="inlineStr">
+      <c r="R3" s="33" t="inlineStr">
         <is>
           <t>Estado. El .md citable pasa a R08.2: ver F1A-09.</t>
         </is>
       </c>
+      <c r="U3" s="41" t="inlineStr">
+        <is>
+          <t>Nada en la aplicación. Quedan CLAUDE.md con las reglas invariables, openspec/config.yaml con el contexto y el preflight, y el maestro exportado a .md citable por línea. Se comprueba abriendo una sesión nueva y preguntándole una regla: si la sabe sin que se la repitan, está.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="51" customHeight="1" s="20">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>F0</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>F0</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t>F0-02</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>Specs as-built de las capacidades existentes</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>A partir del inventario de F0-00 y de docs/superpowers/specs: specs de transitions-st, permissions, remisiones, zoho-sync, derivacion-avisos, trazas, tickets-core tal como están, con los hallazgos R04 marcados «a corregir en Cx». Superpowers queda como histórico.</t>
         </is>
       </c>
-      <c r="F4" s="26" t="inlineStr">
+      <c r="F4" s="33" t="inlineStr">
         <is>
           <t>todas las as-built</t>
         </is>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="33" t="inlineStr">
         <is>
           <t>M1.3, M1.9, Anexo G · docs/superpowers</t>
         </is>
       </c>
-      <c r="H4" s="26" t="inlineStr">
+      <c r="H4" s="33" t="inlineStr">
         <is>
           <t>F0-00</t>
         </is>
       </c>
-      <c r="I4" s="26" t="inlineStr">
+      <c r="I4" s="33" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J4" s="26" t="inlineStr">
+      <c r="J4" s="33" t="inlineStr">
         <is>
           <t>S38</t>
         </is>
       </c>
-      <c r="K4" s="27" t="n"/>
-      <c r="L4" s="27" t="n"/>
-      <c r="M4" s="27" t="n"/>
-      <c r="N4" s="27" t="n"/>
-      <c r="O4" s="27" t="n"/>
-      <c r="P4" s="27" t="n"/>
-      <c r="Q4" s="26" t="inlineStr">
+      <c r="K4" s="34" t="n"/>
+      <c r="L4" s="34" t="n"/>
+      <c r="M4" s="34" t="n"/>
+      <c r="N4" s="34" t="n"/>
+      <c r="O4" s="34" t="n"/>
+      <c r="P4" s="34" t="n"/>
+      <c r="Q4" s="33" t="inlineStr">
         <is>
           <t>Cerrada (38bd062 → 749d205)</t>
         </is>
       </c>
-      <c r="R4" s="26" t="inlineStr">
+      <c r="R4" s="33" t="inlineStr">
         <is>
           <t>Estado. Siete specs as-built; equipo nuevo, soporte remoto, checklist e informes sin spec, por diseño.</t>
         </is>
       </c>
+      <c r="U4" s="41" t="inlineStr">
+        <is>
+          <t>Nada en la aplicación. Quedan las specs as-built en openspec/specs/ —transitions-st, permissions, remisiones, zoho-sync, derivacion-avisos, trazas, tickets-core—, cada una citando el apartado del maestro del que sale. El Anexo H pasa a tener espejo en el repositorio.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="27" customHeight="1" s="20">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>F0</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>F0</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>F0-03</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>Proyecto Engram y carga de decisiones</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>Proyecto Engram; decisiones cerradas (§1.8 y acta 03/09) como observaciones decision/*; convención de topic_key; evaluar Git Sync.</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t>§1.8, acta 03/09</t>
         </is>
       </c>
-      <c r="H5" s="26" t="inlineStr">
+      <c r="H5" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J5" s="26" t="inlineStr">
+      <c r="J5" s="33" t="inlineStr">
         <is>
           <t>S37</t>
         </is>
       </c>
-      <c r="K5" s="27" t="n"/>
-      <c r="L5" s="27" t="n"/>
-      <c r="M5" s="27" t="n"/>
-      <c r="N5" s="27" t="n"/>
-      <c r="O5" s="27" t="n"/>
-      <c r="P5" s="27" t="n"/>
-      <c r="Q5" s="26" t="inlineStr">
+      <c r="K5" s="34" t="n"/>
+      <c r="L5" s="34" t="n"/>
+      <c r="M5" s="34" t="n"/>
+      <c r="N5" s="34" t="n"/>
+      <c r="O5" s="34" t="n"/>
+      <c r="P5" s="34" t="n"/>
+      <c r="Q5" s="33" t="inlineStr">
         <is>
           <t>Cerrada (3aaa0f1)</t>
         </is>
       </c>
-      <c r="R5" s="26" t="inlineStr">
+      <c r="R5" s="33" t="inlineStr">
         <is>
           <t>Estado.</t>
         </is>
       </c>
+      <c r="U5" s="41" t="inlineStr">
+        <is>
+          <t>Nada en la aplicación. Queda la memoria del proyecto: las decisiones cerradas cargadas en Engram como decision/*, con su convención de clave. Se comprueba con mem_search: una decisión del 27/08 se recupera por su nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="39" customHeight="1" s="20">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>F0</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>F0</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>F0-04</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>Pruebas del motor, staging y CI</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>Pruebas mínimas del motor de transiciones (origen/destino declarados; Finalizado único terminal); staging en VPS Hostinger con PostgreSQL; CI.</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>transitions-st</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="33" t="inlineStr">
         <is>
           <t>M11.5</t>
         </is>
       </c>
-      <c r="H6" s="26" t="inlineStr">
+      <c r="H6" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="26" t="inlineStr">
+      <c r="I6" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J6" s="26" t="inlineStr">
+      <c r="J6" s="33" t="inlineStr">
         <is>
           <t>S38</t>
         </is>
       </c>
-      <c r="K6" s="27" t="n"/>
-      <c r="L6" s="27" t="n"/>
-      <c r="M6" s="27" t="n"/>
-      <c r="N6" s="27" t="n"/>
-      <c r="O6" s="27" t="n"/>
-      <c r="P6" s="27" t="n"/>
-      <c r="Q6" s="26" t="inlineStr">
+      <c r="K6" s="34" t="n"/>
+      <c r="L6" s="34" t="n"/>
+      <c r="M6" s="34" t="n"/>
+      <c r="N6" s="34" t="n"/>
+      <c r="O6" s="34" t="n"/>
+      <c r="P6" s="34" t="n"/>
+      <c r="Q6" s="33" t="inlineStr">
         <is>
           <t>Ejecutada · proposal.md sin actualizar</t>
         </is>
       </c>
-      <c r="R6" s="26" t="inlineStr">
+      <c r="R6" s="33" t="inlineStr">
         <is>
           <t>Estado. 20 commits de pruebas y CI (110 ficheros). Su proposal.md sigue diciendo «pendiente de visto bueno»: cerrar el registro.</t>
+        </is>
+      </c>
+      <c r="U6" s="41" t="inlineStr">
+        <is>
+          <t>Lo primero visible de todo el proyecto, aunque no sea una función: la aplicación corriendo en la VPS Hostinger con PostgreSQL, en un sitio donde cualquiera puede entrar a probarla sin el portátil de nadie. Y en CI, las pruebas del motor en verde: cada transición parte y llega a los estados declarados, y Finalizado es el único terminal.</t>
         </is>
       </c>
     </row>
@@ -2221,4206 +2255,4531 @@
           <t>—</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S7" s="19" t="inlineStr">
         <is>
           <t>No existía</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T7" s="19" t="inlineStr">
         <is>
           <t>FILA NUEVA el 17/09/2026. El denominador de avance pasa de 51 a 52 tandas, fechado en el corte de S38 por la regla (a) de unidad_de_avance. Motivo: fila nueva F0-05, no trabajo.</t>
         </is>
       </c>
+      <c r="U7" s="41" t="inlineStr">
+        <is>
+          <t>Nada en la aplicación. Queda el mecanismo: un push con un proposal.md sin cabecera se bloquea, «npm run reconcile» escribe docs/sdd/RECONCILIACION.md con las seis comprobaciones, y docs/sdd/ENTRADA.md recoge las ideas con su regla de tres salidas. Se comprueba intentando empujar un proposal sin cabecera: no sale.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="63" customHeight="1" s="20">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>F1A</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>F1A-01</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>C1 · Guarda del checkbox obligatorio</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>buildTransitionPlan: un checkbox obligatorio que no llega marcado detiene la transición (debt.md M-2). Dos piezas: el chequeo de obligatorio pasa por delante del bloque del checkbox, y la condición es «no llega marcado» (asBool(raw) !== true), no «llega vacío». Devuelve 422 y el ticket no se mueve.</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="33" t="inlineStr">
         <is>
           <t>transitions-st</t>
         </is>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="33" t="inlineStr">
         <is>
           <t>M1.7 · M11.7 · P33 · P64 (R08.2)</t>
         </is>
       </c>
-      <c r="H8" s="26" t="inlineStr">
+      <c r="H8" s="33" t="inlineStr">
         <is>
           <t>Ninguno</t>
         </is>
       </c>
-      <c r="I8" s="26" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J8" s="26" t="inlineStr">
+      <c r="J8" s="33" t="inlineStr">
         <is>
           <t>S38</t>
         </is>
       </c>
-      <c r="K8" s="27" t="n"/>
-      <c r="L8" s="27" t="n"/>
-      <c r="M8" s="27" t="n"/>
-      <c r="N8" s="27" t="n"/>
-      <c r="O8" s="27" t="n"/>
-      <c r="P8" s="27" t="n"/>
-      <c r="Q8" s="26" t="inlineStr">
+      <c r="K8" s="34" t="n"/>
+      <c r="L8" s="34" t="n"/>
+      <c r="M8" s="34" t="n"/>
+      <c r="N8" s="34" t="n"/>
+      <c r="O8" s="34" t="n"/>
+      <c r="P8" s="34" t="n"/>
+      <c r="Q8" s="33" t="inlineStr">
         <is>
           <t>Cerrada 09/09 (ec0ed1f)</t>
         </is>
       </c>
-      <c r="R8" s="26" t="inlineStr">
+      <c r="R8" s="33" t="inlineStr">
         <is>
           <t>Estado y contenido. Tamaño real S, no XS: eran dos piezas. El histórico escrito antes del arreglo queda como P64.</t>
         </is>
       </c>
+      <c r="U8" s="41" t="inlineStr">
+        <is>
+          <t>Al ejecutar «Liberación sin factura» sin marcar el checkbox obligatorio, la aplicación responde 422 y EL TICKET NO SE MUEVE. Antes se movía igual y el checkbox quedaba sin marcar. Se ve intentando la transición: mensaje de error y el estado intacto.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="51" customHeight="1" s="20">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>F1A</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>F1A-02</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>C11 · SLA de un día sobre Notificado</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>SLA existente en Zoho; ampliado con correo redundante al cambiar de área y escalado al superior.</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F9" s="33" t="inlineStr">
         <is>
           <t>transitions-st, derivacion-avisos</t>
         </is>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t>M1.7 (R08.1.md:1570-1575) · P40 · Anexo H (:4561)</t>
         </is>
       </c>
-      <c r="H9" s="26" t="inlineStr">
+      <c r="H9" s="33" t="inlineStr">
         <is>
           <t>Ninguno</t>
         </is>
       </c>
-      <c r="I9" s="26" t="inlineStr">
+      <c r="I9" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J9" s="26" t="inlineStr">
+      <c r="J9" s="33" t="inlineStr">
         <is>
           <t>S38</t>
         </is>
       </c>
-      <c r="K9" s="27" t="n"/>
-      <c r="L9" s="27" t="n"/>
-      <c r="M9" s="27" t="n"/>
-      <c r="N9" s="27" t="n"/>
-      <c r="O9" s="27" t="n"/>
-      <c r="P9" s="27" t="n"/>
-      <c r="Q9" s="26" t="inlineStr">
+      <c r="K9" s="34" t="n"/>
+      <c r="L9" s="34" t="n"/>
+      <c r="M9" s="34" t="n"/>
+      <c r="N9" s="34" t="n"/>
+      <c r="O9" s="34" t="n"/>
+      <c r="P9" s="34" t="n"/>
+      <c r="Q9" s="33" t="inlineStr">
         <is>
           <t>Cerrada 09/09 (6ea3ca8, 5218d11)</t>
         </is>
       </c>
-      <c r="R9" s="26" t="inlineStr">
+      <c r="R9" s="33" t="inlineStr">
         <is>
           <t>Entrada 1: la ampliación de C11 la firma el maestro (R08), no el acta del 03/09, que no trata C11. Se quita «acta 03/09 (ampliada)».</t>
         </is>
       </c>
+      <c r="U9" s="41" t="inlineStr">
+        <is>
+          <t>Un ticket que lleva un día en Notificado dispara el aviso que Zoho tenía y la aplicación no. Al cambiar de área sale un correo redundante y, pasado el plazo, el escalado al superior. Se ve en la bandeja de correo y en el historial del ticket.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="87" customHeight="1" s="20">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>F1A</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>F1A-03</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>C12 · Verificación en equipo nuevo (recuperación as-is)</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>La salida aprobada ya existe en la operación: Verificación —Liberación→ Finalizado (71 usos en 181 tickets). Liberación tiene dos orígenes (En Proceso y Verificación) y M1.4 pasa a seis transiciones. Se escribe en la spec transitions-equipo-nuevo antes de F1B-06. El estado Verificación se abre al empezar la verificación, no al terminarla (M7.3).</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="33" t="inlineStr">
         <is>
           <t>transitions-equipo-nuevo</t>
         </is>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="33" t="inlineStr">
         <is>
           <t>M1.4 · M7.3 · P38 (parcialmente resuelto, R08.2)</t>
         </is>
       </c>
-      <c r="H10" s="26" t="inlineStr">
+      <c r="H10" s="33" t="inlineStr">
         <is>
           <t>Ninguno para la transición (as-is: Verificación —Liberación→ Finalizado, 71 usos observados). La GUARDA de obligatoriedad por familia espera a Gustavo/Calidad · Anexo D nº 38. Se hace antes de F1B-06, que la hereda</t>
         </is>
       </c>
-      <c r="I10" s="26" t="inlineStr">
+      <c r="I10" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J10" s="26" t="inlineStr">
+      <c r="J10" s="33" t="inlineStr">
         <is>
           <t>S38</t>
         </is>
       </c>
-      <c r="K10" s="27" t="n"/>
-      <c r="L10" s="27" t="n"/>
-      <c r="M10" s="27" t="n"/>
-      <c r="N10" s="27" t="n"/>
-      <c r="O10" s="27" t="n"/>
-      <c r="P10" s="27" t="n"/>
-      <c r="Q10" s="26" t="inlineStr">
+      <c r="K10" s="34" t="n"/>
+      <c r="L10" s="34" t="n"/>
+      <c r="M10" s="34" t="n"/>
+      <c r="N10" s="34" t="n"/>
+      <c r="O10" s="34" t="n"/>
+      <c r="P10" s="34" t="n"/>
+      <c r="Q10" s="33" t="inlineStr">
         <is>
           <t>Desbloqueada 10/09 · sin código aún</t>
         </is>
       </c>
-      <c r="R10" s="26" t="inlineStr">
+      <c r="R10" s="33" t="inlineStr">
         <is>
           <t>Entrada 2 en su versión corregida del 10/09. Estaba parada sin código; los 181 tickets la desbloquean sin esperar a Calidad.</t>
         </is>
       </c>
+      <c r="U10" s="41" t="inlineStr">
+        <is>
+          <t>En equipo nuevo, Verificación deja de ser un callejón sin salida: aparece el botón «Liberación», que lleva a Finalizado. Liberación pasa a ofrecerse desde dos orígenes, En Proceso y Verificación, y M1.4 pasa a seis transiciones. Se ve como botón nuevo en la ficha de un ticket en Verificación.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="75" customHeight="1" s="20">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>F1A</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>F1A-04</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>C9 · Bodegajes contra Ingreso a Servicio</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>C9 (parte técnica). Los tres bodegajes de M1.10 (:1685-1702) calculados sobre ticket_transitions; reanclar los indicadores 48 y 49 en la marca de «Ingreso a Servicio»; añadir el campo «fecha de aviso al cliente».</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F11" s="33" t="inlineStr">
         <is>
           <t>trazas, kpis</t>
         </is>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="33" t="inlineStr">
         <is>
           <t>M1.10 · P41</t>
         </is>
       </c>
-      <c r="H11" s="26" t="inlineStr">
+      <c r="H11" s="33" t="inlineStr">
         <is>
           <t>Definición ya resuelta en R08</t>
         </is>
       </c>
-      <c r="I11" s="26" t="inlineStr">
+      <c r="I11" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J11" s="26" t="inlineStr">
+      <c r="J11" s="33" t="inlineStr">
         <is>
           <t>S38</t>
         </is>
       </c>
-      <c r="K11" s="27" t="n"/>
-      <c r="L11" s="27" t="n"/>
-      <c r="M11" s="27" t="n"/>
-      <c r="N11" s="27" t="n"/>
-      <c r="O11" s="27" t="n"/>
-      <c r="P11" s="27" t="n"/>
-      <c r="Q11" s="26" t="inlineStr">
+      <c r="K11" s="34" t="n"/>
+      <c r="L11" s="34" t="n"/>
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="34" t="n"/>
+      <c r="O11" s="34" t="n"/>
+      <c r="P11" s="34" t="n"/>
+      <c r="Q11" s="33" t="inlineStr">
         <is>
           <t>Cerrada 09/09 (e8c5e90)</t>
         </is>
       </c>
-      <c r="R11" s="26" t="inlineStr">
+      <c r="R11" s="33" t="inlineStr">
         <is>
           <t>Entrada 3: el bodegaje de entrada se ancla en Fecha Remisión Entrada → Fecha OV (R08), no en la marca de Ingreso a Servicio, que sólo vale para los indicadores 48 y 49. Dejó expuesto el hito (bodegaje.ts, marcaIngresoAServicio); los indicadores se construyen en F1C-06, porque no hay módulo de KPIs.</t>
         </is>
       </c>
+      <c r="U11" s="41" t="inlineStr">
+        <is>
+          <t>Todavía no hay pantalla de indicadores, pero el dato ya es correcto: los tres bodegajes se calculan sobre el historial de transiciones y no sobre la fecha de creación del ticket, que Comercial abre por anticipado. Y aparece el campo «Fecha de aviso al cliente» en el formulario, que antes faltaba.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="39" customHeight="1" s="20">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>F1A</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>F1A-05</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>audit-F1A</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>Auditoría de blueprint leyendo el código tras C1, C11 y C9; C12 declarada fuera. Hallazgos al Anexo D.</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="G12" s="33" t="inlineStr">
         <is>
           <t>M11.6</t>
         </is>
       </c>
-      <c r="H12" s="26" t="inlineStr">
+      <c r="H12" s="33" t="inlineStr">
         <is>
           <t>Ninguno. NO regenera docs/artefactos/ (no hay generador todavía); audita leyendo el código</t>
         </is>
       </c>
-      <c r="I12" s="26" t="inlineStr">
+      <c r="I12" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J12" s="26" t="inlineStr">
+      <c r="J12" s="33" t="inlineStr">
         <is>
           <t>S38</t>
         </is>
       </c>
-      <c r="K12" s="27" t="n"/>
-      <c r="L12" s="27" t="n"/>
-      <c r="M12" s="27" t="n"/>
-      <c r="N12" s="27" t="n"/>
-      <c r="O12" s="27" t="n"/>
-      <c r="P12" s="27" t="n"/>
-      <c r="Q12" s="26" t="inlineStr">
+      <c r="K12" s="34" t="n"/>
+      <c r="L12" s="34" t="n"/>
+      <c r="M12" s="34" t="n"/>
+      <c r="N12" s="34" t="n"/>
+      <c r="O12" s="34" t="n"/>
+      <c r="P12" s="34" t="n"/>
+      <c r="Q12" s="33" t="inlineStr">
         <is>
           <t>Ejecutada 09/09 (auditó e8c5e90)</t>
         </is>
       </c>
-      <c r="R12" s="26" t="inlineStr">
+      <c r="R12" s="33" t="inlineStr">
         <is>
           <t>Entrada 4: la talla S es la de auditar, confirmada; no la de regenerar. El mapa lo produce F1A-06.</t>
         </is>
       </c>
+      <c r="U12" s="41" t="inlineStr">
+        <is>
+          <t>Nada en la aplicación. Queda el informe de auditoría del blueprint leído del código tras C1, C11 y C9, con sus hallazgos volcados al Anexo D.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="111" customHeight="1" s="20">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>F1A</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>F1A-06</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>Generador del mapa del blueprint</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>Script que genera docs/artefactos/blueprint-*.md (Mermaid stateDiagram-v2) desde transitions.ts, estados.ts y permissions.ts: diagrama completo más una vista por cada una de las tres fases de M1.3.1. Prueba anti-desfase en CI (mismo patrón que migrate.test.ts). docs/artefactos/blueprintserviciotecnico.html queda como histórico congelado en a3a8f03. Antes del criterio de aceptación hay que cerrar el hueco entre los 38 pasos que cita el maestro y los 36 que declara el código (34 con botón + 2 sin botón).</t>
         </is>
       </c>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="F13" s="33" t="inlineStr">
         <is>
           <t>transitions-st</t>
         </is>
       </c>
-      <c r="G13" s="26" t="inlineStr">
+      <c r="G13" s="33" t="inlineStr">
         <is>
           <t>Anexo F (R08.2) · Decisiones 10/09 §9 · entrada 4</t>
         </is>
       </c>
-      <c r="H13" s="26" t="inlineStr">
+      <c r="H13" s="33" t="inlineStr">
         <is>
           <t>Ninguno (decision/mapa-blueprint-generado, 10/09)</t>
         </is>
       </c>
-      <c r="I13" s="26" t="inlineStr">
+      <c r="I13" s="33" t="inlineStr">
         <is>
           <t>Por dimensionar (exploración corta; si da más que S se revisa la decisión)</t>
         </is>
       </c>
-      <c r="J13" s="26" t="inlineStr">
+      <c r="J13" s="33" t="inlineStr">
         <is>
           <t>S38</t>
         </is>
       </c>
-      <c r="K13" s="27" t="n"/>
-      <c r="L13" s="27" t="n"/>
-      <c r="M13" s="27" t="n"/>
-      <c r="N13" s="27" t="n"/>
-      <c r="O13" s="27" t="n"/>
-      <c r="P13" s="27" t="n"/>
-      <c r="Q13" s="26" t="inlineStr">
+      <c r="K13" s="34" t="n"/>
+      <c r="L13" s="34" t="n"/>
+      <c r="M13" s="34" t="n"/>
+      <c r="N13" s="34" t="n"/>
+      <c r="O13" s="34" t="n"/>
+      <c r="P13" s="34" t="n"/>
+      <c r="Q13" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R13" s="26" t="inlineStr">
+      <c r="R13" s="33" t="inlineStr">
         <is>
           <t>Nueva (entrada 4, decidida 10/09). Va antes de F1B-06, para que los flujos nuevos nazcan con su diagrama.</t>
         </is>
       </c>
+      <c r="U13" s="41" t="inlineStr">
+        <is>
+          <t>Aparece el mapa del flujo como diagrama —uno completo y una vista por cada fase—, generado desde el código y no dibujado a mano. Cualquiera lo abre y ve los estados y transiciones que la aplicación tiene hoy. Y si alguien añade una transición sin regenerar, CI se pone rojo.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="111" customHeight="1" s="20">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>F1A</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>F1A-07</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>IV-2 · Fechas derivadas impuestas por el servidor</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>Fecha creación ticket, Fecha Remisión Entrada y Fecha Revisión Informe se calculan en el servidor, que ignora lo que llegue del navegador para esos tres campos. Hoy valoresTransicion.ts las deriva en el navegador y el servidor sólo exige que lleguen (transitionExec.ts:77). La zona horaria se fija de forma explícita: diaLocal usa la del proceso, y en el VPS cinco horas de cada día cambiarían de fecha. Decide la tanda: si recalcula siempre o respeta un valor ya escrito (semántica actual de yaEsta). Antes, barrer qué otros KPI o campos consumen las tres fechas.</t>
         </is>
       </c>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="F14" s="33" t="inlineStr">
         <is>
           <t>trazas</t>
         </is>
       </c>
-      <c r="G14" s="26" t="inlineStr">
+      <c r="G14" s="33" t="inlineStr">
         <is>
           <t>M1.10 (R08.2) · Decisiones 10/09 §4</t>
         </is>
       </c>
-      <c r="H14" s="26" t="inlineStr">
+      <c r="H14" s="33" t="inlineStr">
         <is>
           <t>Ninguno (decision/iv2-fechas-derivadas, 10/09)</t>
         </is>
       </c>
-      <c r="I14" s="26" t="inlineStr">
+      <c r="I14" s="33" t="inlineStr">
         <is>
           <t>S (a confirmar)</t>
         </is>
       </c>
-      <c r="J14" s="26" t="inlineStr">
+      <c r="J14" s="33" t="inlineStr">
         <is>
           <t>S38</t>
         </is>
       </c>
-      <c r="K14" s="27" t="n"/>
-      <c r="L14" s="27" t="n"/>
-      <c r="M14" s="27" t="n"/>
-      <c r="N14" s="27" t="n"/>
-      <c r="O14" s="27" t="n"/>
-      <c r="P14" s="27" t="n"/>
-      <c r="Q14" s="26" t="inlineStr">
+      <c r="K14" s="34" t="n"/>
+      <c r="L14" s="34" t="n"/>
+      <c r="M14" s="34" t="n"/>
+      <c r="N14" s="34" t="n"/>
+      <c r="O14" s="34" t="n"/>
+      <c r="P14" s="34" t="n"/>
+      <c r="Q14" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R14" s="26" t="inlineStr">
+      <c r="R14" s="33" t="inlineStr">
         <is>
           <t>Nueva. Condición previa del bodegaje de entrada: con P21 cerrado, IV-2 deja de ser opcional.</t>
         </is>
       </c>
+      <c r="U14" s="41" t="inlineStr">
+        <is>
+          <t>Para quien usa la aplicación no cambia lo que ve: las tres fechas derivadas siguen saliendo rellenas y bloqueadas. Lo que cambia es que ya no pueden llegar mal —ni desde el navegador ni desde una llamada directa a la API—, porque las calcula el servidor e ignora lo que le manden. Con ellas dejan de ensuciarse los indicadores que las usan.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="63" customHeight="1" s="20">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>F1A</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>F1A-08</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>IV-4 · Tercera puerta de la asociación OV ↔ ticket</t>
         </is>
       </c>
-      <c r="E15" s="26" t="inlineStr">
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>remision.ts:218-226 escribe salesorder_id sin pasar por ticketConOrdenVenta. Se valida como las otras dos puertas la regla que se mantiene: «una OV → un solo ticket vigente». El it.fails de ordenVentaUnTicket.test.ts:161 pasa a verde. El orden de las guardas se declara en F1B-10.</t>
         </is>
       </c>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="F15" s="33" t="inlineStr">
         <is>
           <t>remisiones, tickets-core</t>
         </is>
       </c>
-      <c r="G15" s="26" t="inlineStr">
+      <c r="G15" s="33" t="inlineStr">
         <is>
           <t>Decisiones 10/09 §2 · M4.4 (R08.2)</t>
         </is>
       </c>
-      <c r="H15" s="26" t="inlineStr">
+      <c r="H15" s="33" t="inlineStr">
         <is>
           <t>Ninguno (decision/n52-cardinalidad-ov la desbloquea)</t>
         </is>
       </c>
-      <c r="I15" s="26" t="inlineStr">
+      <c r="I15" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J15" s="26" t="inlineStr">
+      <c r="J15" s="33" t="inlineStr">
         <is>
           <t>S38</t>
         </is>
       </c>
-      <c r="K15" s="27" t="n"/>
-      <c r="L15" s="27" t="n"/>
-      <c r="M15" s="27" t="n"/>
-      <c r="N15" s="27" t="n"/>
-      <c r="O15" s="27" t="n"/>
-      <c r="P15" s="27" t="n"/>
-      <c r="Q15" s="26" t="inlineStr">
+      <c r="K15" s="34" t="n"/>
+      <c r="L15" s="34" t="n"/>
+      <c r="M15" s="34" t="n"/>
+      <c r="N15" s="34" t="n"/>
+      <c r="O15" s="34" t="n"/>
+      <c r="P15" s="34" t="n"/>
+      <c r="Q15" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R15" s="26" t="inlineStr">
+      <c r="R15" s="33" t="inlineStr">
         <is>
           <t>Nueva. IV-4 pasa de bloqueado a construible con la decisión n52.</t>
         </is>
       </c>
+      <c r="U15" s="41" t="inlineStr">
+        <is>
+          <t>Si alguien intenta asociar en la remisión de entrada una orden de venta que ya pertenece a otro ticket, la aplicación responde 409 y NO ESCRIBE NADA. Antes respondía 201 y la orden acababa en los dos tickets a la vez.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="51" customHeight="1" s="20">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>F1A</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>F1A-09</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>Barrido de citas tras la R08.2</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>Regenerar docs/Manifesto/…_R08.2.md desde el .docx y actualizar las citas por línea en specs, registros de correcciones, documento de decisiones, CLAUDE.md y este plan. El cambio de revisión desplaza todas las citas.</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F16" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="26" t="inlineStr">
+      <c r="G16" s="33" t="inlineStr">
         <is>
           <t>R08.2 §1.2 «Después de esta revisión»</t>
         </is>
       </c>
-      <c r="H16" s="26" t="inlineStr">
+      <c r="H16" s="33" t="inlineStr">
         <is>
           <t>Ninguno</t>
         </is>
       </c>
-      <c r="I16" s="26" t="inlineStr">
+      <c r="I16" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J16" s="26" t="inlineStr">
+      <c r="J16" s="33" t="inlineStr">
         <is>
           <t>S38</t>
         </is>
       </c>
-      <c r="K16" s="27" t="n"/>
-      <c r="L16" s="27" t="n"/>
-      <c r="M16" s="27" t="n"/>
-      <c r="N16" s="27" t="n"/>
-      <c r="O16" s="27" t="n"/>
-      <c r="P16" s="27" t="n"/>
-      <c r="Q16" s="26" t="inlineStr">
+      <c r="K16" s="34" t="n"/>
+      <c r="L16" s="34" t="n"/>
+      <c r="M16" s="34" t="n"/>
+      <c r="N16" s="34" t="n"/>
+      <c r="O16" s="34" t="n"/>
+      <c r="P16" s="34" t="n"/>
+      <c r="Q16" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R16" s="26" t="inlineStr">
+      <c r="R16" s="33" t="inlineStr">
         <is>
           <t>Nueva. La R08.2 la declara tanda propia, no efecto secundario.</t>
         </is>
       </c>
+      <c r="U16" s="41" t="inlineStr">
+        <is>
+          <t>Nada en la aplicación. Quedan las citas al documento maestro actualizadas a la R08.2 en specs, registros, CLAUDE.md y el plan, de modo que una cita por línea vuelva a apuntar donde dice.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="51" customHeight="1" s="20">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>F1B</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>F1B-01</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>Serial único y autocompletado</t>
         </is>
       </c>
-      <c r="E17" s="26" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>Código único de ticket por serial; serial obligatorio en la remisión; autocompletado de cliente, modelo y OV activas.</t>
         </is>
       </c>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="F17" s="33" t="inlineStr">
         <is>
           <t>tickets-core, zoho-sync</t>
         </is>
       </c>
-      <c r="G17" s="26" t="inlineStr">
+      <c r="G17" s="33" t="inlineStr">
         <is>
           <t>Ítems 1, 19 · §1.8 (14/08, 20/08)</t>
         </is>
       </c>
-      <c r="H17" s="26" t="inlineStr">
+      <c r="H17" s="33" t="inlineStr">
         <is>
           <t>Ninguno</t>
         </is>
       </c>
-      <c r="I17" s="26" t="inlineStr">
+      <c r="I17" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J17" s="26" t="inlineStr">
+      <c r="J17" s="33" t="inlineStr">
         <is>
           <t>S39</t>
         </is>
       </c>
-      <c r="K17" s="27" t="n"/>
-      <c r="L17" s="27" t="n"/>
-      <c r="M17" s="27" t="n"/>
-      <c r="N17" s="27" t="n"/>
-      <c r="O17" s="27" t="n"/>
-      <c r="P17" s="27" t="n"/>
-      <c r="Q17" s="26" t="inlineStr">
+      <c r="K17" s="34" t="n"/>
+      <c r="L17" s="34" t="n"/>
+      <c r="M17" s="34" t="n"/>
+      <c r="N17" s="34" t="n"/>
+      <c r="O17" s="34" t="n"/>
+      <c r="P17" s="34" t="n"/>
+      <c r="Q17" s="33" t="inlineStr">
         <is>
           <t>Ejecutada según su documento (09/09, base c45bcb1) · cierra IV-6</t>
         </is>
       </c>
-      <c r="R17" s="26" t="inlineStr">
+      <c r="R17" s="33" t="inlineStr">
         <is>
           <t>Estado según docs/sdd/F1B-01_Serial_llave_de_entrada.md. «OV activas» pasan a ser las OV libres: sin ticket vigente, no anuladas y fuera de cuarentena (F1B-11).</t>
         </is>
       </c>
+      <c r="U17" s="41" t="inlineStr">
+        <is>
+          <t>En la remisión, el serial del equipo es obligatorio, y al escribirlo se autocompletan solos el cliente, el modelo y las órdenes de venta activas de ese equipo. Cada ticket queda con su código único por serial: dos tickets del mismo equipo dejan de ser dos historias sin relación.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="39" customHeight="1" s="20">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>F1B</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>F1B-02</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>Hoja de vida: cuatro campos y enlace a Drive</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>Alta por Comercial; fecha de adquisición, fecha de factura, fin de garantía, código interno del cliente (identificador secundario); botón de enlace a la carpeta de Drive (fase 0 de migración).</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="33" t="inlineStr">
         <is>
           <t>hojas-vida</t>
         </is>
       </c>
-      <c r="G18" s="26" t="inlineStr">
+      <c r="G18" s="33" t="inlineStr">
         <is>
           <t>Ítem 9 · P8 · 27/08</t>
         </is>
       </c>
-      <c r="H18" s="26" t="inlineStr">
+      <c r="H18" s="33" t="inlineStr">
         <is>
           <t>decision/p8-p54-drive · quién carga los campos</t>
         </is>
       </c>
-      <c r="I18" s="26" t="inlineStr">
+      <c r="I18" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J18" s="26" t="inlineStr">
+      <c r="J18" s="33" t="inlineStr">
         <is>
           <t>S39</t>
         </is>
       </c>
-      <c r="K18" s="27" t="n"/>
-      <c r="L18" s="27" t="n"/>
-      <c r="M18" s="27" t="n"/>
-      <c r="N18" s="27" t="n"/>
-      <c r="O18" s="27" t="n"/>
-      <c r="P18" s="27" t="n"/>
-      <c r="Q18" s="26" t="inlineStr">
+      <c r="K18" s="34" t="n"/>
+      <c r="L18" s="34" t="n"/>
+      <c r="M18" s="34" t="n"/>
+      <c r="N18" s="34" t="n"/>
+      <c r="O18" s="34" t="n"/>
+      <c r="P18" s="34" t="n"/>
+      <c r="Q18" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R18" s="26" t="n"/>
+      <c r="R18" s="33" t="n"/>
+      <c r="U18" s="41" t="inlineStr">
+        <is>
+          <t>Cada equipo tiene hoja de vida con fecha de adquisición, fecha de factura, fin de garantía y código interno del cliente, que sirve para buscarlo cuando el cliente no usa el serial. Y un botón que abre su carpeta de Drive sin salir del ticket.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="123" customHeight="1" s="20">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>F1B</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>F1B-03</t>
         </is>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>Tipo de servicio y ticket sin OV</t>
         </is>
       </c>
-      <c r="E19" s="26" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>Desplegable inicial (Clasificaciones) que oculta pasos; prefijos autogenerados y sólo documentales (P37). P21: se confirma el modelo construido, OV opcional al crear el ticket y obligatoria en Habilitar Servicio («obligatoria para trabajar, no para recibir»). Habilitar Servicio exige remisión de entrada vigente en los tres orígenes. Retirar el origen Ticket creado obliga a relajar a propósito el invariante 3 (admitir estados cuya única salida la aplica el servidor); el recuento de pasos resultante se mide, no se supone. Garantía: OVI a nombre del cliente real (cambio de práctica). Antes de cambiar, contar los tickets que llegaron a Ingresado sin remisión.</t>
         </is>
       </c>
-      <c r="F19" s="26" t="inlineStr">
+      <c r="F19" s="33" t="inlineStr">
         <is>
           <t>tickets-core, transitions-st</t>
         </is>
       </c>
-      <c r="G19" s="26" t="inlineStr">
+      <c r="G19" s="33" t="inlineStr">
         <is>
           <t>Ítems 2, 20 · P21 (cerrado) · P37 · M1.2 (R08.2) · Decisiones 10/09 §7</t>
         </is>
       </c>
-      <c r="H19" s="26" t="inlineStr">
+      <c r="H19" s="33" t="inlineStr">
         <is>
           <t>decision/p21-ingreso-sin-ov CERRADO 10/09 · pendiente: decision/ovi-garantia-autor</t>
         </is>
       </c>
-      <c r="I19" s="26" t="inlineStr">
+      <c r="I19" s="33" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J19" s="26" t="inlineStr">
+      <c r="J19" s="33" t="inlineStr">
         <is>
           <t>S40</t>
         </is>
       </c>
-      <c r="K19" s="27" t="n"/>
-      <c r="L19" s="27" t="n"/>
-      <c r="M19" s="27" t="n"/>
-      <c r="N19" s="27" t="n"/>
-      <c r="O19" s="27" t="n"/>
-      <c r="P19" s="27" t="n"/>
-      <c r="Q19" s="26" t="inlineStr">
+      <c r="K19" s="34" t="n"/>
+      <c r="L19" s="34" t="n"/>
+      <c r="M19" s="34" t="n"/>
+      <c r="N19" s="34" t="n"/>
+      <c r="O19" s="34" t="n"/>
+      <c r="P19" s="34" t="n"/>
+      <c r="Q19" s="33" t="inlineStr">
         <is>
           <t>Ejecutable (gate cerrado 10/09)</t>
         </is>
       </c>
-      <c r="R19" s="26" t="inlineStr">
+      <c r="R19" s="33" t="inlineStr">
         <is>
           <t>P21 cerrado: deja de ser regla parametrizada. Se añade la guarda de remisión vigente y la OVI de garantía; pasa de M a L y se parte si no cabe en tres días. El trabajo de Remisión creada como espera va a F1B-08.</t>
         </is>
       </c>
+      <c r="U19" s="41" t="inlineStr">
+        <is>
+          <t>Al crear el ticket se elige el tipo de servicio en un desplegable y el formulario OCULTA los pasos que no aplican. La orden de venta es opcional al recibir el equipo y obligatoria para empezar a trabajar. «Habilitar Servicio» deja de ofrecerse si no hay remisión de entrada vigente, en los tres orígenes. Y un servicio en garantía se asocia con una OVI a nombre del cliente real.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="39" customHeight="1" s="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>F1B</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>F1B-04</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>Recepción unificada y fin del texto libre</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>Remisión con datos de cliente y equipo; accesorios por lista cerrada; foto sólo con novedad; rotulación y almacenamiento; desplegables en etapas críticas.</t>
         </is>
       </c>
-      <c r="F20" s="26" t="inlineStr">
+      <c r="F20" s="33" t="inlineStr">
         <is>
           <t>remisiones, tickets-core</t>
         </is>
       </c>
-      <c r="G20" s="26" t="inlineStr">
+      <c r="G20" s="33" t="inlineStr">
         <is>
           <t>Ítems 4, 10 · acta 03/09 tema 2</t>
         </is>
       </c>
-      <c r="H20" s="26" t="inlineStr">
+      <c r="H20" s="33" t="inlineStr">
         <is>
           <t>Ninguno</t>
         </is>
       </c>
-      <c r="I20" s="26" t="inlineStr">
+      <c r="I20" s="33" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J20" s="26" t="inlineStr">
+      <c r="J20" s="33" t="inlineStr">
         <is>
           <t>S40</t>
         </is>
       </c>
-      <c r="K20" s="27" t="n"/>
-      <c r="L20" s="27" t="n"/>
-      <c r="M20" s="27" t="n"/>
-      <c r="N20" s="27" t="n"/>
-      <c r="O20" s="27" t="n"/>
-      <c r="P20" s="27" t="n"/>
-      <c r="Q20" s="26" t="inlineStr">
+      <c r="K20" s="34" t="n"/>
+      <c r="L20" s="34" t="n"/>
+      <c r="M20" s="34" t="n"/>
+      <c r="N20" s="34" t="n"/>
+      <c r="O20" s="34" t="n"/>
+      <c r="P20" s="34" t="n"/>
+      <c r="Q20" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R20" s="26" t="n"/>
+      <c r="R20" s="33" t="n"/>
+      <c r="U20" s="41" t="inlineStr">
+        <is>
+          <t>La recepción se hace en UNA pantalla, con los datos del cliente y del equipo juntos. Los accesorios se eligen de una lista cerrada en vez de escribirse a mano, la foto se pide sólo si hay novedad, y las etapas críticas dejan de admitir texto libre. Rotulación y ubicación de almacenamiento quedan registradas.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="39" customHeight="1" s="20">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>F1B</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>F1B-05</t>
         </is>
       </c>
-      <c r="D21" s="26" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>Roles, traspaso, checkbox comercial y trazas</t>
         </is>
       </c>
-      <c r="E21" s="26" t="inlineStr">
+      <c r="E21" s="33" t="inlineStr">
         <is>
           <t>Permisos y vistas por área; traspaso formal al cambiar de fase; checkbox «Cumple condiciones comerciales»; fecha, hora y persona en toda transición, sin excepciones.</t>
         </is>
       </c>
-      <c r="F21" s="26" t="inlineStr">
+      <c r="F21" s="33" t="inlineStr">
         <is>
           <t>permissions, trazas</t>
         </is>
       </c>
-      <c r="G21" s="26" t="inlineStr">
+      <c r="G21" s="33" t="inlineStr">
         <is>
           <t>Ítems 5, 6, 7 · R08</t>
         </is>
       </c>
-      <c r="H21" s="26" t="inlineStr">
+      <c r="H21" s="33" t="inlineStr">
         <is>
           <t>Ninguno</t>
         </is>
       </c>
-      <c r="I21" s="26" t="inlineStr">
+      <c r="I21" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J21" s="26" t="inlineStr">
+      <c r="J21" s="33" t="inlineStr">
         <is>
           <t>S41</t>
         </is>
       </c>
-      <c r="K21" s="27" t="n"/>
-      <c r="L21" s="27" t="n"/>
-      <c r="M21" s="27" t="n"/>
-      <c r="N21" s="27" t="n"/>
-      <c r="O21" s="27" t="n"/>
-      <c r="P21" s="27" t="n"/>
-      <c r="Q21" s="26" t="inlineStr">
+      <c r="K21" s="34" t="n"/>
+      <c r="L21" s="34" t="n"/>
+      <c r="M21" s="34" t="n"/>
+      <c r="N21" s="34" t="n"/>
+      <c r="O21" s="34" t="n"/>
+      <c r="P21" s="34" t="n"/>
+      <c r="Q21" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R21" s="26" t="n"/>
+      <c r="R21" s="33" t="n"/>
+      <c r="U21" s="41" t="inlineStr">
+        <is>
+          <t>Cada persona ve y puede lo suyo. Al cambiar de fase hay traspaso formal, no un cambio de estado silencioso. Aparece el checkbox «Cumple condiciones comerciales». Y toda transición queda con fecha, hora y persona, SIN EXCEPCIONES: el historial deja de tener huecos.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="75" customHeight="1" s="20">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>F1B</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>F1B-06</t>
         </is>
       </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>Blueprints equipo nuevo y soporte remoto</t>
         </is>
       </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="E22" s="33" t="inlineStr">
         <is>
           <t>Flujos M1.4 y M1.5 en transitions.ts con la misma convención. Equipo nuevo con seis transiciones (Liberación desde En Proceso y desde Verificación), heredadas de F1A-03 y construidas con los datos observados. Salida rechazada de Verificación según P38. Comercial y posible-cliente se proponen dejar en Zoho CRM en 2026. El diagrama lo produce F1A-06 sin trabajo extra.</t>
         </is>
       </c>
-      <c r="F22" s="26" t="inlineStr">
+      <c r="F22" s="33" t="inlineStr">
         <is>
           <t>transitions-equipo-nuevo, transitions-soporte-remoto</t>
         </is>
       </c>
-      <c r="G22" s="26" t="inlineStr">
+      <c r="G22" s="33" t="inlineStr">
         <is>
           <t>M1.4, M1.5, M1.11, M1.12</t>
         </is>
       </c>
-      <c r="H22" s="26" t="inlineStr">
+      <c r="H22" s="33" t="inlineStr">
         <is>
           <t>decision/flujos-comercial-posible-cliente · decision/p38-verificacion-calidad (sólo la guarda y la salida rechazada)</t>
         </is>
       </c>
-      <c r="I22" s="26" t="inlineStr">
+      <c r="I22" s="33" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J22" s="26" t="inlineStr">
+      <c r="J22" s="33" t="inlineStr">
         <is>
           <t>S42</t>
         </is>
       </c>
-      <c r="K22" s="27" t="n"/>
-      <c r="L22" s="27" t="n"/>
-      <c r="M22" s="27" t="n"/>
-      <c r="N22" s="27" t="n"/>
-      <c r="O22" s="27" t="n"/>
-      <c r="P22" s="27" t="n"/>
-      <c r="Q22" s="26" t="inlineStr">
+      <c r="K22" s="34" t="n"/>
+      <c r="L22" s="34" t="n"/>
+      <c r="M22" s="34" t="n"/>
+      <c r="N22" s="34" t="n"/>
+      <c r="O22" s="34" t="n"/>
+      <c r="P22" s="34" t="n"/>
+      <c r="Q22" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R22" s="26" t="inlineStr">
+      <c r="R22" s="33" t="inlineStr">
         <is>
           <t>Seis transiciones en equipo nuevo, no cinco. P38 como gate parcial.</t>
         </is>
       </c>
+      <c r="U22" s="41" t="inlineStr">
+        <is>
+          <t>Los tickets de equipo nuevo y de soporte remoto dejan de ir por el flujo de servicio técnico: cada rama tiene sus propios estados y sus propios botones, con la misma convención. Verificación de equipo nuevo estrena su salida rechazada. El diagrama sale solo del generador de F1A-06.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="27" customHeight="1" s="20">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>F1B</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>F1B-07</t>
         </is>
       </c>
-      <c r="D23" s="26" t="inlineStr">
+      <c r="D23" s="33" t="inlineStr">
         <is>
           <t>Prioridad automática y «Mis tickets»</t>
         </is>
       </c>
-      <c r="E23" s="26" t="inlineStr">
+      <c r="E23" s="33" t="inlineStr">
         <is>
           <t>High/Low por calificación de cliente y contrato (as-is R05); lista autoordenada; edición bloqueada al técnico.</t>
         </is>
       </c>
-      <c r="F23" s="26" t="inlineStr">
+      <c r="F23" s="33" t="inlineStr">
         <is>
           <t>tickets-core</t>
         </is>
       </c>
-      <c r="G23" s="26" t="inlineStr">
+      <c r="G23" s="33" t="inlineStr">
         <is>
           <t>Ítem 8 · R05</t>
         </is>
       </c>
-      <c r="H23" s="26" t="inlineStr">
+      <c r="H23" s="33" t="inlineStr">
         <is>
           <t>decision/top5-prioridad</t>
         </is>
       </c>
-      <c r="I23" s="26" t="inlineStr">
+      <c r="I23" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J23" s="26" t="inlineStr">
+      <c r="J23" s="33" t="inlineStr">
         <is>
           <t>S43</t>
         </is>
       </c>
-      <c r="K23" s="27" t="n"/>
-      <c r="L23" s="27" t="n"/>
-      <c r="M23" s="27" t="n"/>
-      <c r="N23" s="27" t="n"/>
-      <c r="O23" s="27" t="n"/>
-      <c r="P23" s="27" t="n"/>
-      <c r="Q23" s="26" t="inlineStr">
+      <c r="K23" s="34" t="n"/>
+      <c r="L23" s="34" t="n"/>
+      <c r="M23" s="34" t="n"/>
+      <c r="N23" s="34" t="n"/>
+      <c r="O23" s="34" t="n"/>
+      <c r="P23" s="34" t="n"/>
+      <c r="Q23" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R23" s="26" t="n"/>
+      <c r="R23" s="33" t="n"/>
+      <c r="U23" s="41" t="inlineStr">
+        <is>
+          <t>La lista de tickets se ordena sola: la prioridad se calcula desde la calificación del cliente y su contrato, y el técnico no la puede editar. Y cada uno tiene su vista «Mis tickets» en lugar de buscarse en la lista general.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="99" customHeight="1" s="20">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>F1B</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>F1B-08</t>
         </is>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>Paridad de vistas y política Zoho</t>
         </is>
       </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>Listado y ficha equivalentes a Zoho Desk; lectura Zoho verificada en tickets, OV y contactos; política de escritura (P44). Tablero: IV-1 (la regex de boardView.ts:35 acierta 2 de 8 estados en_espera; se sustituye por ESTADOS_EN_ESPERA). Remisión creada entra en en_espera con área Comercial (hoy «ninguna», estados.ts:90) y alarma de 72 h en SLA_HORAS_POR_ESTADO (sla.ts:34). La vista «Todos» devuelve también los cerrados, pedidos al seleccionarla; se separa case 'todos' de default.</t>
         </is>
       </c>
-      <c r="F24" s="26" t="inlineStr">
+      <c r="F24" s="33" t="inlineStr">
         <is>
           <t>tickets-core, zoho-sync</t>
         </is>
       </c>
-      <c r="G24" s="26" t="inlineStr">
+      <c r="G24" s="33" t="inlineStr">
         <is>
           <t>Ítems 17, 22 · P44 · Decisiones 10/09 §3 y §7.1–7.2</t>
         </is>
       </c>
-      <c r="H24" s="26" t="inlineStr">
+      <c r="H24" s="33" t="inlineStr">
         <is>
           <t>decision/p44-escritura-zoho · decision/escalado-remision-creada (la alarma pone roja la guarda de C11 hasta declarar el cargo de Comercial que recibe el escalado)</t>
         </is>
       </c>
-      <c r="I24" s="26" t="inlineStr">
+      <c r="I24" s="33" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J24" s="26" t="inlineStr">
+      <c r="J24" s="33" t="inlineStr">
         <is>
           <t>S44</t>
         </is>
       </c>
-      <c r="K24" s="27" t="n"/>
-      <c r="L24" s="27" t="n"/>
-      <c r="M24" s="27" t="n"/>
-      <c r="N24" s="27" t="n"/>
-      <c r="O24" s="27" t="n"/>
-      <c r="P24" s="27" t="n"/>
-      <c r="Q24" s="26" t="inlineStr">
+      <c r="K24" s="34" t="n"/>
+      <c r="L24" s="34" t="n"/>
+      <c r="M24" s="34" t="n"/>
+      <c r="N24" s="34" t="n"/>
+      <c r="O24" s="34" t="n"/>
+      <c r="P24" s="34" t="n"/>
+      <c r="Q24" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R24" s="26" t="inlineStr">
+      <c r="R24" s="33" t="inlineStr">
         <is>
           <t>Recibe la vista «Todos» (decision/vista-todos-tablero), IV-1 y Remisión creada como espera con alarma. Pasa de M a L.</t>
         </is>
       </c>
-      <c r="S24" s="26" t="inlineStr">
+      <c r="S24" s="33" t="inlineStr">
         <is>
           <t>PARCIAL — cerrado en tablero, pendiente en alarma y paridad Zoho</t>
         </is>
       </c>
-      <c r="T24" s="26" t="inlineStr">
+      <c r="T24" s="33" t="inlineStr">
         <is>
           <t>Construido 10/09/2026 (c30c74c, b07c91c, 52277b4, b4576ef, 48d7545; archivado 821d17e, PASS WITH WARNINGS 10/10 req · 17/17 esc): vista «Todos» con cerrados, IV-1 (deja /espera/i) y Remisión creada reclasificada a espera interna. Pendiente: alarma de 72 h sobre Remisión creada (decision/escalado-remision-creada, sin cargo de Comercial asignado) y paridad de listado/ficha con Zoho (P44). Ver docs/sdd/R08.3_Expediente_de_cambios.md §2 A.6 y §8.1, contra 6be9cf0.</t>
         </is>
       </c>
+      <c r="U24" s="41" t="inlineStr">
+        <is>
+          <t>El tablero enseña bajo «En espera» los ONCE estados que lo son, no los dos que la expresión acertaba por el nombre. La vista «Todos» devuelve también los cerrados. Un ticket en «Remisión creada» aparece como espera de Comercial y salta una alarma a las 72 h si nadie le pone orden de venta. Y las vistas de listado y ficha se parecen a las de Zoho Desk lo bastante como para no echarlas de menos.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="87" customHeight="1" s="20">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>F1B</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>F1B-10</t>
         </is>
       </c>
-      <c r="D25" s="26" t="inlineStr">
+      <c r="D25" s="33" t="inlineStr">
         <is>
           <t>Orden único de precedencia entre guardas</t>
         </is>
       </c>
-      <c r="E25" s="26" t="inlineStr">
+      <c r="E25" s="33" t="inlineStr">
         <is>
           <t>Orden único de precedencia entre guardas en las dos puertas del motor (createManagedTicket y executeTransition), y en la del alta de remisión; unifica transitions-st §3.8 (a) y (b) y tickets-core §4.1. Hoy las dos puertas de la OV evalúan la misma regla en órdenes opuestos (409 frente a 422) y el 409 de estado contesta antes que el 403 de área. De las 12 pruebas de precedencia cambian al menos 2 y, con el orden «422 antes que 409», 6; tres cambian el error que ve el usuario.</t>
         </is>
       </c>
-      <c r="F25" s="26" t="inlineStr">
+      <c r="F25" s="33" t="inlineStr">
         <is>
           <t>transitions-st, tickets-core</t>
         </is>
       </c>
-      <c r="G25" s="26" t="inlineStr">
+      <c r="G25" s="33" t="inlineStr">
         <is>
           <t>transitions-st §3.8 (a) y (b) · tickets-core §4.1 · entrada 5.a de F0-01</t>
         </is>
       </c>
-      <c r="H25" s="26" t="inlineStr">
+      <c r="H25" s="33" t="inlineStr">
         <is>
           <t>— (ninguno técnico; el orden se declara en la spec)</t>
         </is>
       </c>
-      <c r="I25" s="26" t="inlineStr">
+      <c r="I25" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J25" s="26" t="inlineStr">
+      <c r="J25" s="33" t="inlineStr">
         <is>
           <t>Por asignar</t>
         </is>
       </c>
-      <c r="K25" s="27" t="n"/>
-      <c r="L25" s="27" t="n"/>
-      <c r="M25" s="27" t="n"/>
-      <c r="N25" s="27" t="n"/>
-      <c r="O25" s="27" t="n"/>
-      <c r="P25" s="27" t="n"/>
-      <c r="Q25" s="26" t="inlineStr">
+      <c r="K25" s="34" t="n"/>
+      <c r="L25" s="34" t="n"/>
+      <c r="M25" s="34" t="n"/>
+      <c r="N25" s="34" t="n"/>
+      <c r="O25" s="34" t="n"/>
+      <c r="P25" s="34" t="n"/>
+      <c r="Q25" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R25" s="26" t="inlineStr">
+      <c r="R25" s="33" t="inlineStr">
         <is>
           <t>Nueva (entrada 5.a). Numeración del plan .md: F1B-10.</t>
         </is>
       </c>
+      <c r="U25" s="41" t="inlineStr">
+        <is>
+          <t>Cuando varias cosas fallan a la vez, el usuario ve EL ERROR QUE IMPORTA y no el primero con el que se topó el servidor: primero si existe el sujeto, luego si puede, luego si el contenido vale, y por último si ya existía. Tres de los mensajes de hoy cambian. Lo que NO toca es el alta de remisión, que sigue incumpliendo ese orden en dos puntos (IV-12).</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="63" customHeight="1" s="20">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>F1B</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>F1B-09</t>
         </is>
       </c>
-      <c r="D26" s="26" t="inlineStr">
+      <c r="D26" s="33" t="inlineStr">
         <is>
           <t>audit-F1B</t>
         </is>
       </c>
-      <c r="E26" s="26" t="inlineStr">
+      <c r="E26" s="33" t="inlineStr">
         <is>
           <t>Auditoría de los tres flujos (servicio técnico, equipo nuevo, soporte remoto) leyendo el código; extensión a equipo nuevo y soporte remoto como pide M11.6.</t>
         </is>
       </c>
-      <c r="F26" s="26" t="inlineStr">
+      <c r="F26" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G26" s="26" t="inlineStr">
+      <c r="G26" s="33" t="inlineStr">
         <is>
           <t>M11.6</t>
         </is>
       </c>
-      <c r="H26" s="26" t="inlineStr">
+      <c r="H26" s="33" t="inlineStr">
         <is>
           <t>Ninguno. Hereda el generador de decision/mapa-blueprint-generado, que se construye en F1A (F1A-06) antes de F1B-06; la extensión de M11.6 deja de ser manual</t>
         </is>
       </c>
-      <c r="I26" s="26" t="inlineStr">
+      <c r="I26" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J26" s="26" t="inlineStr">
+      <c r="J26" s="33" t="inlineStr">
         <is>
           <t>S44</t>
         </is>
       </c>
-      <c r="K26" s="27" t="n"/>
-      <c r="L26" s="27" t="n"/>
-      <c r="M26" s="27" t="n"/>
-      <c r="N26" s="27" t="n"/>
-      <c r="O26" s="27" t="n"/>
-      <c r="P26" s="27" t="n"/>
-      <c r="Q26" s="26" t="inlineStr">
+      <c r="K26" s="34" t="n"/>
+      <c r="L26" s="34" t="n"/>
+      <c r="M26" s="34" t="n"/>
+      <c r="N26" s="34" t="n"/>
+      <c r="O26" s="34" t="n"/>
+      <c r="P26" s="34" t="n"/>
+      <c r="Q26" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R26" s="26" t="inlineStr">
+      <c r="R26" s="33" t="inlineStr">
         <is>
           <t>Entrada 4: auditar (S) queda separado de dibujar (F1A-06).</t>
         </is>
       </c>
+      <c r="U26" s="41" t="inlineStr">
+        <is>
+          <t>Nada en la aplicación. Queda el informe de auditoría de los tres flujos —servicio técnico, equipo nuevo y soporte remoto— leído del código.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="159" customHeight="1" s="20">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B27" s="26" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>F1B</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>F1B-11</t>
         </is>
       </c>
-      <c r="D27" s="26" t="inlineStr">
+      <c r="D27" s="33" t="inlineStr">
         <is>
           <t>Asociación OV ↔ ticket (1 : N) y subOV de lote</t>
         </is>
       </c>
-      <c r="E27" s="26" t="inlineStr">
+      <c r="E27" s="33" t="inlineStr">
         <is>
           <t>Tabla de asociación propia de la app: ticket, OV, transición que asocia, fecha, hora y persona. La FK no puede ir en sales_orders: books.sales_orders es réplica del hub (schema.sql:160) y el sync la borraría. Una asociación se marca liberada con motivo; nunca se borra. Índice único parcial: una OV con un solo ticket vigente. Aprobación y Aprobación y S. Repuestos añaden OV sin sustituir la de entrada; la fecha de OC vive en cada asociación (resuelve su reentrancia) y el bodegaje de entrada toma la de la OV asociada en Habilitar Servicio. SubOV de lote (opción A): formato OV-AAAA-NNN-SS, cuarentena de números no canónicos, saldo por lote (creadas / consumidas / libres), exclusión de OV anuladas o en borrador (el estado ya se sincroniza, schema.sql:161), acción manual «liberar subOV» con traza hasta que exista C2. El N° Ticket de Books (cf_n_ticket) sólo sugiere en el desplegable.</t>
         </is>
       </c>
-      <c r="F27" s="26" t="inlineStr">
+      <c r="F27" s="33" t="inlineStr">
         <is>
           <t>tickets-core, zoho-sync</t>
         </is>
       </c>
-      <c r="G27" s="26" t="inlineStr">
+      <c r="G27" s="33" t="inlineStr">
         <is>
           <t>M4.4 (R08.2) · P52 (cerrado) · Decisiones 10/09 §2, §7.5 y §8</t>
         </is>
       </c>
-      <c r="H27" s="26" t="inlineStr">
+      <c r="H27" s="33" t="inlineStr">
         <is>
           <t>decision/vigencia-contrato (no bloquea el núcleo) · decision/titularidad-ov-equipo (IV-8)</t>
         </is>
       </c>
-      <c r="I27" s="26" t="inlineStr">
+      <c r="I27" s="33" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J27" s="26" t="inlineStr">
+      <c r="J27" s="33" t="inlineStr">
         <is>
           <t>S41 (propuesta)</t>
         </is>
       </c>
-      <c r="K27" s="27" t="n"/>
-      <c r="L27" s="27" t="n"/>
-      <c r="M27" s="27" t="n"/>
-      <c r="N27" s="27" t="n"/>
-      <c r="O27" s="27" t="n"/>
-      <c r="P27" s="27" t="n"/>
-      <c r="Q27" s="26" t="inlineStr">
+      <c r="K27" s="34" t="n"/>
+      <c r="L27" s="34" t="n"/>
+      <c r="M27" s="34" t="n"/>
+      <c r="N27" s="34" t="n"/>
+      <c r="O27" s="34" t="n"/>
+      <c r="P27" s="34" t="n"/>
+      <c r="Q27" s="33" t="inlineStr">
         <is>
           <t>Ejecutable (núcleo)</t>
         </is>
       </c>
-      <c r="R27" s="26" t="inlineStr">
+      <c r="R27" s="33" t="inlineStr">
         <is>
           <t>Nueva. Decisiones del 10/09 (decision/n52-cardinalidad-ov y decision/subov-lote-convencion). Se parte en dos cambios: asociación 1 : N y subOV de lote. Antes: barrer si ya existe alguna subOV con formato _1.</t>
         </is>
       </c>
+      <c r="U27" s="41" t="inlineStr">
+        <is>
+          <t>Un ticket puede tener varias órdenes de venta, y se ve cuál se asoció, en qué transición, cuándo y quién. «Aprobación» AÑADE la orden de reparación sin borrar la de diagnóstico. Una orden de lote se subdivide en OV-AAAA-NNN-SS, una por equipo, con su saldo; y una asociación se libera con motivo, nunca se borra.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="51" customHeight="1" s="20">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>F1C</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>F1C-01</t>
         </is>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D28" s="33" t="inlineStr">
         <is>
           <t>C2 · Estado Anulado con motivo</t>
         </is>
       </c>
-      <c r="E28" s="26" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>Terminal Anulado con motivo tipificado; excluido de las tres métricas de servicios cumplidos; tratamiento del histórico. Al anular, libera las subOV no consumidas del ticket (sustituye la acción manual de F1B-11).</t>
         </is>
       </c>
-      <c r="F28" s="26" t="inlineStr">
+      <c r="F28" s="33" t="inlineStr">
         <is>
           <t>transitions-st, kpis</t>
         </is>
       </c>
-      <c r="G28" s="26" t="inlineStr">
+      <c r="G28" s="33" t="inlineStr">
         <is>
           <t>M1.10 · P32</t>
         </is>
       </c>
-      <c r="H28" s="26" t="inlineStr">
+      <c r="H28" s="33" t="inlineStr">
         <is>
           <t>decision/c2-anulado</t>
         </is>
       </c>
-      <c r="I28" s="26" t="inlineStr">
+      <c r="I28" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J28" s="26" t="inlineStr">
+      <c r="J28" s="33" t="inlineStr">
         <is>
           <t>S40*</t>
         </is>
       </c>
-      <c r="K28" s="27" t="n"/>
-      <c r="L28" s="27" t="n"/>
-      <c r="M28" s="27" t="n"/>
-      <c r="N28" s="27" t="n"/>
-      <c r="O28" s="27" t="n"/>
-      <c r="P28" s="27" t="n"/>
-      <c r="Q28" s="26" t="inlineStr">
+      <c r="K28" s="34" t="n"/>
+      <c r="L28" s="34" t="n"/>
+      <c r="M28" s="34" t="n"/>
+      <c r="N28" s="34" t="n"/>
+      <c r="O28" s="34" t="n"/>
+      <c r="P28" s="34" t="n"/>
+      <c r="Q28" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R28" s="26" t="inlineStr">
+      <c r="R28" s="33" t="inlineStr">
         <is>
           <t>Añade la liberación de subOV (decisión 10/09).</t>
         </is>
       </c>
+      <c r="U28" s="41" t="inlineStr">
+        <is>
+          <t>Aparece el estado «Anulado» con motivo tipificado, y los servicios abandonados dejan de contar como cumplidos en las tres métricas. Al anular, las subOV del ticket que no se consumieron se liberan solas.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="27" customHeight="1" s="20">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B29" s="26" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>F1C</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
         <is>
           <t>F1C-02</t>
         </is>
       </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="D29" s="33" t="inlineStr">
         <is>
           <t>C4 · Dos ramas facturar/entregar</t>
         </is>
       </c>
-      <c r="E29" s="26" t="inlineStr">
+      <c r="E29" s="33" t="inlineStr">
         <is>
           <t>Elimina el ciclo; estado Pendiente de facturar; conserva la primera fecha de remisión de salida.</t>
         </is>
       </c>
-      <c r="F29" s="26" t="inlineStr">
+      <c r="F29" s="33" t="inlineStr">
         <is>
           <t>transitions-st</t>
         </is>
       </c>
-      <c r="G29" s="26" t="inlineStr">
+      <c r="G29" s="33" t="inlineStr">
         <is>
           <t>M1.3.5 · P34 · P6</t>
         </is>
       </c>
-      <c r="H29" s="26" t="inlineStr">
+      <c r="H29" s="33" t="inlineStr">
         <is>
           <t>decision/c4-dos-ramas</t>
         </is>
       </c>
-      <c r="I29" s="26" t="inlineStr">
+      <c r="I29" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J29" s="26" t="inlineStr">
+      <c r="J29" s="33" t="inlineStr">
         <is>
           <t>S41*</t>
         </is>
       </c>
-      <c r="K29" s="27" t="n"/>
-      <c r="L29" s="27" t="n"/>
-      <c r="M29" s="27" t="n"/>
-      <c r="N29" s="27" t="n"/>
-      <c r="O29" s="27" t="n"/>
-      <c r="P29" s="27" t="n"/>
-      <c r="Q29" s="26" t="inlineStr">
+      <c r="K29" s="34" t="n"/>
+      <c r="L29" s="34" t="n"/>
+      <c r="M29" s="34" t="n"/>
+      <c r="N29" s="34" t="n"/>
+      <c r="O29" s="34" t="n"/>
+      <c r="P29" s="34" t="n"/>
+      <c r="Q29" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R29" s="26" t="n"/>
+      <c r="R29" s="33" t="n"/>
+      <c r="U29" s="41" t="inlineStr">
+        <is>
+          <t>Desaparece el ciclo entre facturar y entregar: dos ramas que avanzan y no vuelven, con «Pendiente de facturar» para la vía sin factura. La fecha de la primera salida del equipo deja de pisarse en cada vuelta.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="27" customHeight="1" s="20">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>F1C</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>F1C-03</t>
         </is>
       </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>C3 · Salida de las cuatro esperas</t>
         </is>
       </c>
-      <c r="E30" s="26" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>Transición de escape con caducidad; vía de escape manual con traza y motivo.</t>
         </is>
       </c>
-      <c r="F30" s="26" t="inlineStr">
+      <c r="F30" s="33" t="inlineStr">
         <is>
           <t>transitions-st</t>
         </is>
       </c>
-      <c r="G30" s="26" t="inlineStr">
+      <c r="G30" s="33" t="inlineStr">
         <is>
           <t>M1.3.4 · P31</t>
         </is>
       </c>
-      <c r="H30" s="26" t="inlineStr">
+      <c r="H30" s="33" t="inlineStr">
         <is>
           <t>decision/c3-salida-esperas</t>
         </is>
       </c>
-      <c r="I30" s="26" t="inlineStr">
+      <c r="I30" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J30" s="26" t="inlineStr">
+      <c r="J30" s="33" t="inlineStr">
         <is>
           <t>S43*</t>
         </is>
       </c>
-      <c r="K30" s="27" t="n"/>
-      <c r="L30" s="27" t="n"/>
-      <c r="M30" s="27" t="n"/>
-      <c r="N30" s="27" t="n"/>
-      <c r="O30" s="27" t="n"/>
-      <c r="P30" s="27" t="n"/>
-      <c r="Q30" s="26" t="inlineStr">
+      <c r="K30" s="34" t="n"/>
+      <c r="L30" s="34" t="n"/>
+      <c r="M30" s="34" t="n"/>
+      <c r="N30" s="34" t="n"/>
+      <c r="O30" s="34" t="n"/>
+      <c r="P30" s="34" t="n"/>
+      <c r="Q30" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R30" s="26" t="n"/>
+      <c r="R30" s="33" t="n"/>
+      <c r="U30" s="41" t="inlineStr">
+        <is>
+          <t>Los cuatro estados de espera sin salida dejan de ser callejones: aparece una transición de escape, una caducidad que la sugiere cuando el ticket lleva demasiado parado, y una vía manual con traza y motivo para lo que no encaje. Se acabó editar la base a mano.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="27" customHeight="1" s="20">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B31" s="26" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>F1C</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>F1C-04</t>
         </is>
       </c>
-      <c r="D31" s="26" t="inlineStr">
+      <c r="D31" s="33" t="inlineStr">
         <is>
           <t>C5 · Tipo de evento por transición</t>
         </is>
       </c>
-      <c r="E31" s="26" t="inlineStr">
+      <c r="E31" s="33" t="inlineStr">
         <is>
           <t>Atributo operativo/decisional/logístico en las 34 transiciones; desambiguar «Creación de informe».</t>
         </is>
       </c>
-      <c r="F31" s="26" t="inlineStr">
+      <c r="F31" s="33" t="inlineStr">
         <is>
           <t>transitions-st</t>
         </is>
       </c>
-      <c r="G31" s="26" t="inlineStr">
+      <c r="G31" s="33" t="inlineStr">
         <is>
           <t>M1.8 · P35</t>
         </is>
       </c>
-      <c r="H31" s="26" t="inlineStr">
+      <c r="H31" s="33" t="inlineStr">
         <is>
           <t>decision/c5-tipo-evento</t>
         </is>
       </c>
-      <c r="I31" s="26" t="inlineStr">
+      <c r="I31" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J31" s="26" t="inlineStr">
+      <c r="J31" s="33" t="inlineStr">
         <is>
           <t>S44*</t>
         </is>
       </c>
-      <c r="K31" s="27" t="n"/>
-      <c r="L31" s="27" t="n"/>
-      <c r="M31" s="27" t="n"/>
-      <c r="N31" s="27" t="n"/>
-      <c r="O31" s="27" t="n"/>
-      <c r="P31" s="27" t="n"/>
-      <c r="Q31" s="26" t="inlineStr">
+      <c r="K31" s="34" t="n"/>
+      <c r="L31" s="34" t="n"/>
+      <c r="M31" s="34" t="n"/>
+      <c r="N31" s="34" t="n"/>
+      <c r="O31" s="34" t="n"/>
+      <c r="P31" s="34" t="n"/>
+      <c r="Q31" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R31" s="26" t="n"/>
+      <c r="R31" s="33" t="n"/>
+      <c r="U31" s="41" t="inlineStr">
+        <is>
+          <t>Nada nuevo que pulsar, y aun así es la pieza que falta para medir: cada transición lleva su tipo —operativo, decisional o logístico—, que es lo que hace calculable el análisis de tiempos por tipo de evento.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="27" customHeight="1" s="20">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B32" s="26" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>F1C</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>F1C-05</t>
         </is>
       </c>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="D32" s="33" t="inlineStr">
         <is>
           <t>C10 · Permisos por cargo y propietario</t>
         </is>
       </c>
-      <c r="E32" s="26" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>Tres niveles: área, cargo, propietario del registro; Liberación sin factura exclusiva del gerente comercial.</t>
         </is>
       </c>
-      <c r="F32" s="26" t="inlineStr">
+      <c r="F32" s="33" t="inlineStr">
         <is>
           <t>permissions</t>
         </is>
       </c>
-      <c r="G32" s="26" t="inlineStr">
+      <c r="G32" s="33" t="inlineStr">
         <is>
           <t>M1.9.1 · P39</t>
         </is>
       </c>
-      <c r="H32" s="26" t="inlineStr">
+      <c r="H32" s="33" t="inlineStr">
         <is>
           <t>decision/c10-permisos-cargo</t>
         </is>
       </c>
-      <c r="I32" s="26" t="inlineStr">
+      <c r="I32" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J32" s="26" t="inlineStr">
+      <c r="J32" s="33" t="inlineStr">
         <is>
           <t>S44*</t>
         </is>
       </c>
-      <c r="K32" s="27" t="n"/>
-      <c r="L32" s="27" t="n"/>
-      <c r="M32" s="27" t="n"/>
-      <c r="N32" s="27" t="n"/>
-      <c r="O32" s="27" t="n"/>
-      <c r="P32" s="27" t="n"/>
-      <c r="Q32" s="26" t="inlineStr">
+      <c r="K32" s="34" t="n"/>
+      <c r="L32" s="34" t="n"/>
+      <c r="M32" s="34" t="n"/>
+      <c r="N32" s="34" t="n"/>
+      <c r="O32" s="34" t="n"/>
+      <c r="P32" s="34" t="n"/>
+      <c r="Q32" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R32" s="26" t="n"/>
+      <c r="R32" s="33" t="n"/>
+      <c r="U32" s="41" t="inlineStr">
+        <is>
+          <t>Los permisos dejan de ser sólo por área: también por cargo y por propietario del registro. «Liberación sin factura» pasa a ser exclusiva del gerente comercial, en vez de poder ejecutarla toda el área comercial.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="63" customHeight="1" s="20">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B33" s="26" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>F1C</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>F1C-06</t>
         </is>
       </c>
-      <c r="D33" s="26" t="inlineStr">
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t>C7 + C9 · Esperas que paran el reloj</t>
         </is>
       </c>
-      <c r="E33" s="26" t="inlineStr">
+      <c r="E33" s="33" t="inlineStr">
         <is>
           <t>Sub-estados de pausa; los tres bodegajes como tiempo a descontar del SLA. Construye los indicadores 48, 49 y 56 sobre el hito que dejó F1A-04 (marcaIngresoAServicio, bodegaje.ts). Bodegaje de entrada = tiempo en Remisión creada, de Fecha Remisión Entrada a la OV de entrada. Depende de F1A-07.</t>
         </is>
       </c>
-      <c r="F33" s="26" t="inlineStr">
+      <c r="F33" s="33" t="inlineStr">
         <is>
           <t>trazas, kpis</t>
         </is>
       </c>
-      <c r="G33" s="26" t="inlineStr">
+      <c r="G33" s="33" t="inlineStr">
         <is>
           <t>M1.10 · M1.6c</t>
         </is>
       </c>
-      <c r="H33" s="26" t="inlineStr">
+      <c r="H33" s="33" t="inlineStr">
         <is>
           <t>decision/c7-reloj-sla</t>
         </is>
       </c>
-      <c r="I33" s="26" t="inlineStr">
+      <c r="I33" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J33" s="26" t="inlineStr">
+      <c r="J33" s="33" t="inlineStr">
         <is>
           <t>S46*</t>
         </is>
       </c>
-      <c r="K33" s="27" t="n"/>
-      <c r="L33" s="27" t="n"/>
-      <c r="M33" s="27" t="n"/>
-      <c r="N33" s="27" t="n"/>
-      <c r="O33" s="27" t="n"/>
-      <c r="P33" s="27" t="n"/>
-      <c r="Q33" s="26" t="inlineStr">
+      <c r="K33" s="34" t="n"/>
+      <c r="L33" s="34" t="n"/>
+      <c r="M33" s="34" t="n"/>
+      <c r="N33" s="34" t="n"/>
+      <c r="O33" s="34" t="n"/>
+      <c r="P33" s="34" t="n"/>
+      <c r="Q33" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R33" s="26" t="inlineStr">
+      <c r="R33" s="33" t="inlineStr">
         <is>
           <t>Recoge los indicadores que F1A-04 no pudo construir por falta de módulo de KPIs; bodegaje de entrada sobre Remisión creada (10/09).</t>
         </is>
       </c>
+      <c r="U33" s="41" t="inlineStr">
+        <is>
+          <t>El reloj del SLA se para mientras el ticket espera a alguien de fuera, y los tres bodegajes se descuentan del tiempo comprometido. Aparecen calculados los indicadores 48, 49 y 56 sobre el hito que dejó F1A-04.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="39" customHeight="1" s="20">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B34" s="33" t="inlineStr">
         <is>
           <t>F1C</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="C34" s="33" t="inlineStr">
         <is>
           <t>F1C-07</t>
         </is>
       </c>
-      <c r="D34" s="26" t="inlineStr">
+      <c r="D34" s="33" t="inlineStr">
         <is>
           <t>C6 · QA/QC antes de la liberación</t>
         </is>
       </c>
-      <c r="E34" s="26" t="inlineStr">
+      <c r="E34" s="33" t="inlineStr">
         <is>
           <t>Etapa de QA con retrabajo; base de las validaciones con firma; depende de C12. Modelable sobre la Verificación de equipo nuevo, una vez cerrado lo que queda de P38.</t>
         </is>
       </c>
-      <c r="F34" s="26" t="inlineStr">
+      <c r="F34" s="33" t="inlineStr">
         <is>
           <t>transitions-st</t>
         </is>
       </c>
-      <c r="G34" s="26" t="inlineStr">
+      <c r="G34" s="33" t="inlineStr">
         <is>
           <t>M9.1</t>
         </is>
       </c>
-      <c r="H34" s="26" t="inlineStr">
+      <c r="H34" s="33" t="inlineStr">
         <is>
           <t>decision/c6-qa-liberacion · decision/p38-verificacion-calidad</t>
         </is>
       </c>
-      <c r="I34" s="26" t="inlineStr">
+      <c r="I34" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J34" s="26" t="inlineStr">
+      <c r="J34" s="33" t="inlineStr">
         <is>
           <t>S47*</t>
         </is>
       </c>
-      <c r="K34" s="27" t="n"/>
-      <c r="L34" s="27" t="n"/>
-      <c r="M34" s="27" t="n"/>
-      <c r="N34" s="27" t="n"/>
-      <c r="O34" s="27" t="n"/>
-      <c r="P34" s="27" t="n"/>
-      <c r="Q34" s="26" t="inlineStr">
+      <c r="K34" s="34" t="n"/>
+      <c r="L34" s="34" t="n"/>
+      <c r="M34" s="34" t="n"/>
+      <c r="N34" s="34" t="n"/>
+      <c r="O34" s="34" t="n"/>
+      <c r="P34" s="34" t="n"/>
+      <c r="Q34" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R34" s="26" t="inlineStr">
+      <c r="R34" s="33" t="inlineStr">
         <is>
           <t>Añade P38 como condición previa.</t>
         </is>
       </c>
+      <c r="U34" s="41" t="inlineStr">
+        <is>
+          <t>Antes de liberar un equipo hay una etapa de control de calidad: si no pasa, vuelve a ejecución con prioridad alta en lugar de salir igual. Se modela sobre la Verificación que equipo nuevo ya practica.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="27" customHeight="1" s="20">
-      <c r="A35" s="25" t="inlineStr">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B35" s="26" t="inlineStr">
+      <c r="B35" s="33" t="inlineStr">
         <is>
           <t>F1C</t>
         </is>
       </c>
-      <c r="C35" s="26" t="inlineStr">
+      <c r="C35" s="33" t="inlineStr">
         <is>
           <t>F1C-08</t>
         </is>
       </c>
-      <c r="D35" s="26" t="inlineStr">
+      <c r="D35" s="33" t="inlineStr">
         <is>
           <t>Rutas abreviadas</t>
         </is>
       </c>
-      <c r="E35" s="26" t="inlineStr">
+      <c r="E35" s="33" t="inlineStr">
         <is>
           <t>Equipo sin novedades y calibración directa.</t>
         </is>
       </c>
-      <c r="F35" s="26" t="inlineStr">
+      <c r="F35" s="33" t="inlineStr">
         <is>
           <t>transitions-st</t>
         </is>
       </c>
-      <c r="G35" s="26" t="inlineStr">
+      <c r="G35" s="33" t="inlineStr">
         <is>
           <t>M1.6 · P15 · P59</t>
         </is>
       </c>
-      <c r="H35" s="26" t="inlineStr">
+      <c r="H35" s="33" t="inlineStr">
         <is>
           <t>decision/p15-p59-rutas</t>
         </is>
       </c>
-      <c r="I35" s="26" t="inlineStr">
+      <c r="I35" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J35" s="26" t="inlineStr">
+      <c r="J35" s="33" t="inlineStr">
         <is>
           <t>S48*</t>
         </is>
       </c>
-      <c r="K35" s="27" t="n"/>
-      <c r="L35" s="27" t="n"/>
-      <c r="M35" s="27" t="n"/>
-      <c r="N35" s="27" t="n"/>
-      <c r="O35" s="27" t="n"/>
-      <c r="P35" s="27" t="n"/>
-      <c r="Q35" s="26" t="inlineStr">
+      <c r="K35" s="34" t="n"/>
+      <c r="L35" s="34" t="n"/>
+      <c r="M35" s="34" t="n"/>
+      <c r="N35" s="34" t="n"/>
+      <c r="O35" s="34" t="n"/>
+      <c r="P35" s="34" t="n"/>
+      <c r="Q35" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R35" s="26" t="n"/>
+      <c r="R35" s="33" t="n"/>
+      <c r="U35" s="41" t="inlineStr">
+        <is>
+          <t>Un equipo sin novedades o una calibración directa recorren una ruta corta, sin arrastrar las etapas que no aplican. Hoy pasan por todas.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="51" customHeight="1" s="20">
-      <c r="A36" s="25" t="inlineStr">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B36" s="26" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>F1D</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C36" s="33" t="inlineStr">
         <is>
           <t>F1D-01</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D36" s="33" t="inlineStr">
         <is>
           <t>Modelo de datos del catálogo</t>
         </is>
       </c>
-      <c r="E36" s="26" t="inlineStr">
+      <c r="E36" s="33" t="inlineStr">
         <is>
           <t>Fase → nivel macro → subnivel → ítem; por ítem: qué, cómo, tipo de dato y límites, obligatoriedad, criterio de falla, evidencia, repuesto, acción si No OK, ítems relacionados, comentario de falla; versionado por marca-modelo.</t>
         </is>
       </c>
-      <c r="F36" s="26" t="inlineStr">
+      <c r="F36" s="33" t="inlineStr">
         <is>
           <t>diagnostico-checklist</t>
         </is>
       </c>
-      <c r="G36" s="26" t="inlineStr">
+      <c r="G36" s="33" t="inlineStr">
         <is>
           <t>M2.2 · acta 03/09 tema 3 · Excel GRIMM v9</t>
         </is>
       </c>
-      <c r="H36" s="26" t="inlineStr">
+      <c r="H36" s="33" t="inlineStr">
         <is>
           <t>Ninguno (estructura validada 03/09)</t>
         </is>
       </c>
-      <c r="I36" s="26" t="inlineStr">
+      <c r="I36" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J36" s="26" t="inlineStr">
+      <c r="J36" s="33" t="inlineStr">
         <is>
           <t>S42</t>
         </is>
       </c>
-      <c r="K36" s="27" t="n"/>
-      <c r="L36" s="27" t="n"/>
-      <c r="M36" s="27" t="n"/>
-      <c r="N36" s="27" t="n"/>
-      <c r="O36" s="27" t="n"/>
-      <c r="P36" s="27" t="n"/>
-      <c r="Q36" s="26" t="inlineStr">
+      <c r="K36" s="34" t="n"/>
+      <c r="L36" s="34" t="n"/>
+      <c r="M36" s="34" t="n"/>
+      <c r="N36" s="34" t="n"/>
+      <c r="O36" s="34" t="n"/>
+      <c r="P36" s="34" t="n"/>
+      <c r="Q36" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R36" s="26" t="n"/>
+      <c r="R36" s="33" t="n"/>
+      <c r="U36" s="41" t="inlineStr">
+        <is>
+          <t>Nada visible para el técnico todavía: queda el modelo de datos del árbol de inspección —fase, nivel macro, subnivel, ítem— con criterio de falla, evidencia, repuesto y acción por ítem, versionado por marca y modelo.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="27" customHeight="1" s="20">
-      <c r="A37" s="25" t="inlineStr">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B37" s="26" t="inlineStr">
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>F1D</t>
         </is>
       </c>
-      <c r="C37" s="26" t="inlineStr">
+      <c r="C37" s="33" t="inlineStr">
         <is>
           <t>F1D-02</t>
         </is>
       </c>
-      <c r="D37" s="26" t="inlineStr">
+      <c r="D37" s="33" t="inlineStr">
         <is>
           <t>Importador desde Excel</t>
         </is>
       </c>
-      <c r="E37" s="26" t="inlineStr">
+      <c r="E37" s="33" t="inlineStr">
         <is>
           <t>Carga del catálogo (GRIMM EDM180 v9, Horiba APxA-370) con validación y reporte de filas rechazadas; reentrante.</t>
         </is>
       </c>
-      <c r="F37" s="26" t="inlineStr">
+      <c r="F37" s="33" t="inlineStr">
         <is>
           <t>diagnostico-checklist</t>
         </is>
       </c>
-      <c r="G37" s="26" t="inlineStr">
+      <c r="G37" s="33" t="inlineStr">
         <is>
           <t>M2.1 (plantillas Excel)</t>
         </is>
       </c>
-      <c r="H37" s="26" t="inlineStr">
+      <c r="H37" s="33" t="inlineStr">
         <is>
           <t>Versión depurada del Excel (11/09); se puede importar v9</t>
         </is>
       </c>
-      <c r="I37" s="26" t="inlineStr">
+      <c r="I37" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J37" s="26" t="inlineStr">
+      <c r="J37" s="33" t="inlineStr">
         <is>
           <t>S43</t>
         </is>
       </c>
-      <c r="K37" s="27" t="n"/>
-      <c r="L37" s="27" t="n"/>
-      <c r="M37" s="27" t="n"/>
-      <c r="N37" s="27" t="n"/>
-      <c r="O37" s="27" t="n"/>
-      <c r="P37" s="27" t="n"/>
-      <c r="Q37" s="26" t="inlineStr">
+      <c r="K37" s="34" t="n"/>
+      <c r="L37" s="34" t="n"/>
+      <c r="M37" s="34" t="n"/>
+      <c r="N37" s="34" t="n"/>
+      <c r="O37" s="34" t="n"/>
+      <c r="P37" s="34" t="n"/>
+      <c r="Q37" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R37" s="26" t="n"/>
+      <c r="R37" s="33" t="n"/>
+      <c r="U37" s="41" t="inlineStr">
+        <is>
+          <t>Se puede cargar el árbol de inspección de un equipo desde su Excel, con un reporte de las filas que no entraron y por qué. Y se puede volver a cargar sin duplicar nada, que es lo que permite corregir el catálogo sin miedo.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="51" customHeight="1" s="20">
-      <c r="A38" s="25" t="inlineStr">
+      <c r="A38" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B38" s="26" t="inlineStr">
+      <c r="B38" s="33" t="inlineStr">
         <is>
           <t>F1D</t>
         </is>
       </c>
-      <c r="C38" s="26" t="inlineStr">
+      <c r="C38" s="33" t="inlineStr">
         <is>
           <t>F1D-03</t>
         </is>
       </c>
-      <c r="D38" s="26" t="inlineStr">
+      <c r="D38" s="33" t="inlineStr">
         <is>
           <t>Niveles macro (N1) como transiciones internas</t>
         </is>
       </c>
-      <c r="E38" s="26" t="inlineStr">
+      <c r="E38" s="33" t="inlineStr">
         <is>
           <t>Transiciones dentro de Rev./Diagnostico generadas desde el N1 del catálogo importado (los ocho N1 del GRIMM o su agrupación en las cuatro macro-fases, según P45); N2/N3 son los checkpoints; el equipo sin novedades recorre las macros.</t>
         </is>
       </c>
-      <c r="F38" s="26" t="inlineStr">
+      <c r="F38" s="33" t="inlineStr">
         <is>
           <t>transitions-st, diagnostico-checklist</t>
         </is>
       </c>
-      <c r="G38" s="26" t="inlineStr">
+      <c r="G38" s="33" t="inlineStr">
         <is>
           <t>M2.1 · P59 · docs/inspecciones</t>
         </is>
       </c>
-      <c r="H38" s="26" t="inlineStr">
+      <c r="H38" s="33" t="inlineStr">
         <is>
           <t>decision/p45-macro-fases (¿transición = N1 o macro-fase?)</t>
         </is>
       </c>
-      <c r="I38" s="26" t="inlineStr">
+      <c r="I38" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J38" s="26" t="inlineStr">
+      <c r="J38" s="33" t="inlineStr">
         <is>
           <t>S44</t>
         </is>
       </c>
-      <c r="K38" s="27" t="n"/>
-      <c r="L38" s="27" t="n"/>
-      <c r="M38" s="27" t="n"/>
-      <c r="N38" s="27" t="n"/>
-      <c r="O38" s="27" t="n"/>
-      <c r="P38" s="27" t="n"/>
-      <c r="Q38" s="26" t="inlineStr">
+      <c r="K38" s="34" t="n"/>
+      <c r="L38" s="34" t="n"/>
+      <c r="M38" s="34" t="n"/>
+      <c r="N38" s="34" t="n"/>
+      <c r="O38" s="34" t="n"/>
+      <c r="P38" s="34" t="n"/>
+      <c r="Q38" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R38" s="26" t="n"/>
+      <c r="R38" s="33" t="n"/>
+      <c r="U38" s="41" t="inlineStr">
+        <is>
+          <t>Dentro de «Rev./Diagnostico» aparecen las fases del diagnóstico como pasos propios, generadas desde el catálogo del equipo. El técnico deja de tener un único estado opaco de varios días y pasa a verse por dónde va.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="39" customHeight="1" s="20">
-      <c r="A39" s="25" t="inlineStr">
+      <c r="A39" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B39" s="26" t="inlineStr">
+      <c r="B39" s="33" t="inlineStr">
         <is>
           <t>F1D</t>
         </is>
       </c>
-      <c r="C39" s="26" t="inlineStr">
+      <c r="C39" s="33" t="inlineStr">
         <is>
           <t>F1D-04</t>
         </is>
       </c>
-      <c r="D39" s="26" t="inlineStr">
+      <c r="D39" s="33" t="inlineStr">
         <is>
           <t>Captura por visita y validación por macro</t>
         </is>
       </c>
-      <c r="E39" s="26" t="inlineStr">
+      <c r="E39" s="33" t="inlineStr">
         <is>
           <t>Macro OK → subniveles conformes; No OK → despliegue del detalle; OK/No OK obligatorio para transicionar; valores con rango; foto sólo con novedad.</t>
         </is>
       </c>
-      <c r="F39" s="26" t="inlineStr">
+      <c r="F39" s="33" t="inlineStr">
         <is>
           <t>diagnostico-checklist</t>
         </is>
       </c>
-      <c r="G39" s="26" t="inlineStr">
+      <c r="G39" s="33" t="inlineStr">
         <is>
           <t>M2.3 · acta 03/09</t>
         </is>
       </c>
-      <c r="H39" s="26" t="inlineStr">
+      <c r="H39" s="33" t="inlineStr">
         <is>
           <t>Ninguno</t>
         </is>
       </c>
-      <c r="I39" s="26" t="inlineStr">
+      <c r="I39" s="33" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J39" s="26" t="inlineStr">
+      <c r="J39" s="33" t="inlineStr">
         <is>
           <t>S45</t>
         </is>
       </c>
-      <c r="K39" s="27" t="n"/>
-      <c r="L39" s="27" t="n"/>
-      <c r="M39" s="27" t="n"/>
-      <c r="N39" s="27" t="n"/>
-      <c r="O39" s="27" t="n"/>
-      <c r="P39" s="27" t="n"/>
-      <c r="Q39" s="26" t="inlineStr">
+      <c r="K39" s="34" t="n"/>
+      <c r="L39" s="34" t="n"/>
+      <c r="M39" s="34" t="n"/>
+      <c r="N39" s="34" t="n"/>
+      <c r="O39" s="34" t="n"/>
+      <c r="P39" s="34" t="n"/>
+      <c r="Q39" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R39" s="26" t="n"/>
+      <c r="R39" s="33" t="n"/>
+      <c r="U39" s="41" t="inlineStr">
+        <is>
+          <t>El técnico hace la inspección EN LA APLICACIÓN: marca OK o No OK por nivel macro y, si algo sale No OK, se despliega el detalle de ese bloque. Sin marcar no se avanza. Los valores con rango se validan al escribirlos y la foto se pide sólo cuando hay novedad.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="39" customHeight="1" s="20">
-      <c r="A40" s="25" t="inlineStr">
+      <c r="A40" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B40" s="26" t="inlineStr">
+      <c r="B40" s="33" t="inlineStr">
         <is>
           <t>F1D</t>
         </is>
       </c>
-      <c r="C40" s="26" t="inlineStr">
+      <c r="C40" s="33" t="inlineStr">
         <is>
           <t>F1D-05</t>
         </is>
       </c>
-      <c r="D40" s="26" t="inlineStr">
+      <c r="D40" s="33" t="inlineStr">
         <is>
           <t>Encadenamiento No OK</t>
         </is>
       </c>
-      <c r="E40" s="26" t="inlineStr">
+      <c r="E40" s="33" t="inlineStr">
         <is>
           <t>Activación de ítems relacionados (tabla origen → destino como «Flujo No OK 2»); rama activa; acción sugerida; traza de activación.</t>
         </is>
       </c>
-      <c r="F40" s="26" t="inlineStr">
+      <c r="F40" s="33" t="inlineStr">
         <is>
           <t>diagnostico-checklist</t>
         </is>
       </c>
-      <c r="G40" s="26" t="inlineStr">
+      <c r="G40" s="33" t="inlineStr">
         <is>
           <t>Excel v7/v9 · tarea Gerencia 11/09</t>
         </is>
       </c>
-      <c r="H40" s="26" t="inlineStr">
+      <c r="H40" s="33" t="inlineStr">
         <is>
           <t>Ninguno</t>
         </is>
       </c>
-      <c r="I40" s="26" t="inlineStr">
+      <c r="I40" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J40" s="26" t="inlineStr">
+      <c r="J40" s="33" t="inlineStr">
         <is>
           <t>S46</t>
         </is>
       </c>
-      <c r="K40" s="27" t="n"/>
-      <c r="L40" s="27" t="n"/>
-      <c r="M40" s="27" t="n"/>
-      <c r="N40" s="27" t="n"/>
-      <c r="O40" s="27" t="n"/>
-      <c r="P40" s="27" t="n"/>
-      <c r="Q40" s="26" t="inlineStr">
+      <c r="K40" s="34" t="n"/>
+      <c r="L40" s="34" t="n"/>
+      <c r="M40" s="34" t="n"/>
+      <c r="N40" s="34" t="n"/>
+      <c r="O40" s="34" t="n"/>
+      <c r="P40" s="34" t="n"/>
+      <c r="Q40" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R40" s="26" t="n"/>
+      <c r="R40" s="33" t="n"/>
+      <c r="U40" s="41" t="inlineStr">
+        <is>
+          <t>Al marcar un ítem No OK, el sistema ACTIVA SOLO los ítems relacionados y los muestra como rama activa, con la acción sugerida y la traza de desde qué ítem se activaron. El conocimiento de qué mirar cuando algo falla deja de estar en la cabeza del técnico.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="75" customHeight="1" s="20">
-      <c r="A41" s="25" t="inlineStr">
+      <c r="A41" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B41" s="26" t="inlineStr">
+      <c r="B41" s="33" t="inlineStr">
         <is>
           <t>F1D</t>
         </is>
       </c>
-      <c r="C41" s="26" t="inlineStr">
+      <c r="C41" s="33" t="inlineStr">
         <is>
           <t>F1D-06</t>
         </is>
       </c>
-      <c r="D41" s="26" t="inlineStr">
+      <c r="D41" s="33" t="inlineStr">
         <is>
           <t>Criterio de falla en acción y repuestos por etapa</t>
         </is>
       </c>
-      <c r="E41" s="26" t="inlineStr">
+      <c r="E41" s="33" t="inlineStr">
         <is>
           <t>Alerta registra; Cobrable genera línea de cotización (repuesto + horas); Bloqueante impide liberar; sólo repuestos de la etapa (Zoho Books por categoría).</t>
         </is>
       </c>
-      <c r="F41" s="26" t="inlineStr">
+      <c r="F41" s="33" t="inlineStr">
         <is>
           <t>diagnostico-checklist, inventario-lectura</t>
         </is>
       </c>
-      <c r="G41" s="26" t="inlineStr">
+      <c r="G41" s="33" t="inlineStr">
         <is>
           <t>M2.2 · M2.3 R08 · ítem 12 (tema tratado sin decisión: sólo tarea, acta:368-370)</t>
         </is>
       </c>
-      <c r="H41" s="26" t="inlineStr">
+      <c r="H41" s="33" t="inlineStr">
         <is>
           <t>Ninguno</t>
         </is>
       </c>
-      <c r="I41" s="26" t="inlineStr">
+      <c r="I41" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J41" s="26" t="inlineStr">
+      <c r="J41" s="33" t="inlineStr">
         <is>
           <t>S46</t>
         </is>
       </c>
-      <c r="K41" s="27" t="n"/>
-      <c r="L41" s="27" t="n"/>
-      <c r="M41" s="27" t="n"/>
-      <c r="N41" s="27" t="n"/>
-      <c r="O41" s="27" t="n"/>
-      <c r="P41" s="27" t="n"/>
-      <c r="Q41" s="26" t="inlineStr">
+      <c r="K41" s="34" t="n"/>
+      <c r="L41" s="34" t="n"/>
+      <c r="M41" s="34" t="n"/>
+      <c r="N41" s="34" t="n"/>
+      <c r="O41" s="34" t="n"/>
+      <c r="P41" s="34" t="n"/>
+      <c r="Q41" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R41" s="26" t="inlineStr">
+      <c r="R41" s="33" t="inlineStr">
         <is>
           <t>Barrido del registro F0-01: el tema 4 del 03/09 salió sin decisión. No cambia la tanda; cambia lo que espera quien la ejecute.</t>
         </is>
       </c>
+      <c r="U41" s="41" t="inlineStr">
+        <is>
+          <t>Un ítem marcado Cobrable genera su línea de cotización con repuesto y horas; uno Bloqueante impide liberar el equipo; uno de Alerta sólo queda registrado. Y la lista de repuestos que se ofrece es la de esa etapa, no el inventario entero.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="27" customHeight="1" s="20">
-      <c r="A42" s="25" t="inlineStr">
+      <c r="A42" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B42" s="26" t="inlineStr">
+      <c r="B42" s="33" t="inlineStr">
         <is>
           <t>F1D</t>
         </is>
       </c>
-      <c r="C42" s="26" t="inlineStr">
+      <c r="C42" s="33" t="inlineStr">
         <is>
           <t>F1D-07</t>
         </is>
       </c>
-      <c r="D42" s="26" t="inlineStr">
+      <c r="D42" s="33" t="inlineStr">
         <is>
           <t>Formulario de falla nueva</t>
         </is>
       </c>
-      <c r="E42" s="26" t="inlineStr">
+      <c r="E42" s="33" t="inlineStr">
         <is>
           <t>Formulario condicional con la misma estructura del catálogo; alimenta la base de conocimiento; bloqueante o aviso según decisión.</t>
         </is>
       </c>
-      <c r="F42" s="26" t="inlineStr">
+      <c r="F42" s="33" t="inlineStr">
         <is>
           <t>diagnostico-checklist</t>
         </is>
       </c>
-      <c r="G42" s="26" t="inlineStr">
+      <c r="G42" s="33" t="inlineStr">
         <is>
           <t>Acta 03/09 tema 5</t>
         </is>
       </c>
-      <c r="H42" s="26" t="inlineStr">
+      <c r="H42" s="33" t="inlineStr">
         <is>
           <t>decision/falla-nueva-bloqueante (Gustavo)</t>
         </is>
       </c>
-      <c r="I42" s="26" t="inlineStr">
+      <c r="I42" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J42" s="26" t="inlineStr">
+      <c r="J42" s="33" t="inlineStr">
         <is>
           <t>S47</t>
         </is>
       </c>
-      <c r="K42" s="27" t="n"/>
-      <c r="L42" s="27" t="n"/>
-      <c r="M42" s="27" t="n"/>
-      <c r="N42" s="27" t="n"/>
-      <c r="O42" s="27" t="n"/>
-      <c r="P42" s="27" t="n"/>
-      <c r="Q42" s="26" t="inlineStr">
+      <c r="K42" s="34" t="n"/>
+      <c r="L42" s="34" t="n"/>
+      <c r="M42" s="34" t="n"/>
+      <c r="N42" s="34" t="n"/>
+      <c r="O42" s="34" t="n"/>
+      <c r="P42" s="34" t="n"/>
+      <c r="Q42" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R42" s="26" t="n"/>
+      <c r="R42" s="33" t="n"/>
+      <c r="U42" s="41" t="inlineStr">
+        <is>
+          <t>Si aparece una falla que el catálogo no tiene, el técnico la registra ahí mismo en un formulario con la misma estructura, y esa falla alimenta la base de conocimiento en vez de perderse en un comentario.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="39" customHeight="1" s="20">
-      <c r="A43" s="25" t="inlineStr">
+      <c r="A43" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B43" s="26" t="inlineStr">
+      <c r="B43" s="33" t="inlineStr">
         <is>
           <t>F1D</t>
         </is>
       </c>
-      <c r="C43" s="26" t="inlineStr">
+      <c r="C43" s="33" t="inlineStr">
         <is>
           <t>F1D-08</t>
         </is>
       </c>
-      <c r="D43" s="26" t="inlineStr">
+      <c r="D43" s="33" t="inlineStr">
         <is>
           <t>Segundo equipo (Horiba APxA-370)</t>
         </is>
       </c>
-      <c r="E43" s="26" t="inlineStr">
+      <c r="E43" s="33" t="inlineStr">
         <is>
           <t>Importar y recorrer un Horiba para demostrar que incorporar un equipo es configuración.</t>
         </is>
       </c>
-      <c r="F43" s="26" t="inlineStr">
+      <c r="F43" s="33" t="inlineStr">
         <is>
           <t>diagnostico-checklist</t>
         </is>
       </c>
-      <c r="G43" s="26" t="inlineStr">
+      <c r="G43" s="33" t="inlineStr">
         <is>
           <t>Acta 03/09 (macros coinciden)</t>
         </is>
       </c>
-      <c r="H43" s="26" t="inlineStr">
+      <c r="H43" s="33" t="inlineStr">
         <is>
           <t>Catálogo Horiba depurado</t>
         </is>
       </c>
-      <c r="I43" s="26" t="inlineStr">
+      <c r="I43" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J43" s="26" t="inlineStr">
+      <c r="J43" s="33" t="inlineStr">
         <is>
           <t>S47</t>
         </is>
       </c>
-      <c r="K43" s="27" t="n"/>
-      <c r="L43" s="27" t="n"/>
-      <c r="M43" s="27" t="n"/>
-      <c r="N43" s="27" t="n"/>
-      <c r="O43" s="27" t="n"/>
-      <c r="P43" s="27" t="n"/>
-      <c r="Q43" s="26" t="inlineStr">
+      <c r="K43" s="34" t="n"/>
+      <c r="L43" s="34" t="n"/>
+      <c r="M43" s="34" t="n"/>
+      <c r="N43" s="34" t="n"/>
+      <c r="O43" s="34" t="n"/>
+      <c r="P43" s="34" t="n"/>
+      <c r="Q43" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R43" s="26" t="n"/>
+      <c r="R43" s="33" t="n"/>
+      <c r="U43" s="41" t="inlineStr">
+        <is>
+          <t>Un Horiba APxA-370 se recorre entero de principio a fin, demostrando que incorporar un equipo nuevo al sistema es CONFIGURARLO y no programarlo. Es la prueba de que el modelo aguanta más de una marca.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="27" customHeight="1" s="20">
-      <c r="A44" s="25" t="inlineStr">
+      <c r="A44" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B44" s="26" t="inlineStr">
+      <c r="B44" s="33" t="inlineStr">
         <is>
           <t>F1D</t>
         </is>
       </c>
-      <c r="C44" s="26" t="inlineStr">
+      <c r="C44" s="33" t="inlineStr">
         <is>
           <t>F1D-09</t>
         </is>
       </c>
-      <c r="D44" s="26" t="inlineStr">
+      <c r="D44" s="33" t="inlineStr">
         <is>
           <t>audit-F1D</t>
         </is>
       </c>
-      <c r="E44" s="26" t="inlineStr">
+      <c r="E44" s="33" t="inlineStr">
         <is>
           <t>Coherencia macro-transiciones ↔ catálogo; ítems sin criterio; ramas sin salida.</t>
         </is>
       </c>
-      <c r="F44" s="26" t="inlineStr">
+      <c r="F44" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G44" s="26" t="inlineStr">
+      <c r="G44" s="33" t="inlineStr">
         <is>
           <t>M11.6</t>
         </is>
       </c>
-      <c r="H44" s="26" t="inlineStr">
+      <c r="H44" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I44" s="26" t="inlineStr">
+      <c r="I44" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J44" s="26" t="inlineStr">
+      <c r="J44" s="33" t="inlineStr">
         <is>
           <t>S47</t>
         </is>
       </c>
-      <c r="K44" s="27" t="n"/>
-      <c r="L44" s="27" t="n"/>
-      <c r="M44" s="27" t="n"/>
-      <c r="N44" s="27" t="n"/>
-      <c r="O44" s="27" t="n"/>
-      <c r="P44" s="27" t="n"/>
-      <c r="Q44" s="26" t="inlineStr">
+      <c r="K44" s="34" t="n"/>
+      <c r="L44" s="34" t="n"/>
+      <c r="M44" s="34" t="n"/>
+      <c r="N44" s="34" t="n"/>
+      <c r="O44" s="34" t="n"/>
+      <c r="P44" s="34" t="n"/>
+      <c r="Q44" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R44" s="26" t="n"/>
+      <c r="R44" s="33" t="n"/>
+      <c r="U44" s="41" t="inlineStr">
+        <is>
+          <t>Nada en la aplicación. Queda la auditoría del diagnóstico: coherencia entre las macro-transiciones y el catálogo, ítems sin criterio de falla y ramas de encadenamiento sin salida.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="27" customHeight="1" s="20">
-      <c r="A45" s="25" t="inlineStr">
+      <c r="A45" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B45" s="26" t="inlineStr">
+      <c r="B45" s="33" t="inlineStr">
         <is>
           <t>F1E</t>
         </is>
       </c>
-      <c r="C45" s="26" t="inlineStr">
+      <c r="C45" s="33" t="inlineStr">
         <is>
           <t>F1E-01</t>
         </is>
       </c>
-      <c r="D45" s="26" t="inlineStr">
+      <c r="D45" s="33" t="inlineStr">
         <is>
           <t>Modelo del informe</t>
         </is>
       </c>
-      <c r="E45" s="26" t="inlineStr">
+      <c r="E45" s="33" t="inlineStr">
         <is>
           <t>Tres bloques (estado inicial, diagnóstico, repuestos); campos abiertos en F1; comentario de falla volcado automáticamente ante No OK.</t>
         </is>
       </c>
-      <c r="F45" s="26" t="inlineStr">
+      <c r="F45" s="33" t="inlineStr">
         <is>
           <t>informes</t>
         </is>
       </c>
-      <c r="G45" s="26" t="inlineStr">
+      <c r="G45" s="33" t="inlineStr">
         <is>
           <t>Acta 03/09 tema 6 · M2.5</t>
         </is>
       </c>
-      <c r="H45" s="26" t="inlineStr">
+      <c r="H45" s="33" t="inlineStr">
         <is>
           <t>decision/p14-remisiones-entrada</t>
         </is>
       </c>
-      <c r="I45" s="26" t="inlineStr">
+      <c r="I45" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J45" s="26" t="inlineStr">
+      <c r="J45" s="33" t="inlineStr">
         <is>
           <t>S46</t>
         </is>
       </c>
-      <c r="K45" s="27" t="n"/>
-      <c r="L45" s="27" t="n"/>
-      <c r="M45" s="27" t="n"/>
-      <c r="N45" s="27" t="n"/>
-      <c r="O45" s="27" t="n"/>
-      <c r="P45" s="27" t="n"/>
-      <c r="Q45" s="26" t="inlineStr">
+      <c r="K45" s="34" t="n"/>
+      <c r="L45" s="34" t="n"/>
+      <c r="M45" s="34" t="n"/>
+      <c r="N45" s="34" t="n"/>
+      <c r="O45" s="34" t="n"/>
+      <c r="P45" s="34" t="n"/>
+      <c r="Q45" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R45" s="26" t="n"/>
+      <c r="R45" s="33" t="n"/>
+      <c r="U45" s="41" t="inlineStr">
+        <is>
+          <t>Nada visible todavía: queda el modelo del informe con sus tres bloques —estado inicial, diagnóstico y repuestos—, y la regla de que el comentario de falla se vuelca solo cuando un ítem sale No OK.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="27" customHeight="1" s="20">
-      <c r="A46" s="25" t="inlineStr">
+      <c r="A46" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B46" s="26" t="inlineStr">
+      <c r="B46" s="33" t="inlineStr">
         <is>
           <t>F1E</t>
         </is>
       </c>
-      <c r="C46" s="26" t="inlineStr">
+      <c r="C46" s="33" t="inlineStr">
         <is>
           <t>F1E-02</t>
         </is>
       </c>
-      <c r="D46" s="26" t="inlineStr">
+      <c r="D46" s="33" t="inlineStr">
         <is>
           <t>Informe de diagnóstico</t>
         </is>
       </c>
-      <c r="E46" s="26" t="inlineStr">
+      <c r="E46" s="33" t="inlineStr">
         <is>
           <t>Generación por plantilla desde ticket + checklist; nomenclatura legible por comentario, sin diccionario aparte.</t>
         </is>
       </c>
-      <c r="F46" s="26" t="inlineStr">
+      <c r="F46" s="33" t="inlineStr">
         <is>
           <t>informes</t>
         </is>
       </c>
-      <c r="G46" s="26" t="inlineStr">
+      <c r="G46" s="33" t="inlineStr">
         <is>
           <t>M2.5 · acta 03/09</t>
         </is>
       </c>
-      <c r="H46" s="26" t="inlineStr">
+      <c r="H46" s="33" t="inlineStr">
         <is>
           <t>Ninguno</t>
         </is>
       </c>
-      <c r="I46" s="26" t="inlineStr">
+      <c r="I46" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J46" s="26" t="inlineStr">
+      <c r="J46" s="33" t="inlineStr">
         <is>
           <t>S47</t>
         </is>
       </c>
-      <c r="K46" s="27" t="n"/>
-      <c r="L46" s="27" t="n"/>
-      <c r="M46" s="27" t="n"/>
-      <c r="N46" s="27" t="n"/>
-      <c r="O46" s="27" t="n"/>
-      <c r="P46" s="27" t="n"/>
-      <c r="Q46" s="26" t="inlineStr">
+      <c r="K46" s="34" t="n"/>
+      <c r="L46" s="34" t="n"/>
+      <c r="M46" s="34" t="n"/>
+      <c r="N46" s="34" t="n"/>
+      <c r="O46" s="34" t="n"/>
+      <c r="P46" s="34" t="n"/>
+      <c r="Q46" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R46" s="26" t="n"/>
+      <c r="R46" s="33" t="n"/>
+      <c r="U46" s="41" t="inlineStr">
+        <is>
+          <t>El informe de diagnóstico se genera SOLO desde el ticket y el checklist, con su plantilla. Se acabó redactarlo a mano a partir de notas.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="27" customHeight="1" s="20">
-      <c r="A47" s="25" t="inlineStr">
+      <c r="A47" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B47" s="26" t="inlineStr">
+      <c r="B47" s="33" t="inlineStr">
         <is>
           <t>F1E</t>
         </is>
       </c>
-      <c r="C47" s="26" t="inlineStr">
+      <c r="C47" s="33" t="inlineStr">
         <is>
           <t>F1E-03</t>
         </is>
       </c>
-      <c r="D47" s="26" t="inlineStr">
+      <c r="D47" s="33" t="inlineStr">
         <is>
           <t>Informe de salida con motivos tipificados</t>
         </is>
       </c>
-      <c r="E47" s="26" t="inlineStr">
+      <c r="E47" s="33" t="inlineStr">
         <is>
           <t>Rojo → verde si se corrigió; rojo con motivo (cliente no aprueba · repuesto inexistente · sin solución); evidencia; conclusión derivada.</t>
         </is>
       </c>
-      <c r="F47" s="26" t="inlineStr">
+      <c r="F47" s="33" t="inlineStr">
         <is>
           <t>informes</t>
         </is>
       </c>
-      <c r="G47" s="26" t="inlineStr">
+      <c r="G47" s="33" t="inlineStr">
         <is>
           <t>M2.5 (27/08)</t>
         </is>
       </c>
-      <c r="H47" s="26" t="inlineStr">
+      <c r="H47" s="33" t="inlineStr">
         <is>
           <t>C2 recomendado antes</t>
         </is>
       </c>
-      <c r="I47" s="26" t="inlineStr">
+      <c r="I47" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J47" s="26" t="inlineStr">
+      <c r="J47" s="33" t="inlineStr">
         <is>
           <t>S48</t>
         </is>
       </c>
-      <c r="K47" s="27" t="n"/>
-      <c r="L47" s="27" t="n"/>
-      <c r="M47" s="27" t="n"/>
-      <c r="N47" s="27" t="n"/>
-      <c r="O47" s="27" t="n"/>
-      <c r="P47" s="27" t="n"/>
-      <c r="Q47" s="26" t="inlineStr">
+      <c r="K47" s="34" t="n"/>
+      <c r="L47" s="34" t="n"/>
+      <c r="M47" s="34" t="n"/>
+      <c r="N47" s="34" t="n"/>
+      <c r="O47" s="34" t="n"/>
+      <c r="P47" s="34" t="n"/>
+      <c r="Q47" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R47" s="26" t="n"/>
+      <c r="R47" s="33" t="n"/>
+      <c r="U47" s="41" t="inlineStr">
+        <is>
+          <t>El informe de salida dice qué estaba en rojo y pasó a verde, y qué sigue en rojo con su motivo tipificado —el cliente no aprobó, el repuesto no existe, no tiene solución—, con su evidencia y la conclusión derivada.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="27" customHeight="1" s="20">
-      <c r="A48" s="25" t="inlineStr">
+      <c r="A48" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B48" s="26" t="inlineStr">
+      <c r="B48" s="33" t="inlineStr">
         <is>
           <t>F1E</t>
         </is>
       </c>
-      <c r="C48" s="26" t="inlineStr">
+      <c r="C48" s="33" t="inlineStr">
         <is>
           <t>F1E-04</t>
         </is>
       </c>
-      <c r="D48" s="26" t="inlineStr">
+      <c r="D48" s="33" t="inlineStr">
         <is>
           <t>Validación por dos personas y firma</t>
         </is>
       </c>
-      <c r="E48" s="26" t="inlineStr">
+      <c r="E48" s="33" t="inlineStr">
         <is>
           <t>Revisión ligada a roles; firma automática por etapa; informe emitido inmutable en la hoja de vida.</t>
         </is>
       </c>
-      <c r="F48" s="26" t="inlineStr">
+      <c r="F48" s="33" t="inlineStr">
         <is>
           <t>informes, permissions</t>
         </is>
       </c>
-      <c r="G48" s="26" t="inlineStr">
+      <c r="G48" s="33" t="inlineStr">
         <is>
           <t>P10 · M9.1</t>
         </is>
       </c>
-      <c r="H48" s="26" t="inlineStr">
+      <c r="H48" s="33" t="inlineStr">
         <is>
           <t>decision/roles-validacion-informe</t>
         </is>
       </c>
-      <c r="I48" s="26" t="inlineStr">
+      <c r="I48" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J48" s="26" t="inlineStr">
+      <c r="J48" s="33" t="inlineStr">
         <is>
           <t>S49</t>
         </is>
       </c>
-      <c r="K48" s="27" t="n"/>
-      <c r="L48" s="27" t="n"/>
-      <c r="M48" s="27" t="n"/>
-      <c r="N48" s="27" t="n"/>
-      <c r="O48" s="27" t="n"/>
-      <c r="P48" s="27" t="n"/>
-      <c r="Q48" s="26" t="inlineStr">
+      <c r="K48" s="34" t="n"/>
+      <c r="L48" s="34" t="n"/>
+      <c r="M48" s="34" t="n"/>
+      <c r="N48" s="34" t="n"/>
+      <c r="O48" s="34" t="n"/>
+      <c r="P48" s="34" t="n"/>
+      <c r="Q48" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R48" s="26" t="n"/>
+      <c r="R48" s="33" t="n"/>
+      <c r="U48" s="41" t="inlineStr">
+        <is>
+          <t>Un informe lo revisan dos personas antes de emitirse, se firma por etapa, y una vez emitido queda inmutable en la hoja de vida del equipo. El cliente recibe siempre un documento que alguien ha validado.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="27" customHeight="1" s="20">
-      <c r="A49" s="25" t="inlineStr">
+      <c r="A49" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B49" s="26" t="inlineStr">
+      <c r="B49" s="33" t="inlineStr">
         <is>
           <t>F1E</t>
         </is>
       </c>
-      <c r="C49" s="26" t="inlineStr">
+      <c r="C49" s="33" t="inlineStr">
         <is>
           <t>F1E-05</t>
         </is>
       </c>
-      <c r="D49" s="26" t="inlineStr">
+      <c r="D49" s="33" t="inlineStr">
         <is>
           <t>Flujo del informe en el documento maestro</t>
         </is>
       </c>
-      <c r="E49" s="26" t="inlineStr">
+      <c r="E49" s="33" t="inlineStr">
         <is>
           <t>Entregable documental (compromiso 27/08) reflejado en la spec informes.</t>
         </is>
       </c>
-      <c r="F49" s="26" t="inlineStr">
+      <c r="F49" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G49" s="26" t="inlineStr">
+      <c r="G49" s="33" t="inlineStr">
         <is>
           <t>Entregable 3</t>
         </is>
       </c>
-      <c r="H49" s="26" t="inlineStr">
+      <c r="H49" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I49" s="26" t="inlineStr">
+      <c r="I49" s="33" t="inlineStr">
         <is>
           <t>doc</t>
         </is>
       </c>
-      <c r="J49" s="26" t="inlineStr">
+      <c r="J49" s="33" t="inlineStr">
         <is>
           <t>S50</t>
         </is>
       </c>
-      <c r="K49" s="27" t="n"/>
-      <c r="L49" s="27" t="n"/>
-      <c r="M49" s="27" t="n"/>
-      <c r="N49" s="27" t="n"/>
-      <c r="O49" s="27" t="n"/>
-      <c r="P49" s="27" t="n"/>
-      <c r="Q49" s="26" t="inlineStr">
+      <c r="K49" s="34" t="n"/>
+      <c r="L49" s="34" t="n"/>
+      <c r="M49" s="34" t="n"/>
+      <c r="N49" s="34" t="n"/>
+      <c r="O49" s="34" t="n"/>
+      <c r="P49" s="34" t="n"/>
+      <c r="Q49" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R49" s="26" t="n"/>
+      <c r="R49" s="33" t="n"/>
+      <c r="U49" s="41" t="inlineStr">
+        <is>
+          <t>Nada en la aplicación. Entregable documental: el flujo del informe reflejado en el maestro y en la spec de informes.</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="27" customHeight="1" s="20">
-      <c r="A50" s="25" t="inlineStr">
+      <c r="A50" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B50" s="26" t="inlineStr">
+      <c r="B50" s="33" t="inlineStr">
         <is>
           <t>F1F</t>
         </is>
       </c>
-      <c r="C50" s="26" t="inlineStr">
+      <c r="C50" s="33" t="inlineStr">
         <is>
           <t>F1F-01</t>
         </is>
       </c>
-      <c r="D50" s="26" t="inlineStr">
+      <c r="D50" s="33" t="inlineStr">
         <is>
           <t>Migración de tickets abiertos y fecha de corte</t>
         </is>
       </c>
-      <c r="E50" s="26" t="inlineStr">
+      <c r="E50" s="33" t="inlineStr">
         <is>
           <t>Tickets abiertos de Zoho Desk al estado equivalente; regla de corte.</t>
         </is>
       </c>
-      <c r="F50" s="26" t="inlineStr">
+      <c r="F50" s="33" t="inlineStr">
         <is>
           <t>zoho-sync, tickets-core</t>
         </is>
       </c>
-      <c r="G50" s="26" t="inlineStr">
+      <c r="G50" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H50" s="26" t="inlineStr">
+      <c r="H50" s="33" t="inlineStr">
         <is>
           <t>decision/fecha-corte</t>
         </is>
       </c>
-      <c r="I50" s="26" t="inlineStr">
+      <c r="I50" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J50" s="26" t="inlineStr">
+      <c r="J50" s="33" t="inlineStr">
         <is>
           <t>S50</t>
         </is>
       </c>
-      <c r="K50" s="27" t="n"/>
-      <c r="L50" s="27" t="n"/>
-      <c r="M50" s="27" t="n"/>
-      <c r="N50" s="27" t="n"/>
-      <c r="O50" s="27" t="n"/>
-      <c r="P50" s="27" t="n"/>
-      <c r="Q50" s="26" t="inlineStr">
+      <c r="K50" s="34" t="n"/>
+      <c r="L50" s="34" t="n"/>
+      <c r="M50" s="34" t="n"/>
+      <c r="N50" s="34" t="n"/>
+      <c r="O50" s="34" t="n"/>
+      <c r="P50" s="34" t="n"/>
+      <c r="Q50" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R50" s="26" t="n"/>
+      <c r="R50" s="33" t="n"/>
+      <c r="U50" s="41" t="inlineStr">
+        <is>
+          <t>Los tickets abiertos de Zoho Desk aparecen en la aplicación en su estado equivalente, con la fecha de corte declarada: desde ese día los tickets nacen aquí. Es el momento en que el trabajo del día a día se muda.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="27" customHeight="1" s="20">
-      <c r="A51" s="25" t="inlineStr">
+      <c r="A51" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B51" s="26" t="inlineStr">
+      <c r="B51" s="33" t="inlineStr">
         <is>
           <t>F1F</t>
         </is>
       </c>
-      <c r="C51" s="26" t="inlineStr">
+      <c r="C51" s="33" t="inlineStr">
         <is>
           <t>F1F-02</t>
         </is>
       </c>
-      <c r="D51" s="26" t="inlineStr">
+      <c r="D51" s="33" t="inlineStr">
         <is>
           <t>Respaldo y continuidad</t>
         </is>
       </c>
-      <c r="E51" s="26" t="inlineStr">
+      <c r="E51" s="33" t="inlineStr">
         <is>
           <t>Exportación periódica de PostgreSQL, adjuntos e informes; formato y periodicidad (M12.8 propuesto).</t>
         </is>
       </c>
-      <c r="F51" s="26" t="inlineStr">
+      <c r="F51" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G51" s="26" t="inlineStr">
+      <c r="G51" s="33" t="inlineStr">
         <is>
           <t>Convocatoria 03/09</t>
         </is>
       </c>
-      <c r="H51" s="26" t="inlineStr">
+      <c r="H51" s="33" t="inlineStr">
         <is>
           <t>decision/p55-backup</t>
         </is>
       </c>
-      <c r="I51" s="26" t="inlineStr">
+      <c r="I51" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J51" s="26" t="inlineStr">
+      <c r="J51" s="33" t="inlineStr">
         <is>
           <t>S51</t>
         </is>
       </c>
-      <c r="K51" s="27" t="n"/>
-      <c r="L51" s="27" t="n"/>
-      <c r="M51" s="27" t="n"/>
-      <c r="N51" s="27" t="n"/>
-      <c r="O51" s="27" t="n"/>
-      <c r="P51" s="27" t="n"/>
-      <c r="Q51" s="26" t="inlineStr">
+      <c r="K51" s="34" t="n"/>
+      <c r="L51" s="34" t="n"/>
+      <c r="M51" s="34" t="n"/>
+      <c r="N51" s="34" t="n"/>
+      <c r="O51" s="34" t="n"/>
+      <c r="P51" s="34" t="n"/>
+      <c r="Q51" s="33" t="inlineStr">
         <is>
           <t>Escrita · espera gate</t>
         </is>
       </c>
-      <c r="R51" s="26" t="n"/>
+      <c r="R51" s="33" t="n"/>
+      <c r="U51" s="41" t="inlineStr">
+        <is>
+          <t>Hay copia periódica de la base, los adjuntos y los informes, con formato y periodicidad escritos. Deja de depender de que nadie borre nada.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="27" customHeight="1" s="20">
-      <c r="A52" s="25" t="inlineStr">
+      <c r="A52" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B52" s="26" t="inlineStr">
+      <c r="B52" s="33" t="inlineStr">
         <is>
           <t>F1F</t>
         </is>
       </c>
-      <c r="C52" s="26" t="inlineStr">
+      <c r="C52" s="33" t="inlineStr">
         <is>
           <t>F1F-03</t>
         </is>
       </c>
-      <c r="D52" s="26" t="inlineStr">
+      <c r="D52" s="33" t="inlineStr">
         <is>
           <t>Aceptación con servicios reales</t>
         </is>
       </c>
-      <c r="E52" s="26" t="inlineStr">
+      <c r="E52" s="33" t="inlineStr">
         <is>
           <t>Dos o tres servicios reales con Servicio Técnico; ajustes.</t>
         </is>
       </c>
-      <c r="F52" s="26" t="inlineStr">
+      <c r="F52" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G52" s="26" t="inlineStr">
+      <c r="G52" s="33" t="inlineStr">
         <is>
           <t>Recomendación Excel v9</t>
         </is>
       </c>
-      <c r="H52" s="26" t="inlineStr">
+      <c r="H52" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I52" s="26" t="inlineStr">
+      <c r="I52" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J52" s="26" t="inlineStr">
+      <c r="J52" s="33" t="inlineStr">
         <is>
           <t>S51–S52</t>
         </is>
       </c>
-      <c r="K52" s="27" t="n"/>
-      <c r="L52" s="27" t="n"/>
-      <c r="M52" s="27" t="n"/>
-      <c r="N52" s="27" t="n"/>
-      <c r="O52" s="27" t="n"/>
-      <c r="P52" s="27" t="n"/>
-      <c r="Q52" s="26" t="inlineStr">
+      <c r="K52" s="34" t="n"/>
+      <c r="L52" s="34" t="n"/>
+      <c r="M52" s="34" t="n"/>
+      <c r="N52" s="34" t="n"/>
+      <c r="O52" s="34" t="n"/>
+      <c r="P52" s="34" t="n"/>
+      <c r="Q52" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R52" s="26" t="n"/>
+      <c r="R52" s="33" t="n"/>
+      <c r="U52" s="41" t="inlineStr">
+        <is>
+          <t>Dos o tres servicios reales se hacen de principio a fin en la aplicación, con Servicio Técnico delante. Es la primera vez que la evidencia no es una prueba sino un equipo de un cliente.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="27" customHeight="1" s="20">
-      <c r="A53" s="25" t="inlineStr">
+      <c r="A53" s="32" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B53" s="26" t="inlineStr">
+      <c r="B53" s="33" t="inlineStr">
         <is>
           <t>F1F</t>
         </is>
       </c>
-      <c r="C53" s="26" t="inlineStr">
+      <c r="C53" s="33" t="inlineStr">
         <is>
           <t>F1F-04</t>
         </is>
       </c>
-      <c r="D53" s="26" t="inlineStr">
+      <c r="D53" s="33" t="inlineStr">
         <is>
           <t>Formación, Zoho a solo lectura, audit-F1</t>
         </is>
       </c>
-      <c r="E53" s="26" t="inlineStr">
+      <c r="E53" s="33" t="inlineStr">
         <is>
           <t>Formación breve; Zoho Desk a solo lectura; auditoría final; Anexo H.</t>
         </is>
       </c>
-      <c r="F53" s="26" t="inlineStr">
+      <c r="F53" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G53" s="26" t="inlineStr">
+      <c r="G53" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H53" s="26" t="inlineStr">
+      <c r="H53" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I53" s="26" t="inlineStr">
+      <c r="I53" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J53" s="26" t="inlineStr">
+      <c r="J53" s="33" t="inlineStr">
         <is>
           <t>S53</t>
         </is>
       </c>
-      <c r="K53" s="27" t="n"/>
-      <c r="L53" s="27" t="n"/>
-      <c r="M53" s="27" t="n"/>
-      <c r="N53" s="27" t="n"/>
-      <c r="O53" s="27" t="n"/>
-      <c r="P53" s="27" t="n"/>
-      <c r="Q53" s="26" t="inlineStr">
+      <c r="K53" s="34" t="n"/>
+      <c r="L53" s="34" t="n"/>
+      <c r="M53" s="34" t="n"/>
+      <c r="N53" s="34" t="n"/>
+      <c r="O53" s="34" t="n"/>
+      <c r="P53" s="34" t="n"/>
+      <c r="Q53" s="33" t="inlineStr">
         <is>
           <t>Escrita · sin gate</t>
         </is>
       </c>
-      <c r="R53" s="26" t="n"/>
+      <c r="R53" s="33" t="n"/>
+      <c r="U53" s="41" t="inlineStr">
+        <is>
+          <t>Zoho Desk pasa a SOLO LECTURA y el equipo trabaja en la aplicación. Es el punto en el que el proyecto cumple su compromiso del 31/12/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="20">
-      <c r="A54" s="25" t="inlineStr">
+      <c r="A54" s="32" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="B54" s="26" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="C54" s="26" t="inlineStr">
+      <c r="C54" s="33" t="inlineStr">
         <is>
           <t>F2-01</t>
         </is>
       </c>
-      <c r="D54" s="26" t="inlineStr">
+      <c r="D54" s="33" t="inlineStr">
         <is>
           <t>Dashboard operativo Kanban</t>
         </is>
       </c>
-      <c r="E54" s="26" t="inlineStr">
+      <c r="E54" s="33" t="inlineStr">
         <is>
           <t>WIP por etapa y riesgo de compromiso.</t>
         </is>
       </c>
-      <c r="F54" s="26" t="inlineStr">
+      <c r="F54" s="33" t="inlineStr">
         <is>
           <t>kpis</t>
         </is>
       </c>
-      <c r="G54" s="26" t="inlineStr">
+      <c r="G54" s="33" t="inlineStr">
         <is>
           <t>Ítem 13</t>
         </is>
       </c>
-      <c r="H54" s="26" t="inlineStr">
+      <c r="H54" s="33" t="inlineStr">
         <is>
           <t>Datos F1</t>
         </is>
       </c>
-      <c r="I54" s="26" t="inlineStr">
+      <c r="I54" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J54" s="26" t="inlineStr">
+      <c r="J54" s="33" t="inlineStr">
         <is>
           <t>2027 T1</t>
         </is>
       </c>
-      <c r="K54" s="27" t="n"/>
-      <c r="L54" s="27" t="n"/>
-      <c r="M54" s="27" t="n"/>
-      <c r="N54" s="27" t="n"/>
-      <c r="O54" s="27" t="n"/>
-      <c r="P54" s="27" t="n"/>
-      <c r="Q54" s="26" t="inlineStr">
+      <c r="K54" s="34" t="n"/>
+      <c r="L54" s="34" t="n"/>
+      <c r="M54" s="34" t="n"/>
+      <c r="N54" s="34" t="n"/>
+      <c r="O54" s="34" t="n"/>
+      <c r="P54" s="34" t="n"/>
+      <c r="Q54" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R54" s="26" t="n"/>
+      <c r="R54" s="33" t="n"/>
+      <c r="U54" s="41" t="inlineStr">
+        <is>
+          <t>Un tablero Kanban con el trabajo en curso por etapa y el riesgo de incumplir la fecha comprometida.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="63" customHeight="1" s="20">
-      <c r="A55" s="25" t="inlineStr">
+      <c r="A55" s="32" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="B55" s="26" t="inlineStr">
+      <c r="B55" s="33" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="C55" s="26" t="inlineStr">
+      <c r="C55" s="33" t="inlineStr">
         <is>
           <t>F2-02</t>
         </is>
       </c>
-      <c r="D55" s="26" t="inlineStr">
+      <c r="D55" s="33" t="inlineStr">
         <is>
           <t>KPIs de OTD y lead times</t>
         </is>
       </c>
-      <c r="E55" s="26" t="inlineStr">
+      <c r="E55" s="33" t="inlineStr">
         <is>
           <t>OTD, lead time total y de cotización; tres bodegajes; Anulado excluido. Bodegaje de entrada = tiempo en Remisión creada. La verificación de equipo nuevo no se mide con la duración del estado mientras se registre al terminar (M7.3). Las OVI se excluyen de los KPI de ingresos y ticket promedio.</t>
         </is>
       </c>
-      <c r="F55" s="26" t="inlineStr">
+      <c r="F55" s="33" t="inlineStr">
         <is>
           <t>kpis</t>
         </is>
       </c>
-      <c r="G55" s="26" t="inlineStr">
+      <c r="G55" s="33" t="inlineStr">
         <is>
           <t>Ítem 14 · C9</t>
         </is>
       </c>
-      <c r="H55" s="26" t="inlineStr">
+      <c r="H55" s="33" t="inlineStr">
         <is>
           <t>C2 · F1A-07 (fechas del servidor)</t>
         </is>
       </c>
-      <c r="I55" s="26" t="inlineStr">
+      <c r="I55" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J55" s="26" t="inlineStr">
+      <c r="J55" s="33" t="inlineStr">
         <is>
           <t>2027 T1</t>
         </is>
       </c>
-      <c r="K55" s="27" t="n"/>
-      <c r="L55" s="27" t="n"/>
-      <c r="M55" s="27" t="n"/>
-      <c r="N55" s="27" t="n"/>
-      <c r="O55" s="27" t="n"/>
-      <c r="P55" s="27" t="n"/>
-      <c r="Q55" s="26" t="inlineStr">
+      <c r="K55" s="34" t="n"/>
+      <c r="L55" s="34" t="n"/>
+      <c r="M55" s="34" t="n"/>
+      <c r="N55" s="34" t="n"/>
+      <c r="O55" s="34" t="n"/>
+      <c r="P55" s="34" t="n"/>
+      <c r="Q55" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R55" s="26" t="inlineStr">
+      <c r="R55" s="33" t="inlineStr">
         <is>
           <t>Añade las precisiones de medición del 10/09, la exclusión de OVI y la dependencia de IV-2.</t>
         </is>
       </c>
+      <c r="U55" s="41" t="inlineStr">
+        <is>
+          <t>Los indicadores de cumplimiento de fecha y de tiempos de ciclo, calculados y a la vista, con Anulado excluido y las OVI fuera de los KPI de ingresos.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="20">
-      <c r="A56" s="25" t="inlineStr">
+      <c r="A56" s="32" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="B56" s="26" t="inlineStr">
+      <c r="B56" s="33" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="C56" s="26" t="inlineStr">
+      <c r="C56" s="33" t="inlineStr">
         <is>
           <t>F2-03</t>
         </is>
       </c>
-      <c r="D56" s="26" t="inlineStr">
+      <c r="D56" s="33" t="inlineStr">
         <is>
           <t>Descuento de repuesto usado</t>
         </is>
       </c>
-      <c r="E56" s="26" t="inlineStr">
+      <c r="E56" s="33" t="inlineStr">
         <is>
           <t>Sobre orden aprobada.</t>
         </is>
       </c>
-      <c r="F56" s="26" t="inlineStr">
+      <c r="F56" s="33" t="inlineStr">
         <is>
           <t>inventario</t>
         </is>
       </c>
-      <c r="G56" s="26" t="inlineStr">
+      <c r="G56" s="33" t="inlineStr">
         <is>
           <t>Ítem 15</t>
         </is>
       </c>
-      <c r="H56" s="26" t="inlineStr">
+      <c r="H56" s="33" t="inlineStr">
         <is>
           <t>P44</t>
         </is>
       </c>
-      <c r="I56" s="26" t="inlineStr">
+      <c r="I56" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J56" s="26" t="inlineStr">
+      <c r="J56" s="33" t="inlineStr">
         <is>
           <t>2027 T1</t>
         </is>
       </c>
-      <c r="K56" s="27" t="n"/>
-      <c r="L56" s="27" t="n"/>
-      <c r="M56" s="27" t="n"/>
-      <c r="N56" s="27" t="n"/>
-      <c r="O56" s="27" t="n"/>
-      <c r="P56" s="27" t="n"/>
-      <c r="Q56" s="26" t="inlineStr">
+      <c r="K56" s="34" t="n"/>
+      <c r="L56" s="34" t="n"/>
+      <c r="M56" s="34" t="n"/>
+      <c r="N56" s="34" t="n"/>
+      <c r="O56" s="34" t="n"/>
+      <c r="P56" s="34" t="n"/>
+      <c r="Q56" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R56" s="26" t="n"/>
+      <c r="R56" s="33" t="n"/>
+      <c r="U56" s="41" t="inlineStr">
+        <is>
+          <t>Al aprobarse una orden, el repuesto usado se descuenta del inventario sin que nadie lo apunte aparte.</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="27" customHeight="1" s="20">
-      <c r="A57" s="25" t="inlineStr">
+      <c r="A57" s="32" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="B57" s="26" t="inlineStr">
+      <c r="B57" s="33" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="C57" s="26" t="inlineStr">
+      <c r="C57" s="33" t="inlineStr">
         <is>
           <t>F2-04</t>
         </is>
       </c>
-      <c r="D57" s="26" t="inlineStr">
+      <c r="D57" s="33" t="inlineStr">
         <is>
           <t>Comentarios predefinidos</t>
         </is>
       </c>
-      <c r="E57" s="26" t="inlineStr">
+      <c r="E57" s="33" t="inlineStr">
         <is>
           <t>A partir del análisis de ~90 tickets (tres lotes de 30).</t>
         </is>
       </c>
-      <c r="F57" s="26" t="inlineStr">
+      <c r="F57" s="33" t="inlineStr">
         <is>
           <t>informes, diagnostico-checklist</t>
         </is>
       </c>
-      <c r="G57" s="26" t="inlineStr">
+      <c r="G57" s="33" t="inlineStr">
         <is>
           <t>Acta 03/09 tema 6</t>
         </is>
       </c>
-      <c r="H57" s="26" t="inlineStr">
+      <c r="H57" s="33" t="inlineStr">
         <is>
           <t>Volumen de tickets</t>
         </is>
       </c>
-      <c r="I57" s="26" t="inlineStr">
+      <c r="I57" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J57" s="26" t="inlineStr">
+      <c r="J57" s="33" t="inlineStr">
         <is>
           <t>2027 T1</t>
         </is>
       </c>
-      <c r="K57" s="27" t="n"/>
-      <c r="L57" s="27" t="n"/>
-      <c r="M57" s="27" t="n"/>
-      <c r="N57" s="27" t="n"/>
-      <c r="O57" s="27" t="n"/>
-      <c r="P57" s="27" t="n"/>
-      <c r="Q57" s="26" t="inlineStr">
+      <c r="K57" s="34" t="n"/>
+      <c r="L57" s="34" t="n"/>
+      <c r="M57" s="34" t="n"/>
+      <c r="N57" s="34" t="n"/>
+      <c r="O57" s="34" t="n"/>
+      <c r="P57" s="34" t="n"/>
+      <c r="Q57" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R57" s="26" t="n"/>
+      <c r="R57" s="33" t="n"/>
+      <c r="U57" s="41" t="inlineStr">
+        <is>
+          <t>Comentarios predefinidos por etapa, sacados del análisis de unos noventa tickets reales.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="27" customHeight="1" s="20">
-      <c r="A58" s="25" t="inlineStr">
+      <c r="A58" s="32" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="B58" s="26" t="inlineStr">
+      <c r="B58" s="33" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="C58" s="26" t="inlineStr">
+      <c r="C58" s="33" t="inlineStr">
         <is>
           <t>F2-05</t>
         </is>
       </c>
-      <c r="D58" s="26" t="inlineStr">
+      <c r="D58" s="33" t="inlineStr">
         <is>
           <t>Liberación de mesa y solicitud automática de materiales</t>
         </is>
       </c>
-      <c r="E58" s="26" t="inlineStr">
+      <c r="E58" s="33" t="inlineStr">
         <is>
           <t>Cola de espera sin aprobación en plazo; solicitud al entrar en espera de repuesto.</t>
         </is>
       </c>
-      <c r="F58" s="26" t="inlineStr">
+      <c r="F58" s="33" t="inlineStr">
         <is>
           <t>transitions-st</t>
         </is>
       </c>
-      <c r="G58" s="26" t="inlineStr">
+      <c r="G58" s="33" t="inlineStr">
         <is>
           <t>Ítems 30, 32</t>
         </is>
       </c>
-      <c r="H58" s="26" t="inlineStr">
+      <c r="H58" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I58" s="26" t="inlineStr">
+      <c r="I58" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J58" s="26" t="inlineStr">
+      <c r="J58" s="33" t="inlineStr">
         <is>
           <t>2027 T1</t>
         </is>
       </c>
-      <c r="K58" s="27" t="n"/>
-      <c r="L58" s="27" t="n"/>
-      <c r="M58" s="27" t="n"/>
-      <c r="N58" s="27" t="n"/>
-      <c r="O58" s="27" t="n"/>
-      <c r="P58" s="27" t="n"/>
-      <c r="Q58" s="26" t="inlineStr">
+      <c r="K58" s="34" t="n"/>
+      <c r="L58" s="34" t="n"/>
+      <c r="M58" s="34" t="n"/>
+      <c r="N58" s="34" t="n"/>
+      <c r="O58" s="34" t="n"/>
+      <c r="P58" s="34" t="n"/>
+      <c r="Q58" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R58" s="26" t="n"/>
+      <c r="R58" s="33" t="n"/>
+      <c r="U58" s="41" t="inlineStr">
+        <is>
+          <t>La mesa de trabajo se libera sola cuando el cliente no aprueba en plazo, y al entrar en espera de repuesto se lanza la solicitud de material.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="20">
-      <c r="A59" s="25" t="inlineStr">
+      <c r="A59" s="32" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="B59" s="26" t="inlineStr">
+      <c r="B59" s="33" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="C59" s="26" t="inlineStr">
+      <c r="C59" s="33" t="inlineStr">
         <is>
           <t>F2-06</t>
         </is>
       </c>
-      <c r="D59" s="26" t="inlineStr">
+      <c r="D59" s="33" t="inlineStr">
         <is>
           <t>App móvil/tablet responsive</t>
         </is>
       </c>
-      <c r="E59" s="26" t="inlineStr">
+      <c r="E59" s="33" t="inlineStr">
         <is>
           <t>Checklists, fotos y firma; sin offline.</t>
         </is>
       </c>
-      <c r="F59" s="26" t="inlineStr">
+      <c r="F59" s="33" t="inlineStr">
         <is>
           <t>diagnostico-checklist</t>
         </is>
       </c>
-      <c r="G59" s="26" t="inlineStr">
+      <c r="G59" s="33" t="inlineStr">
         <is>
           <t>Ítem 18</t>
         </is>
       </c>
-      <c r="H59" s="26" t="inlineStr">
+      <c r="H59" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I59" s="26" t="inlineStr">
+      <c r="I59" s="33" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J59" s="26" t="inlineStr">
+      <c r="J59" s="33" t="inlineStr">
         <is>
           <t>2027 T1</t>
         </is>
       </c>
-      <c r="K59" s="27" t="n"/>
-      <c r="L59" s="27" t="n"/>
-      <c r="M59" s="27" t="n"/>
-      <c r="N59" s="27" t="n"/>
-      <c r="O59" s="27" t="n"/>
-      <c r="P59" s="27" t="n"/>
-      <c r="Q59" s="26" t="inlineStr">
+      <c r="K59" s="34" t="n"/>
+      <c r="L59" s="34" t="n"/>
+      <c r="M59" s="34" t="n"/>
+      <c r="N59" s="34" t="n"/>
+      <c r="O59" s="34" t="n"/>
+      <c r="P59" s="34" t="n"/>
+      <c r="Q59" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R59" s="26" t="n"/>
+      <c r="R59" s="33" t="n"/>
+      <c r="U59" s="41" t="inlineStr">
+        <is>
+          <t>La aplicación se usa desde tablet o móvil para checklists, fotos y firma, con el equipo delante.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="27" customHeight="1" s="20">
-      <c r="A60" s="25" t="inlineStr">
+      <c r="A60" s="32" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="B60" s="26" t="inlineStr">
+      <c r="B60" s="33" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="C60" s="26" t="inlineStr">
+      <c r="C60" s="33" t="inlineStr">
         <is>
           <t>F2-07</t>
         </is>
       </c>
-      <c r="D60" s="26" t="inlineStr">
+      <c r="D60" s="33" t="inlineStr">
         <is>
           <t>Migración del histórico documental y Drive</t>
         </is>
       </c>
-      <c r="E60" s="26" t="inlineStr">
+      <c r="E60" s="33" t="inlineStr">
         <is>
           <t>Herramienta independiente; convivencia con Drive.</t>
         </is>
       </c>
-      <c r="F60" s="26" t="inlineStr">
+      <c r="F60" s="33" t="inlineStr">
         <is>
           <t>hojas-vida</t>
         </is>
       </c>
-      <c r="G60" s="26" t="inlineStr">
+      <c r="G60" s="33" t="inlineStr">
         <is>
           <t>P8 · P54</t>
         </is>
       </c>
-      <c r="H60" s="26" t="inlineStr">
+      <c r="H60" s="33" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="I60" s="26" t="inlineStr">
+      <c r="I60" s="33" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J60" s="26" t="inlineStr">
+      <c r="J60" s="33" t="inlineStr">
         <is>
           <t>2027 T1</t>
         </is>
       </c>
-      <c r="K60" s="27" t="n"/>
-      <c r="L60" s="27" t="n"/>
-      <c r="M60" s="27" t="n"/>
-      <c r="N60" s="27" t="n"/>
-      <c r="O60" s="27" t="n"/>
-      <c r="P60" s="27" t="n"/>
-      <c r="Q60" s="26" t="inlineStr">
+      <c r="K60" s="34" t="n"/>
+      <c r="L60" s="34" t="n"/>
+      <c r="M60" s="34" t="n"/>
+      <c r="N60" s="34" t="n"/>
+      <c r="O60" s="34" t="n"/>
+      <c r="P60" s="34" t="n"/>
+      <c r="Q60" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R60" s="26" t="n"/>
+      <c r="R60" s="33" t="n"/>
+      <c r="U60" s="41" t="inlineStr">
+        <is>
+          <t>El histórico documental migrado, conviviendo con Drive mientras haga falta.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="27" customHeight="1" s="20">
-      <c r="A61" s="25" t="inlineStr">
+      <c r="A61" s="32" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="B61" s="26" t="inlineStr">
+      <c r="B61" s="33" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="C61" s="26" t="inlineStr">
+      <c r="C61" s="33" t="inlineStr">
         <is>
           <t>F2-08</t>
         </is>
       </c>
-      <c r="D61" s="26" t="inlineStr">
+      <c r="D61" s="33" t="inlineStr">
         <is>
           <t>Calendario de vencimientos de calibración</t>
         </is>
       </c>
-      <c r="E61" s="26" t="inlineStr">
+      <c r="E61" s="33" t="inlineStr">
         <is>
           <t>Interno, Grimm.</t>
         </is>
       </c>
-      <c r="F61" s="26" t="inlineStr">
+      <c r="F61" s="33" t="inlineStr">
         <is>
           <t>kpis</t>
         </is>
       </c>
-      <c r="G61" s="26" t="inlineStr">
+      <c r="G61" s="33" t="inlineStr">
         <is>
           <t>Ítem 37</t>
         </is>
       </c>
-      <c r="H61" s="26" t="inlineStr">
+      <c r="H61" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I61" s="26" t="inlineStr">
+      <c r="I61" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J61" s="26" t="inlineStr">
+      <c r="J61" s="33" t="inlineStr">
         <is>
           <t>2027 T1</t>
         </is>
       </c>
-      <c r="K61" s="27" t="n"/>
-      <c r="L61" s="27" t="n"/>
-      <c r="M61" s="27" t="n"/>
-      <c r="N61" s="27" t="n"/>
-      <c r="O61" s="27" t="n"/>
-      <c r="P61" s="27" t="n"/>
-      <c r="Q61" s="26" t="inlineStr">
+      <c r="K61" s="34" t="n"/>
+      <c r="L61" s="34" t="n"/>
+      <c r="M61" s="34" t="n"/>
+      <c r="N61" s="34" t="n"/>
+      <c r="O61" s="34" t="n"/>
+      <c r="P61" s="34" t="n"/>
+      <c r="Q61" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R61" s="26" t="n"/>
+      <c r="R61" s="33" t="n"/>
+      <c r="U61" s="41" t="inlineStr">
+        <is>
+          <t>Calendario interno de vencimientos de calibración.</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="27" customHeight="1" s="20">
-      <c r="A62" s="25" t="inlineStr">
+      <c r="A62" s="32" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="B62" s="26" t="inlineStr">
+      <c r="B62" s="33" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="C62" s="26" t="inlineStr">
+      <c r="C62" s="33" t="inlineStr">
         <is>
           <t>F3-01</t>
         </is>
       </c>
-      <c r="D62" s="26" t="inlineStr">
+      <c r="D62" s="33" t="inlineStr">
         <is>
           <t>C8 · Estados → etapas visibles del portal</t>
         </is>
       </c>
-      <c r="E62" s="26" t="inlineStr">
+      <c r="E62" s="33" t="inlineStr">
         <is>
           <t>Traducción de los 21 estados.</t>
         </is>
       </c>
-      <c r="F62" s="26" t="inlineStr">
+      <c r="F62" s="33" t="inlineStr">
         <is>
           <t>portal</t>
         </is>
       </c>
-      <c r="G62" s="26" t="inlineStr">
+      <c r="G62" s="33" t="inlineStr">
         <is>
           <t>C8 · M8.2</t>
         </is>
       </c>
-      <c r="H62" s="26" t="inlineStr">
+      <c r="H62" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I62" s="26" t="inlineStr">
+      <c r="I62" s="33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J62" s="26" t="inlineStr">
+      <c r="J62" s="33" t="inlineStr">
         <is>
           <t>2027 T2</t>
         </is>
       </c>
-      <c r="K62" s="27" t="n"/>
-      <c r="L62" s="27" t="n"/>
-      <c r="M62" s="27" t="n"/>
-      <c r="N62" s="27" t="n"/>
-      <c r="O62" s="27" t="n"/>
-      <c r="P62" s="27" t="n"/>
-      <c r="Q62" s="26" t="inlineStr">
+      <c r="K62" s="34" t="n"/>
+      <c r="L62" s="34" t="n"/>
+      <c r="M62" s="34" t="n"/>
+      <c r="N62" s="34" t="n"/>
+      <c r="O62" s="34" t="n"/>
+      <c r="P62" s="34" t="n"/>
+      <c r="Q62" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R62" s="26" t="n"/>
+      <c r="R62" s="33" t="n"/>
+      <c r="U62" s="41" t="inlineStr">
+        <is>
+          <t>El cliente ve etapas en lenguaje llano —recibido, diagnosticando, esperando tu aprobación—, no los 21 estados internos.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="39" customHeight="1" s="20">
-      <c r="A63" s="25" t="inlineStr">
+      <c r="A63" s="32" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="B63" s="26" t="inlineStr">
+      <c r="B63" s="33" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="C63" s="26" t="inlineStr">
+      <c r="C63" s="33" t="inlineStr">
         <is>
           <t>F3-02</t>
         </is>
       </c>
-      <c r="D63" s="26" t="inlineStr">
+      <c r="D63" s="33" t="inlineStr">
         <is>
           <t>Área de cliente nivel básico</t>
         </is>
       </c>
-      <c r="E63" s="26" t="inlineStr">
+      <c r="E63" s="33" t="inlineStr">
         <is>
           <t>Hoja de vida reducida, seguimiento, aprobación de cotizaciones en un clic (piloto con contratos).</t>
         </is>
       </c>
-      <c r="F63" s="26" t="inlineStr">
+      <c r="F63" s="33" t="inlineStr">
         <is>
           <t>portal</t>
         </is>
       </c>
-      <c r="G63" s="26" t="inlineStr">
+      <c r="G63" s="33" t="inlineStr">
         <is>
           <t>Ítems 26, 29 · M8.2, M8.3, M8.6</t>
         </is>
       </c>
-      <c r="H63" s="26" t="inlineStr">
+      <c r="H63" s="33" t="inlineStr">
         <is>
           <t>Seguridad previa</t>
         </is>
       </c>
-      <c r="I63" s="26" t="inlineStr">
+      <c r="I63" s="33" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J63" s="26" t="inlineStr">
+      <c r="J63" s="33" t="inlineStr">
         <is>
           <t>2027 T2</t>
         </is>
       </c>
-      <c r="K63" s="27" t="n"/>
-      <c r="L63" s="27" t="n"/>
-      <c r="M63" s="27" t="n"/>
-      <c r="N63" s="27" t="n"/>
-      <c r="O63" s="27" t="n"/>
-      <c r="P63" s="27" t="n"/>
-      <c r="Q63" s="26" t="inlineStr">
+      <c r="K63" s="34" t="n"/>
+      <c r="L63" s="34" t="n"/>
+      <c r="M63" s="34" t="n"/>
+      <c r="N63" s="34" t="n"/>
+      <c r="O63" s="34" t="n"/>
+      <c r="P63" s="34" t="n"/>
+      <c r="Q63" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R63" s="26" t="n"/>
+      <c r="R63" s="33" t="n"/>
+      <c r="U63" s="41" t="inlineStr">
+        <is>
+          <t>El cliente entra a su área, consulta la hoja de vida reducida de sus equipos, sigue el estado del servicio y aprueba cotizaciones en un clic.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="39" customHeight="1" s="20">
-      <c r="A64" s="25" t="inlineStr">
+      <c r="A64" s="32" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="B64" s="26" t="inlineStr">
+      <c r="B64" s="33" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="C64" s="26" t="inlineStr">
+      <c r="C64" s="33" t="inlineStr">
         <is>
           <t>F3-03</t>
         </is>
       </c>
-      <c r="D64" s="26" t="inlineStr">
+      <c r="D64" s="33" t="inlineStr">
         <is>
           <t>Identidad registrada y seguridad</t>
         </is>
       </c>
-      <c r="E64" s="26" t="inlineStr">
+      <c r="E64" s="33" t="inlineStr">
         <is>
           <t>OAuth2/OIDC; ciclo de vida de usuarios del cliente; MFA; certificados no enumerables; firmware; filtro KBI/KBE; datos personales; incidentes; sesiones; revisión previa.</t>
         </is>
       </c>
-      <c r="F64" s="26" t="inlineStr">
+      <c r="F64" s="33" t="inlineStr">
         <is>
           <t>portal, permissions</t>
         </is>
       </c>
-      <c r="G64" s="26" t="inlineStr">
+      <c r="G64" s="33" t="inlineStr">
         <is>
           <t>Ítem 52 · convocatoria 03/09</t>
         </is>
       </c>
-      <c r="H64" s="26" t="inlineStr">
+      <c r="H64" s="33" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="I64" s="26" t="inlineStr">
+      <c r="I64" s="33" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J64" s="26" t="inlineStr">
+      <c r="J64" s="33" t="inlineStr">
         <is>
           <t>2027 T2</t>
         </is>
       </c>
-      <c r="K64" s="27" t="n"/>
-      <c r="L64" s="27" t="n"/>
-      <c r="M64" s="27" t="n"/>
-      <c r="N64" s="27" t="n"/>
-      <c r="O64" s="27" t="n"/>
-      <c r="P64" s="27" t="n"/>
-      <c r="Q64" s="26" t="inlineStr">
+      <c r="K64" s="34" t="n"/>
+      <c r="L64" s="34" t="n"/>
+      <c r="M64" s="34" t="n"/>
+      <c r="N64" s="34" t="n"/>
+      <c r="O64" s="34" t="n"/>
+      <c r="P64" s="34" t="n"/>
+      <c r="Q64" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R64" s="26" t="n"/>
+      <c r="R64" s="33" t="n"/>
+      <c r="U64" s="41" t="inlineStr">
+        <is>
+          <t>Identidad registrada con doble factor, certificados verificables sin poder enumerarlos, y los controles de seguridad que la puesta en producción del portal exige.</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="20">
-      <c r="A65" s="25" t="inlineStr">
+      <c r="A65" s="32" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="B65" s="26" t="inlineStr">
+      <c r="B65" s="33" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="C65" s="26" t="inlineStr">
+      <c r="C65" s="33" t="inlineStr">
         <is>
           <t>F4-01</t>
         </is>
       </c>
-      <c r="D65" s="26" t="inlineStr">
+      <c r="D65" s="33" t="inlineStr">
         <is>
           <t>Inventario transaccional</t>
         </is>
       </c>
-      <c r="E65" s="26" t="inlineStr">
+      <c r="E65" s="33" t="inlineStr">
         <is>
           <t>Reserva soft/hard, punto de pedido, alertas.</t>
         </is>
       </c>
-      <c r="F65" s="26" t="inlineStr">
+      <c r="F65" s="33" t="inlineStr">
         <is>
           <t>inventario</t>
         </is>
       </c>
-      <c r="G65" s="26" t="inlineStr">
+      <c r="G65" s="33" t="inlineStr">
         <is>
           <t>Ítems 31, 34</t>
         </is>
       </c>
-      <c r="H65" s="26" t="inlineStr">
+      <c r="H65" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I65" s="26" t="inlineStr">
+      <c r="I65" s="33" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J65" s="26" t="inlineStr">
+      <c r="J65" s="33" t="inlineStr">
         <is>
           <t>2027 S2</t>
         </is>
       </c>
-      <c r="K65" s="27" t="n"/>
-      <c r="L65" s="27" t="n"/>
-      <c r="M65" s="27" t="n"/>
-      <c r="N65" s="27" t="n"/>
-      <c r="O65" s="27" t="n"/>
-      <c r="P65" s="27" t="n"/>
-      <c r="Q65" s="26" t="inlineStr">
+      <c r="K65" s="34" t="n"/>
+      <c r="L65" s="34" t="n"/>
+      <c r="M65" s="34" t="n"/>
+      <c r="N65" s="34" t="n"/>
+      <c r="O65" s="34" t="n"/>
+      <c r="P65" s="34" t="n"/>
+      <c r="Q65" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R65" s="26" t="n"/>
+      <c r="R65" s="33" t="n"/>
+      <c r="U65" s="41" t="inlineStr">
+        <is>
+          <t>Inventario con reserva firme y blanda, punto de pedido y alertas.</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="27" customHeight="1" s="20">
-      <c r="A66" s="25" t="inlineStr">
+      <c r="A66" s="32" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="B66" s="26" t="inlineStr">
+      <c r="B66" s="33" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="C66" s="26" t="inlineStr">
+      <c r="C66" s="33" t="inlineStr">
         <is>
           <t>F4-02</t>
         </is>
       </c>
-      <c r="D66" s="26" t="inlineStr">
+      <c r="D66" s="33" t="inlineStr">
         <is>
           <t>Parámetro de carga y calendario de citas</t>
         </is>
       </c>
-      <c r="E66" s="26" t="inlineStr">
+      <c r="E66" s="33" t="inlineStr">
         <is>
           <t>Carga del ST; slots del banco de calibración.</t>
         </is>
       </c>
-      <c r="F66" s="26" t="inlineStr">
+      <c r="F66" s="33" t="inlineStr">
         <is>
           <t>capacidad</t>
         </is>
       </c>
-      <c r="G66" s="26" t="inlineStr">
+      <c r="G66" s="33" t="inlineStr">
         <is>
           <t>Ítems 35, 36</t>
         </is>
       </c>
-      <c r="H66" s="26" t="inlineStr">
+      <c r="H66" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I66" s="26" t="inlineStr">
+      <c r="I66" s="33" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J66" s="26" t="inlineStr">
+      <c r="J66" s="33" t="inlineStr">
         <is>
           <t>2027 S2</t>
         </is>
       </c>
-      <c r="K66" s="27" t="n"/>
-      <c r="L66" s="27" t="n"/>
-      <c r="M66" s="27" t="n"/>
-      <c r="N66" s="27" t="n"/>
-      <c r="O66" s="27" t="n"/>
-      <c r="P66" s="27" t="n"/>
-      <c r="Q66" s="26" t="inlineStr">
+      <c r="K66" s="34" t="n"/>
+      <c r="L66" s="34" t="n"/>
+      <c r="M66" s="34" t="n"/>
+      <c r="N66" s="34" t="n"/>
+      <c r="O66" s="34" t="n"/>
+      <c r="P66" s="34" t="n"/>
+      <c r="Q66" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R66" s="26" t="n"/>
+      <c r="R66" s="33" t="n"/>
+      <c r="U66" s="41" t="inlineStr">
+        <is>
+          <t>Agenda de citas con la carga real del servicio técnico y los slots del banco de calibración.</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="20">
-      <c r="A67" s="25" t="inlineStr">
+      <c r="A67" s="32" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="B67" s="26" t="inlineStr">
+      <c r="B67" s="33" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="C67" s="26" t="inlineStr">
+      <c r="C67" s="33" t="inlineStr">
         <is>
           <t>F4-03</t>
         </is>
       </c>
-      <c r="D67" s="26" t="inlineStr">
+      <c r="D67" s="33" t="inlineStr">
         <is>
           <t>Dashboards por rol y cuellos de botella</t>
         </is>
       </c>
-      <c r="E67" s="26" t="inlineStr">
+      <c r="E67" s="33" t="inlineStr">
         <is>
           <t>Dirección, comercial, planificador, técnico; análisis de esperas.</t>
         </is>
       </c>
-      <c r="F67" s="26" t="inlineStr">
+      <c r="F67" s="33" t="inlineStr">
         <is>
           <t>kpis</t>
         </is>
       </c>
-      <c r="G67" s="26" t="inlineStr">
+      <c r="G67" s="33" t="inlineStr">
         <is>
           <t>Ítems 41, 43</t>
         </is>
       </c>
-      <c r="H67" s="26" t="inlineStr">
+      <c r="H67" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I67" s="26" t="inlineStr">
+      <c r="I67" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J67" s="26" t="inlineStr">
+      <c r="J67" s="33" t="inlineStr">
         <is>
           <t>2027 S2</t>
         </is>
       </c>
-      <c r="K67" s="27" t="n"/>
-      <c r="L67" s="27" t="n"/>
-      <c r="M67" s="27" t="n"/>
-      <c r="N67" s="27" t="n"/>
-      <c r="O67" s="27" t="n"/>
-      <c r="P67" s="27" t="n"/>
-      <c r="Q67" s="26" t="inlineStr">
+      <c r="K67" s="34" t="n"/>
+      <c r="L67" s="34" t="n"/>
+      <c r="M67" s="34" t="n"/>
+      <c r="N67" s="34" t="n"/>
+      <c r="O67" s="34" t="n"/>
+      <c r="P67" s="34" t="n"/>
+      <c r="Q67" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R67" s="26" t="n"/>
+      <c r="R67" s="33" t="n"/>
+      <c r="U67" s="41" t="inlineStr">
+        <is>
+          <t>Dashboards por rol y análisis de dónde se atasca el trabajo.</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="27" customHeight="1" s="20">
-      <c r="A68" s="25" t="inlineStr">
+      <c r="A68" s="32" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="B68" s="26" t="inlineStr">
+      <c r="B68" s="33" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="C68" s="26" t="inlineStr">
+      <c r="C68" s="33" t="inlineStr">
         <is>
           <t>F4-04</t>
         </is>
       </c>
-      <c r="D68" s="26" t="inlineStr">
+      <c r="D68" s="33" t="inlineStr">
         <is>
           <t>Capa RAG / KB y copiloto</t>
         </is>
       </c>
-      <c r="E68" s="26" t="inlineStr">
+      <c r="E68" s="33" t="inlineStr">
         <is>
           <t>pgvector o «LLM wiki»; KBI/KBE; copiloto interno; KB Externa publicada; firmware.</t>
         </is>
       </c>
-      <c r="F68" s="26" t="inlineStr">
+      <c r="F68" s="33" t="inlineStr">
         <is>
           <t>conocimiento</t>
         </is>
       </c>
-      <c r="G68" s="26" t="inlineStr">
+      <c r="G68" s="33" t="inlineStr">
         <is>
           <t>Ítems 53–56 · P27</t>
         </is>
       </c>
-      <c r="H68" s="26" t="inlineStr">
+      <c r="H68" s="33" t="inlineStr">
         <is>
           <t>Vía elegida</t>
         </is>
       </c>
-      <c r="I68" s="26" t="inlineStr">
+      <c r="I68" s="33" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J68" s="26" t="inlineStr">
+      <c r="J68" s="33" t="inlineStr">
         <is>
           <t>2027 S2</t>
         </is>
       </c>
-      <c r="K68" s="27" t="n"/>
-      <c r="L68" s="27" t="n"/>
-      <c r="M68" s="27" t="n"/>
-      <c r="N68" s="27" t="n"/>
-      <c r="O68" s="27" t="n"/>
-      <c r="P68" s="27" t="n"/>
-      <c r="Q68" s="26" t="inlineStr">
+      <c r="K68" s="34" t="n"/>
+      <c r="L68" s="34" t="n"/>
+      <c r="M68" s="34" t="n"/>
+      <c r="N68" s="34" t="n"/>
+      <c r="O68" s="34" t="n"/>
+      <c r="P68" s="34" t="n"/>
+      <c r="Q68" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R68" s="26" t="n"/>
+      <c r="R68" s="33" t="n"/>
+      <c r="U68" s="41" t="inlineStr">
+        <is>
+          <t>Base de conocimiento interna y externa, con copiloto para el técnico y contenido publicado al cliente.</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="27" customHeight="1" s="20">
-      <c r="A69" s="25" t="inlineStr">
+      <c r="A69" s="32" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="B69" s="26" t="inlineStr">
+      <c r="B69" s="33" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="C69" s="26" t="inlineStr">
+      <c r="C69" s="33" t="inlineStr">
         <is>
           <t>F4-05</t>
         </is>
       </c>
-      <c r="D69" s="26" t="inlineStr">
+      <c r="D69" s="33" t="inlineStr">
         <is>
           <t>Agendamiento, offline, QR/NFC</t>
         </is>
       </c>
-      <c r="E69" s="26" t="inlineStr">
+      <c r="E69" s="33" t="inlineStr">
         <is>
           <t>Citas (tras el 35); offline con conflictos; QR/NFC en recepción.</t>
         </is>
       </c>
-      <c r="F69" s="26" t="inlineStr">
+      <c r="F69" s="33" t="inlineStr">
         <is>
           <t>portal, diagnostico-checklist</t>
         </is>
       </c>
-      <c r="G69" s="26" t="inlineStr">
+      <c r="G69" s="33" t="inlineStr">
         <is>
           <t>Ítems 27, 28, 50, 57</t>
         </is>
       </c>
-      <c r="H69" s="26" t="inlineStr">
+      <c r="H69" s="33" t="inlineStr">
         <is>
           <t>Parámetro de carga</t>
         </is>
       </c>
-      <c r="I69" s="26" t="inlineStr">
+      <c r="I69" s="33" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J69" s="26" t="inlineStr">
+      <c r="J69" s="33" t="inlineStr">
         <is>
           <t>2027 S2</t>
         </is>
       </c>
-      <c r="K69" s="27" t="n"/>
-      <c r="L69" s="27" t="n"/>
-      <c r="M69" s="27" t="n"/>
-      <c r="N69" s="27" t="n"/>
-      <c r="O69" s="27" t="n"/>
-      <c r="P69" s="27" t="n"/>
-      <c r="Q69" s="26" t="inlineStr">
+      <c r="K69" s="34" t="n"/>
+      <c r="L69" s="34" t="n"/>
+      <c r="M69" s="34" t="n"/>
+      <c r="N69" s="34" t="n"/>
+      <c r="O69" s="34" t="n"/>
+      <c r="P69" s="34" t="n"/>
+      <c r="Q69" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R69" s="26" t="n"/>
+      <c r="R69" s="33" t="n"/>
+      <c r="U69" s="41" t="inlineStr">
+        <is>
+          <t>El cliente agenda su cita, el técnico trabaja sin conexión y la recepción se hace leyendo un QR o NFC.</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="27" customHeight="1" s="20">
-      <c r="A70" s="25" t="inlineStr">
+      <c r="A70" s="32" t="inlineStr">
         <is>
           <t>F5</t>
         </is>
       </c>
-      <c r="B70" s="26" t="inlineStr">
+      <c r="B70" s="33" t="inlineStr">
         <is>
           <t>F5</t>
         </is>
       </c>
-      <c r="C70" s="26" t="inlineStr">
+      <c r="C70" s="33" t="inlineStr">
         <is>
           <t>F5-01</t>
         </is>
       </c>
-      <c r="D70" s="26" t="inlineStr">
+      <c r="D70" s="33" t="inlineStr">
         <is>
           <t>CTP y predicción</t>
         </is>
       </c>
-      <c r="E70" s="26" t="inlineStr">
+      <c r="E70" s="33" t="inlineStr">
         <is>
           <t>Simulador de fecha con capacidad finita; predicción de carga y compras.</t>
         </is>
       </c>
-      <c r="F70" s="26" t="inlineStr">
+      <c r="F70" s="33" t="inlineStr">
         <is>
           <t>capacidad, kpis</t>
         </is>
       </c>
-      <c r="G70" s="26" t="inlineStr">
+      <c r="G70" s="33" t="inlineStr">
         <is>
           <t>Ítems 61–64</t>
         </is>
       </c>
-      <c r="H70" s="26" t="inlineStr">
+      <c r="H70" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I70" s="26" t="inlineStr">
+      <c r="I70" s="33" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J70" s="26" t="inlineStr">
+      <c r="J70" s="33" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="K70" s="27" t="n"/>
-      <c r="L70" s="27" t="n"/>
-      <c r="M70" s="27" t="n"/>
-      <c r="N70" s="27" t="n"/>
-      <c r="O70" s="27" t="n"/>
-      <c r="P70" s="27" t="n"/>
-      <c r="Q70" s="26" t="inlineStr">
+      <c r="K70" s="34" t="n"/>
+      <c r="L70" s="34" t="n"/>
+      <c r="M70" s="34" t="n"/>
+      <c r="N70" s="34" t="n"/>
+      <c r="O70" s="34" t="n"/>
+      <c r="P70" s="34" t="n"/>
+      <c r="Q70" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R70" s="26" t="n"/>
+      <c r="R70" s="33" t="n"/>
+      <c r="U70" s="41" t="inlineStr">
+        <is>
+          <t>Un simulador que promete fecha de entrega con capacidad finita, en vez de estimarla a ojo.</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="27" customHeight="1" s="20">
-      <c r="A71" s="25" t="inlineStr">
+      <c r="A71" s="32" t="inlineStr">
         <is>
           <t>F5</t>
         </is>
       </c>
-      <c r="B71" s="26" t="inlineStr">
+      <c r="B71" s="33" t="inlineStr">
         <is>
           <t>F5</t>
         </is>
       </c>
-      <c r="C71" s="26" t="inlineStr">
+      <c r="C71" s="33" t="inlineStr">
         <is>
           <t>F5-02</t>
         </is>
       </c>
-      <c r="D71" s="26" t="inlineStr">
+      <c r="D71" s="33" t="inlineStr">
         <is>
           <t>Agente conversacional, IoT, premium</t>
         </is>
       </c>
-      <c r="E71" s="26" t="inlineStr">
+      <c r="E71" s="33" t="inlineStr">
         <is>
           <t>Agente sobre KB Externa; telemetría; servicio premium; sustitución total de Zoho Desk.</t>
         </is>
       </c>
-      <c r="F71" s="26" t="inlineStr">
+      <c r="F71" s="33" t="inlineStr">
         <is>
           <t>portal, conocimiento</t>
         </is>
       </c>
-      <c r="G71" s="26" t="inlineStr">
+      <c r="G71" s="33" t="inlineStr">
         <is>
           <t>Ítems 66, 70, 71, 76</t>
         </is>
       </c>
-      <c r="H71" s="26" t="inlineStr">
+      <c r="H71" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I71" s="26" t="inlineStr">
+      <c r="I71" s="33" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J71" s="26" t="inlineStr">
+      <c r="J71" s="33" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="K71" s="27" t="n"/>
-      <c r="L71" s="27" t="n"/>
-      <c r="M71" s="27" t="n"/>
-      <c r="N71" s="27" t="n"/>
-      <c r="O71" s="27" t="n"/>
-      <c r="P71" s="27" t="n"/>
-      <c r="Q71" s="26" t="inlineStr">
+      <c r="K71" s="34" t="n"/>
+      <c r="L71" s="34" t="n"/>
+      <c r="M71" s="34" t="n"/>
+      <c r="N71" s="34" t="n"/>
+      <c r="O71" s="34" t="n"/>
+      <c r="P71" s="34" t="n"/>
+      <c r="Q71" s="33" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="R71" s="26" t="n"/>
+      <c r="R71" s="33" t="n"/>
+      <c r="U71" s="41" t="inlineStr">
+        <is>
+          <t>Agente conversacional sobre la base de conocimiento, telemetría de equipos y servicio premium. Zoho Desk sustituido del todo.</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="20"/>
     <row r="73" ht="15" customHeight="1" s="20">
@@ -6530,1132 +6889,1132 @@
       </c>
     </row>
     <row r="2" ht="75" customHeight="1" s="20">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="33" t="inlineStr">
         <is>
           <t>decision/p21-ingreso-sin-ov</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="33" t="inlineStr">
         <is>
           <t>OV obligatoria desde el inicio o estado provisional</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="C2" s="33" t="inlineStr">
         <is>
           <t>F1B-03</t>
         </is>
       </c>
-      <c r="D2" s="26" t="inlineStr">
+      <c r="D2" s="33" t="inlineStr">
         <is>
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="E2" s="27" t="inlineStr">
+      <c r="E2" s="34" t="inlineStr">
         <is>
           <t>Decidida</t>
         </is>
       </c>
-      <c r="F2" s="27" t="inlineStr">
+      <c r="F2" s="34" t="inlineStr">
         <is>
           <t>Se deja como está: OV opcional en «Nuevo ticket», obligatoria en Habilitar Servicio («obligatoria para trabajar, no para recibir»). Remisión creada es la espera de Comercial (alarma 72 h, en F1B-08); Habilitar Servicio exige remisión vigente; garantía con OVI a nombre del cliente.</t>
         </is>
       </c>
-      <c r="G2" s="27" t="inlineStr">
+      <c r="G2" s="34" t="inlineStr">
         <is>
           <t>Alfonso (Gerencia)</t>
         </is>
       </c>
-      <c r="H2" s="27" t="inlineStr">
+      <c r="H2" s="34" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="I2" s="27" t="inlineStr">
+      <c r="I2" s="34" t="inlineStr">
         <is>
           <t>Decisiones 10/09 §7 · R08.2 M1.2 · cierra P21</t>
         </is>
       </c>
     </row>
     <row r="3" ht="27" customHeight="1" s="20">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>decision/p8-p54-drive</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>Botón de enlace a Drive como fase 0; convivencia con Drive</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="33" t="inlineStr">
         <is>
           <t>F1B-02</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="33" t="inlineStr">
         <is>
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="E3" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F3" s="27" t="n"/>
-      <c r="G3" s="27" t="n"/>
-      <c r="H3" s="27" t="n"/>
-      <c r="I3" s="27" t="n"/>
+      <c r="F3" s="34" t="n"/>
+      <c r="G3" s="34" t="n"/>
+      <c r="H3" s="34" t="n"/>
+      <c r="I3" s="34" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="20">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>decision/p45-macro-fases</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>Juego de macro-fases común a todas las marcas</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t>F1D-03</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>11/09/2026 (Johny)</t>
         </is>
       </c>
-      <c r="E4" s="27" t="inlineStr">
+      <c r="E4" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="27" t="n"/>
-      <c r="H4" s="27" t="n"/>
-      <c r="I4" s="27" t="n"/>
+      <c r="F4" s="34" t="n"/>
+      <c r="G4" s="34" t="n"/>
+      <c r="H4" s="34" t="n"/>
+      <c r="I4" s="34" t="n"/>
     </row>
     <row r="5" ht="27" customHeight="1" s="20">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>decision/flujos-comercial-posible-cliente</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Alcance de M1.11 y M1.12 en Desk 2.0</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>F1B-06</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F5" s="27" t="n"/>
-      <c r="G5" s="27" t="n"/>
-      <c r="H5" s="27" t="n"/>
-      <c r="I5" s="27" t="n"/>
+      <c r="F5" s="34" t="n"/>
+      <c r="G5" s="34" t="n"/>
+      <c r="H5" s="34" t="n"/>
+      <c r="I5" s="34" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="20">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>decision/top5-prioridad</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Si los Top 5 entran en la prioridad automática</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>F1B-07</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="27" t="n"/>
-      <c r="H6" s="27" t="n"/>
-      <c r="I6" s="27" t="n"/>
+      <c r="F6" s="34" t="n"/>
+      <c r="G6" s="34" t="n"/>
+      <c r="H6" s="34" t="n"/>
+      <c r="I6" s="34" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="20">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>decision/p14-remisiones-entrada</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Quién escribe remisiones_entrada</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>F1E-01</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="20">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>decision/c2-anulado</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Estado Anulado; tratamiento del histórico</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>F1C-01 (protege F1E-03)</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>11/09 o 18/09/2026</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="27" t="n"/>
-      <c r="H8" s="27" t="n"/>
-      <c r="I8" s="27" t="n"/>
+      <c r="F8" s="34" t="n"/>
+      <c r="G8" s="34" t="n"/>
+      <c r="H8" s="34" t="n"/>
+      <c r="I8" s="34" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="20">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>decision/c4-dos-ramas</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Dos ramas; si Facturado es estado</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>F1C-02</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>18/09/2026</t>
         </is>
       </c>
-      <c r="E9" s="27" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F9" s="27" t="n"/>
-      <c r="G9" s="27" t="n"/>
-      <c r="H9" s="27" t="n"/>
-      <c r="I9" s="27" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="20">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>decision/c3-salida-esperas</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>Destino y caducidad de las cuatro esperas</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>F1C-03</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>18/09/2026</t>
         </is>
       </c>
-      <c r="E10" s="27" t="inlineStr">
+      <c r="E10" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F10" s="27" t="n"/>
-      <c r="G10" s="27" t="n"/>
-      <c r="H10" s="27" t="n"/>
-      <c r="I10" s="27" t="n"/>
+      <c r="F10" s="34" t="n"/>
+      <c r="G10" s="34" t="n"/>
+      <c r="H10" s="34" t="n"/>
+      <c r="I10" s="34" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="20">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>decision/c5-tipo-evento</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Desambiguar «Creación de informe»</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>F1C-04</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>18/09/2026</t>
         </is>
       </c>
-      <c r="E11" s="27" t="inlineStr">
+      <c r="E11" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="27" t="n"/>
-      <c r="H11" s="27" t="n"/>
-      <c r="I11" s="27" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="20">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>decision/c10-permisos-cargo</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>Matriz cargo × transición</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>F1C-05</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>25/09/2026</t>
         </is>
       </c>
-      <c r="E12" s="27" t="inlineStr">
+      <c r="E12" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="27" t="n"/>
-      <c r="H12" s="27" t="n"/>
-      <c r="I12" s="27" t="n"/>
+      <c r="F12" s="34" t="n"/>
+      <c r="G12" s="34" t="n"/>
+      <c r="H12" s="34" t="n"/>
+      <c r="I12" s="34" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="20">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>decision/c7-reloj-sla</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>Estados que paran el reloj</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>F1C-06</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>25/09/2026</t>
         </is>
       </c>
-      <c r="E13" s="27" t="inlineStr">
+      <c r="E13" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F13" s="27" t="n"/>
-      <c r="G13" s="27" t="n"/>
-      <c r="H13" s="27" t="n"/>
-      <c r="I13" s="27" t="n"/>
+      <c r="F13" s="34" t="n"/>
+      <c r="G13" s="34" t="n"/>
+      <c r="H13" s="34" t="n"/>
+      <c r="I13" s="34" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="20">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>decision/c6-qa-liberacion</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>Etapa de QA y firmas</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>F1C-07</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>Octubre 2026</t>
         </is>
       </c>
-      <c r="E14" s="27" t="inlineStr">
+      <c r="E14" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="27" t="n"/>
-      <c r="I14" s="27" t="n"/>
+      <c r="F14" s="34" t="n"/>
+      <c r="G14" s="34" t="n"/>
+      <c r="H14" s="34" t="n"/>
+      <c r="I14" s="34" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="20">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>decision/p15-p59-rutas</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>Rutas abreviadas</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>F1C-08</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>Octubre 2026</t>
         </is>
       </c>
-      <c r="E15" s="27" t="inlineStr">
+      <c r="E15" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="27" t="n"/>
-      <c r="H15" s="27" t="n"/>
-      <c r="I15" s="27" t="n"/>
+      <c r="F15" s="34" t="n"/>
+      <c r="G15" s="34" t="n"/>
+      <c r="H15" s="34" t="n"/>
+      <c r="I15" s="34" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="20">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>decision/falla-nueva-bloqueante</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>Si el formulario de falla nueva bloquea</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>F1D-07</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>Gustavo, sin fecha</t>
         </is>
       </c>
-      <c r="E16" s="27" t="inlineStr">
+      <c r="E16" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="27" t="n"/>
-      <c r="H16" s="27" t="n"/>
-      <c r="I16" s="27" t="n"/>
+      <c r="F16" s="34" t="n"/>
+      <c r="G16" s="34" t="n"/>
+      <c r="H16" s="34" t="n"/>
+      <c r="I16" s="34" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="20">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>decision/roles-validacion-informe</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>Las dos personas que validan el informe</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>F1E-04</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>Octubre 2026</t>
         </is>
       </c>
-      <c r="E17" s="27" t="inlineStr">
+      <c r="E17" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="27" t="n"/>
-      <c r="H17" s="27" t="n"/>
-      <c r="I17" s="27" t="n"/>
+      <c r="F17" s="34" t="n"/>
+      <c r="G17" s="34" t="n"/>
+      <c r="H17" s="34" t="n"/>
+      <c r="I17" s="34" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="20">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>decision/p44-escritura-zoho</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>Política de escritura contra Zoho</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>F1B-08</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>Octubre 2026</t>
         </is>
       </c>
-      <c r="E18" s="27" t="inlineStr">
+      <c r="E18" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="27" t="n"/>
-      <c r="H18" s="27" t="n"/>
-      <c r="I18" s="27" t="n"/>
+      <c r="F18" s="34" t="n"/>
+      <c r="G18" s="34" t="n"/>
+      <c r="H18" s="34" t="n"/>
+      <c r="I18" s="34" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="20">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>decision/p55-backup</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>Responsable, alcance y periodicidad del respaldo</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>F1F-02</t>
         </is>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>Antes de noviembre</t>
         </is>
       </c>
-      <c r="E19" s="27" t="inlineStr">
+      <c r="E19" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="27" t="n"/>
-      <c r="H19" s="27" t="n"/>
-      <c r="I19" s="27" t="n"/>
+      <c r="F19" s="34" t="n"/>
+      <c r="G19" s="34" t="n"/>
+      <c r="H19" s="34" t="n"/>
+      <c r="I19" s="34" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="33" t="inlineStr">
         <is>
           <t>decision/fecha-corte</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>Desde cuándo los tickets nacen en la app</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>F1F-01</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>Noviembre 2026</t>
         </is>
       </c>
-      <c r="E20" s="27" t="inlineStr">
+      <c r="E20" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="27" t="n"/>
-      <c r="H20" s="27" t="n"/>
-      <c r="I20" s="27" t="n"/>
+      <c r="F20" s="34" t="n"/>
+      <c r="G20" s="34" t="n"/>
+      <c r="H20" s="34" t="n"/>
+      <c r="I20" s="34" t="n"/>
     </row>
     <row r="21" ht="51" customHeight="1" s="20">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="33" t="inlineStr">
         <is>
           <t>decision/n52-cardinalidad-ov</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Cuántos tickets puede tener una OV, y al revés (P52)</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>F1A-08 · F1B-11</t>
         </is>
       </c>
-      <c r="D21" s="26" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E21" s="27" t="inlineStr">
+      <c r="E21" s="34" t="inlineStr">
         <is>
           <t>Decidida</t>
         </is>
       </c>
-      <c r="F21" s="27" t="inlineStr">
+      <c r="F21" s="34" t="inlineStr">
         <is>
           <t>1 ticket : N OV, sin tabla puente; una OV con un solo ticket vigente; la asociación vive en tabla propia de la app. La OV global por lote se elimina (subórdenes).</t>
         </is>
       </c>
-      <c r="G21" s="27" t="inlineStr">
+      <c r="G21" s="34" t="inlineStr">
         <is>
           <t>Alfonso (Gerencia)</t>
         </is>
       </c>
-      <c r="H21" s="27" t="inlineStr">
+      <c r="H21" s="34" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="I21" s="27" t="inlineStr">
+      <c r="I21" s="34" t="inlineStr">
         <is>
           <t>Decisiones 10/09 §2 · entrada 5.b · cierra P52. La titularidad va aparte (IV-8)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="51" customHeight="1" s="20">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="33" t="inlineStr">
         <is>
           <t>decision/subov-lote-convencion</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>Cómo se identifica el lote y criterios de la subOV</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>F1B-11</t>
         </is>
       </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E22" s="27" t="inlineStr">
+      <c r="E22" s="34" t="inlineStr">
         <is>
           <t>Decidida</t>
         </is>
       </c>
-      <c r="F22" s="27" t="inlineStr">
+      <c r="F22" s="34" t="inlineStr">
         <is>
           <t>Opción A: convención OV-AAAA-NNN-SS (modifica el formato del 27/08), cuarentena, saldo por lote, un ticket vigente por subOV, anulación que libera. B y C registradas como alternativas.</t>
         </is>
       </c>
-      <c r="G22" s="27" t="inlineStr">
+      <c r="G22" s="34" t="inlineStr">
         <is>
           <t>Alfonso (Gerencia)</t>
         </is>
       </c>
-      <c r="H22" s="27" t="inlineStr">
+      <c r="H22" s="34" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="I22" s="27" t="inlineStr">
+      <c r="I22" s="34" t="inlineStr">
         <is>
           <t>Decisiones 10/09 §8 · R08.2 M4.4</t>
         </is>
       </c>
     </row>
     <row r="23" ht="39" customHeight="1" s="20">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="33" t="inlineStr">
         <is>
           <t>decision/vista-todos-tablero</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Qué enseña la vista «Todos» del tablero</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>F1B-08</t>
         </is>
       </c>
-      <c r="D23" s="26" t="inlineStr">
+      <c r="D23" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E23" s="27" t="inlineStr">
+      <c r="E23" s="34" t="inlineStr">
         <is>
           <t>Decidida</t>
         </is>
       </c>
-      <c r="F23" s="27" t="inlineStr">
+      <c r="F23" s="34" t="inlineStr">
         <is>
           <t>Opción (b): devuelve también los cerrados; no se renombra a «Abiertos». Separar case 'todos' de default va en la misma tanda.</t>
         </is>
       </c>
-      <c r="G23" s="27" t="inlineStr">
+      <c r="G23" s="34" t="inlineStr">
         <is>
           <t>Alfonso (Gerencia)</t>
         </is>
       </c>
-      <c r="H23" s="27" t="inlineStr">
+      <c r="H23" s="34" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="I23" s="27" t="inlineStr">
+      <c r="I23" s="34" t="inlineStr">
         <is>
           <t>Decisiones 10/09 §3 · entrada 5.c</t>
         </is>
       </c>
     </row>
     <row r="24" ht="39" customHeight="1" s="20">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="33" t="inlineStr">
         <is>
           <t>decision/iv2-fechas-derivadas</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>Si el servidor impone las tres fechas derivadas (IV-2)</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>F1A-07</t>
         </is>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E24" s="27" t="inlineStr">
+      <c r="E24" s="34" t="inlineStr">
         <is>
           <t>Decidida</t>
         </is>
       </c>
-      <c r="F24" s="27" t="inlineStr">
+      <c r="F24" s="34" t="inlineStr">
         <is>
           <t>Opción (a): el servidor las calcula e ignora lo que llega del navegador; la zona horaria se fija de forma explícita.</t>
         </is>
       </c>
-      <c r="G24" s="27" t="inlineStr">
+      <c r="G24" s="34" t="inlineStr">
         <is>
           <t>Alfonso (Gerencia)</t>
         </is>
       </c>
-      <c r="H24" s="27" t="inlineStr">
+      <c r="H24" s="34" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="I24" s="27" t="inlineStr">
+      <c r="I24" s="34" t="inlineStr">
         <is>
           <t>Decisiones 10/09 §4 · R08.2 M1.10</t>
         </is>
       </c>
     </row>
     <row r="25" ht="39" customHeight="1" s="20">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="33" t="inlineStr">
         <is>
           <t>decision/mapa-blueprint-generado</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Si se mantiene el mapa visual del blueprint (entrada 4)</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>F1A-06 · F1B-09</t>
         </is>
       </c>
-      <c r="D25" s="26" t="inlineStr">
+      <c r="D25" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E25" s="27" t="inlineStr">
+      <c r="E25" s="34" t="inlineStr">
         <is>
           <t>Decidida</t>
         </is>
       </c>
-      <c r="F25" s="27" t="inlineStr">
+      <c r="F25" s="34" t="inlineStr">
         <is>
           <t>Sí, generado desde transitions.ts con prueba anti-desfase. El artefacto interactivo queda como histórico congelado en a3a8f03.</t>
         </is>
       </c>
-      <c r="G25" s="27" t="inlineStr">
+      <c r="G25" s="34" t="inlineStr">
         <is>
           <t>Alfonso (Gerencia)</t>
         </is>
       </c>
-      <c r="H25" s="27" t="inlineStr">
+      <c r="H25" s="34" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="I25" s="27" t="inlineStr">
+      <c r="I25" s="34" t="inlineStr">
         <is>
           <t>Decisiones 10/09 §9 · R08.2 Anexo F</t>
         </is>
       </c>
     </row>
     <row r="26" ht="39" customHeight="1" s="20">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="33" t="inlineStr">
         <is>
           <t>P38 · salida aprobada (Engram obs. #400)</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>Salida aprobada de Verificación en equipo nuevo</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>F1A-03</t>
         </is>
       </c>
-      <c r="D26" s="26" t="inlineStr">
+      <c r="D26" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E26" s="27" t="inlineStr">
+      <c r="E26" s="34" t="inlineStr">
         <is>
           <t>Decidida</t>
         </is>
       </c>
-      <c r="F26" s="27" t="inlineStr">
+      <c r="F26" s="34" t="inlineStr">
         <is>
           <t>Verificación —Liberación→ Finalizado, observada 71 veces en 181 tickets. Verificación es paso del flujo, condicional por familia de equipo.</t>
         </is>
       </c>
-      <c r="G26" s="27" t="inlineStr">
+      <c r="G26" s="34" t="inlineStr">
         <is>
           <t>Alfonso (Gerencia), con datos de Zoho Desk</t>
         </is>
       </c>
-      <c r="H26" s="27" t="inlineStr">
+      <c r="H26" s="34" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="I26" s="27" t="inlineStr">
+      <c r="I26" s="34" t="inlineStr">
         <is>
           <t>Decisiones 10/09 §1 · R08.2 M1.4 · P38 parcial</t>
         </is>
       </c>
     </row>
     <row r="27" ht="39" customHeight="1" s="20">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="33" t="inlineStr">
         <is>
           <t>decision/p38-verificacion-calidad</t>
         </is>
       </c>
-      <c r="B27" s="26" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Resto de P38: obligatoriedad por familia, lote AP-370 de 2024, salida rechazada → Notificado, guarda de certificado</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>F1B-06 · F1C-07</t>
         </is>
       </c>
-      <c r="D27" s="26" t="inlineStr">
+      <c r="D27" s="33" t="inlineStr">
         <is>
           <t>11/09/2026 (Gustavo / Calidad)</t>
         </is>
       </c>
-      <c r="E27" s="27" t="inlineStr">
+      <c r="E27" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F27" s="27" t="n"/>
-      <c r="G27" s="27" t="n"/>
-      <c r="H27" s="27" t="n"/>
-      <c r="I27" s="27" t="inlineStr">
+      <c r="F27" s="34" t="n"/>
+      <c r="G27" s="34" t="n"/>
+      <c r="H27" s="34" t="n"/>
+      <c r="I27" s="34" t="inlineStr">
         <is>
           <t>Decisiones 10/09 §1 · Anexo D nº 38</t>
         </is>
       </c>
     </row>
     <row r="28" ht="51" customHeight="1" s="20">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="33" t="inlineStr">
         <is>
           <t>decision/escalado-remision-creada</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>Qué cargo de Comercial recibe el escalado de Remisión creada a las 72 h</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>F1B-08</t>
         </is>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D28" s="33" t="inlineStr">
         <is>
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="E28" s="27" t="inlineStr">
+      <c r="E28" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="27" t="n"/>
-      <c r="H28" s="27" t="n"/>
-      <c r="I28" s="27" t="inlineStr">
+      <c r="F28" s="34" t="n"/>
+      <c r="G28" s="34" t="n"/>
+      <c r="H28" s="34" t="n"/>
+      <c r="I28" s="34" t="inlineStr">
         <is>
           <t>Sin él, la guarda de C11 queda en rojo: habilitar_servicio no tiene entrada en DERIVACION_POR_DEFECTO (Decisiones 10/09 §7.2)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="27" customHeight="1" s="20">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t>decision/vigencia-contrato</t>
         </is>
       </c>
-      <c r="B29" s="26" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>Si una subOV libre de un contrato vencido se puede consumir</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
         <is>
           <t>F1B-11 (no bloquea el núcleo)</t>
         </is>
       </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="D29" s="33" t="inlineStr">
         <is>
           <t>11/09/2026 (Alfonso / Comercial)</t>
         </is>
       </c>
-      <c r="E29" s="27" t="inlineStr">
+      <c r="E29" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F29" s="27" t="n"/>
-      <c r="G29" s="27" t="n"/>
-      <c r="H29" s="27" t="n"/>
-      <c r="I29" s="27" t="inlineStr">
+      <c r="F29" s="34" t="n"/>
+      <c r="G29" s="34" t="n"/>
+      <c r="H29" s="34" t="n"/>
+      <c r="I29" s="34" t="inlineStr">
         <is>
           <t>Si la respuesta es no, primer motivo para pasar a la opción B</t>
         </is>
       </c>
     </row>
     <row r="30" ht="39" customHeight="1" s="20">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="33" t="inlineStr">
         <is>
           <t>decision/ovi-garantia-autor</t>
         </is>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>Quién crea la OVI de un servicio en garantía</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>F1B-03</t>
         </is>
       </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="E30" s="27" t="inlineStr">
+      <c r="E30" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F30" s="27" t="n"/>
-      <c r="G30" s="27" t="n"/>
-      <c r="H30" s="27" t="n"/>
-      <c r="I30" s="27" t="inlineStr">
+      <c r="F30" s="34" t="n"/>
+      <c r="G30" s="34" t="n"/>
+      <c r="H30" s="34" t="n"/>
+      <c r="I30" s="34" t="inlineStr">
         <is>
           <t>Hoy las crea Servicio Técnico: sería una excepción de autor a «Comercial crea la OV»</t>
         </is>
       </c>
     </row>
     <row r="31" ht="27" customHeight="1" s="20">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="33" t="inlineStr">
         <is>
           <t>decision/titularidad-ov-equipo</t>
         </is>
       </c>
-      <c r="B31" s="26" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>Si la OV y el equipo pueden ser de clientes distintos (IV-8, ticketService.ts:39)</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>F1B-11</t>
         </is>
       </c>
-      <c r="D31" s="26" t="inlineStr">
+      <c r="D31" s="33" t="inlineStr">
         <is>
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="E31" s="27" t="inlineStr">
+      <c r="E31" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F31" s="27" t="n"/>
-      <c r="G31" s="27" t="n"/>
-      <c r="H31" s="27" t="n"/>
-      <c r="I31" s="27" t="inlineStr">
+      <c r="F31" s="34" t="n"/>
+      <c r="G31" s="34" t="n"/>
+      <c r="H31" s="34" t="n"/>
+      <c r="I31" s="34" t="inlineStr">
         <is>
           <t>Va con P52 pero como punto separado (R08.2 §1.2)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="27" customHeight="1" s="20">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>decision/p62-capa-as-built</t>
         </is>
       </c>
-      <c r="B32" s="26" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>Qué se hace con la capa as-built (retirarla o mantener el Anexo H)</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>— (premisa de F0-02)</t>
         </is>
       </c>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="D32" s="33" t="inlineStr">
         <is>
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="E32" s="27" t="inlineStr">
+      <c r="E32" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F32" s="27" t="n"/>
-      <c r="G32" s="27" t="n"/>
-      <c r="H32" s="27" t="n"/>
-      <c r="I32" s="27" t="inlineStr">
+      <c r="F32" s="34" t="n"/>
+      <c r="G32" s="34" t="n"/>
+      <c r="H32" s="34" t="n"/>
+      <c r="I32" s="34" t="inlineStr">
         <is>
           <t>Llevado al 03/09 y no tratado; vuelve al Anexo D</t>
         </is>
       </c>
     </row>
     <row r="33" ht="27" customHeight="1" s="20">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="33" t="inlineStr">
         <is>
           <t>decision/p64-historico-c1</t>
         </is>
       </c>
-      <c r="B33" s="26" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>Qué se hace con las filas de «Liberación sin factura» escritas antes del arreglo de C1</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>— (dato de producción)</t>
         </is>
       </c>
-      <c r="D33" s="26" t="inlineStr">
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t>Por asignar</t>
         </is>
       </c>
-      <c r="E33" s="27" t="inlineStr">
+      <c r="E33" s="34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="27" t="n"/>
-      <c r="H33" s="27" t="n"/>
-      <c r="I33" s="27" t="inlineStr">
+      <c r="F33" s="34" t="n"/>
+      <c r="G33" s="34" t="n"/>
+      <c r="H33" s="34" t="n"/>
+      <c r="I33" s="34" t="inlineStr">
         <is>
           <t>Contar primero contra producción (R08.2 nº 64)</t>
         </is>
@@ -7749,451 +8108,451 @@
       </c>
     </row>
     <row r="2" ht="39" customHeight="1" s="20">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="33" t="inlineStr">
         <is>
           <t>S37</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="33" t="inlineStr">
         <is>
           <t>07/09</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="C2" s="33" t="inlineStr">
         <is>
           <t>F0-00…F0-04 (ejecutadas) · F1A-01, -02, -04, -05 (cerradas 09/09)</t>
         </is>
       </c>
-      <c r="D2" s="26" t="inlineStr">
+      <c r="D2" s="33" t="inlineStr">
         <is>
           <t>F1B-01 (ejecutada 09/09, adelantada)</t>
         </is>
       </c>
-      <c r="E2" s="26" t="n"/>
-      <c r="F2" s="26" t="n"/>
-      <c r="G2" s="26" t="n"/>
-      <c r="H2" s="26" t="n"/>
-      <c r="I2" s="27" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="34" t="n"/>
     </row>
     <row r="3" ht="27" customHeight="1" s="20">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>S38</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>14/09</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="33" t="inlineStr">
         <is>
           <t>F1A-03 · F1A-06 · F1A-07 · F1A-08 · F1A-09</t>
         </is>
       </c>
-      <c r="D3" s="26" t="n"/>
-      <c r="E3" s="26" t="n"/>
-      <c r="F3" s="26" t="n"/>
-      <c r="G3" s="26" t="n"/>
-      <c r="H3" s="26" t="n"/>
-      <c r="I3" s="27" t="n"/>
+      <c r="D3" s="33" t="n"/>
+      <c r="E3" s="33" t="n"/>
+      <c r="F3" s="33" t="n"/>
+      <c r="G3" s="33" t="n"/>
+      <c r="H3" s="33" t="n"/>
+      <c r="I3" s="34" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="20">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>S39</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>21/09</t>
         </is>
       </c>
-      <c r="C4" s="26" t="n"/>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>F1B-02</t>
         </is>
       </c>
-      <c r="E4" s="26" t="n"/>
-      <c r="F4" s="26" t="n"/>
-      <c r="G4" s="26" t="n"/>
-      <c r="H4" s="26" t="n"/>
-      <c r="I4" s="27" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="I4" s="34" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="20">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>S40</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>28/09</t>
         </is>
       </c>
-      <c r="C5" s="26" t="n"/>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>F1B-03 · F1B-04</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>C2 (si decidido)</t>
         </is>
       </c>
-      <c r="F5" s="26" t="n"/>
-      <c r="G5" s="26" t="n"/>
-      <c r="H5" s="26" t="n"/>
-      <c r="I5" s="27" t="n"/>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="n"/>
+      <c r="I5" s="34" t="n"/>
     </row>
     <row r="6" ht="27" customHeight="1" s="20">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>S41</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>05/10</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n"/>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>F1B-05 · F1B-11 (propuesta)</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="F6" s="26" t="n"/>
-      <c r="G6" s="26" t="n"/>
-      <c r="H6" s="26" t="n"/>
-      <c r="I6" s="27" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="34" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="20">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>S42</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>12/10</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n"/>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="C7" s="33" t="n"/>
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>F1B-06</t>
         </is>
       </c>
-      <c r="E7" s="26" t="n"/>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="E7" s="33" t="n"/>
+      <c r="F7" s="33" t="inlineStr">
         <is>
           <t>F1D-01</t>
         </is>
       </c>
-      <c r="G7" s="26" t="n"/>
-      <c r="H7" s="26" t="n"/>
-      <c r="I7" s="27" t="n"/>
+      <c r="G7" s="33" t="n"/>
+      <c r="H7" s="33" t="n"/>
+      <c r="I7" s="34" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="20">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>S43</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>19/10</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n"/>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="C8" s="33" t="n"/>
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>F1B-07</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="33" t="inlineStr">
         <is>
           <t>F1D-02</t>
         </is>
       </c>
-      <c r="G8" s="26" t="n"/>
-      <c r="H8" s="26" t="n"/>
-      <c r="I8" s="27" t="n"/>
+      <c r="G8" s="33" t="n"/>
+      <c r="H8" s="33" t="n"/>
+      <c r="I8" s="34" t="n"/>
     </row>
     <row r="9" ht="27" customHeight="1" s="20">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>S44</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>26/10</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n"/>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="C9" s="33" t="n"/>
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>F1B-08 (ampliada) · F1B-09</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>C5 · C10</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F9" s="33" t="inlineStr">
         <is>
           <t>F1D-03</t>
         </is>
       </c>
-      <c r="G9" s="26" t="n"/>
-      <c r="H9" s="26" t="n"/>
-      <c r="I9" s="27" t="n"/>
+      <c r="G9" s="33" t="n"/>
+      <c r="H9" s="33" t="n"/>
+      <c r="I9" s="34" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="20">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>S45</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>02/11</t>
         </is>
       </c>
-      <c r="C10" s="26" t="n"/>
-      <c r="D10" s="26" t="n"/>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="C10" s="33" t="n"/>
+      <c r="D10" s="33" t="n"/>
+      <c r="E10" s="33" t="n"/>
+      <c r="F10" s="33" t="inlineStr">
         <is>
           <t>F1D-04</t>
         </is>
       </c>
-      <c r="G10" s="26" t="n"/>
-      <c r="H10" s="26" t="n"/>
-      <c r="I10" s="27" t="n"/>
+      <c r="G10" s="33" t="n"/>
+      <c r="H10" s="33" t="n"/>
+      <c r="I10" s="34" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="20">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>S46</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>09/11</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="26" t="n"/>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="C11" s="33" t="n"/>
+      <c r="D11" s="33" t="n"/>
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>C7+C9</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F11" s="33" t="inlineStr">
         <is>
           <t>F1D-05 · F1D-06</t>
         </is>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="33" t="inlineStr">
         <is>
           <t>F1E-01</t>
         </is>
       </c>
-      <c r="H11" s="26" t="n"/>
-      <c r="I11" s="27" t="n"/>
+      <c r="H11" s="33" t="n"/>
+      <c r="I11" s="34" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="20">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>S47</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>16/11</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="C12" s="33" t="n"/>
+      <c r="D12" s="33" t="n"/>
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="33" t="inlineStr">
         <is>
           <t>F1D-07 · F1D-08 · F1D-09</t>
         </is>
       </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="G12" s="33" t="inlineStr">
         <is>
           <t>F1E-02</t>
         </is>
       </c>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="27" t="n"/>
+      <c r="H12" s="33" t="n"/>
+      <c r="I12" s="34" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="20">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>S48</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>23/11</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
-      <c r="D13" s="26" t="n"/>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="C13" s="33" t="n"/>
+      <c r="D13" s="33" t="n"/>
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>Rutas abreviadas</t>
         </is>
       </c>
-      <c r="F13" s="26" t="n"/>
-      <c r="G13" s="26" t="inlineStr">
+      <c r="F13" s="33" t="n"/>
+      <c r="G13" s="33" t="inlineStr">
         <is>
           <t>F1E-03</t>
         </is>
       </c>
-      <c r="H13" s="26" t="n"/>
-      <c r="I13" s="27" t="n"/>
+      <c r="H13" s="33" t="n"/>
+      <c r="I13" s="34" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="20">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>S49</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>30/11</t>
         </is>
       </c>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="26" t="n"/>
-      <c r="E14" s="26" t="n"/>
-      <c r="F14" s="26" t="n"/>
-      <c r="G14" s="26" t="inlineStr">
+      <c r="C14" s="33" t="n"/>
+      <c r="D14" s="33" t="n"/>
+      <c r="E14" s="33" t="n"/>
+      <c r="F14" s="33" t="n"/>
+      <c r="G14" s="33" t="inlineStr">
         <is>
           <t>F1E-04</t>
         </is>
       </c>
-      <c r="H14" s="26" t="n"/>
-      <c r="I14" s="27" t="n"/>
+      <c r="H14" s="33" t="n"/>
+      <c r="I14" s="34" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="20">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>S50</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>07/12</t>
         </is>
       </c>
-      <c r="C15" s="26" t="n"/>
-      <c r="D15" s="26" t="n"/>
-      <c r="E15" s="26" t="n"/>
-      <c r="F15" s="26" t="n"/>
-      <c r="G15" s="26" t="inlineStr">
+      <c r="C15" s="33" t="n"/>
+      <c r="D15" s="33" t="n"/>
+      <c r="E15" s="33" t="n"/>
+      <c r="F15" s="33" t="n"/>
+      <c r="G15" s="33" t="inlineStr">
         <is>
           <t>F1E-05</t>
         </is>
       </c>
-      <c r="H15" s="26" t="inlineStr">
+      <c r="H15" s="33" t="inlineStr">
         <is>
           <t>F1F-01</t>
         </is>
       </c>
-      <c r="I15" s="27" t="n"/>
+      <c r="I15" s="34" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="20">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>S51</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>14/12</t>
         </is>
       </c>
-      <c r="C16" s="26" t="n"/>
-      <c r="D16" s="26" t="n"/>
-      <c r="E16" s="26" t="n"/>
-      <c r="F16" s="26" t="n"/>
-      <c r="G16" s="26" t="n"/>
-      <c r="H16" s="26" t="inlineStr">
+      <c r="C16" s="33" t="n"/>
+      <c r="D16" s="33" t="n"/>
+      <c r="E16" s="33" t="n"/>
+      <c r="F16" s="33" t="n"/>
+      <c r="G16" s="33" t="n"/>
+      <c r="H16" s="33" t="inlineStr">
         <is>
           <t>F1F-02 · F1F-03</t>
         </is>
       </c>
-      <c r="I16" s="27" t="n"/>
+      <c r="I16" s="34" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="20">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>S52</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>21/12</t>
         </is>
       </c>
-      <c r="C17" s="26" t="n"/>
-      <c r="D17" s="26" t="n"/>
-      <c r="E17" s="26" t="n"/>
-      <c r="F17" s="26" t="n"/>
-      <c r="G17" s="26" t="n"/>
-      <c r="H17" s="26" t="inlineStr">
+      <c r="C17" s="33" t="n"/>
+      <c r="D17" s="33" t="n"/>
+      <c r="E17" s="33" t="n"/>
+      <c r="F17" s="33" t="n"/>
+      <c r="G17" s="33" t="n"/>
+      <c r="H17" s="33" t="inlineStr">
         <is>
           <t>F1F-03 · F1F-04</t>
         </is>
       </c>
-      <c r="I17" s="27" t="n"/>
+      <c r="I17" s="34" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="20">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>S53</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>28/12</t>
         </is>
       </c>
-      <c r="C18" s="26" t="n"/>
-      <c r="D18" s="26" t="n"/>
-      <c r="E18" s="26" t="n"/>
-      <c r="F18" s="26" t="n"/>
-      <c r="G18" s="26" t="n"/>
-      <c r="H18" s="26" t="inlineStr">
+      <c r="C18" s="33" t="n"/>
+      <c r="D18" s="33" t="n"/>
+      <c r="E18" s="33" t="n"/>
+      <c r="F18" s="33" t="n"/>
+      <c r="G18" s="33" t="n"/>
+      <c r="H18" s="33" t="inlineStr">
         <is>
           <t>Margen · meta 31/12</t>
         </is>
       </c>
-      <c r="I18" s="27" t="n"/>
+      <c r="I18" s="34" t="n"/>
     </row>
     <row r="20" ht="90" customHeight="1" s="20">
       <c r="A20" s="36" t="inlineStr">
@@ -8285,41 +8644,41 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="20">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="33" t="inlineStr">
         <is>
           <t>F0</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="33" t="inlineStr">
         <is>
           <t>Cimientos SDD</t>
         </is>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="33">
         <f>COUNTIF(Tandas!$B:$B,A2)</f>
         <v/>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A2,Tandas!$K:$K,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A2,Tandas!$K:$K,"Sí")</f>
         <v/>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A2,Tandas!$K:$K,"Con cambios")+COUNTIFS(Tandas!$B:$B,A2,Tandas!$K:$K,"Duda")</f>
         <v/>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A2,Tandas!$K:$K,"No")</f>
         <v/>
       </c>
-      <c r="H2" s="26">
+      <c r="H2" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A2,Tandas!$M:$M,"Sube")</f>
         <v/>
       </c>
-      <c r="I2" s="26">
+      <c r="I2" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A2,Tandas!$M:$M,"Baja")+COUNTIFS(Tandas!$B:$B,A2,Tandas!$M:$M,"Fuera")</f>
         <v/>
       </c>
@@ -8329,41 +8688,41 @@
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="20">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>F1A</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>Correcciones sin decisión pendiente</t>
         </is>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="33">
         <f>COUNTIF(Tandas!$B:$B,A3)</f>
         <v/>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A3,Tandas!$K:$K,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A3,Tandas!$K:$K,"Sí")</f>
         <v/>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A3,Tandas!$K:$K,"Con cambios")+COUNTIFS(Tandas!$B:$B,A3,Tandas!$K:$K,"Duda")</f>
         <v/>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A3,Tandas!$K:$K,"No")</f>
         <v/>
       </c>
-      <c r="H3" s="26">
+      <c r="H3" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A3,Tandas!$M:$M,"Sube")</f>
         <v/>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A3,Tandas!$M:$M,"Baja")+COUNTIFS(Tandas!$B:$B,A3,Tandas!$M:$M,"Fuera")</f>
         <v/>
       </c>
@@ -8373,41 +8732,41 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="20">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>F1B</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>Paridad funcional con el Desk 1.0</t>
         </is>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="33">
         <f>COUNTIF(Tandas!$B:$B,A4)</f>
         <v/>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A4,Tandas!$K:$K,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A4,Tandas!$K:$K,"Sí")</f>
         <v/>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A4,Tandas!$K:$K,"Con cambios")+COUNTIFS(Tandas!$B:$B,A4,Tandas!$K:$K,"Duda")</f>
         <v/>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A4,Tandas!$K:$K,"No")</f>
         <v/>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A4,Tandas!$M:$M,"Sube")</f>
         <v/>
       </c>
-      <c r="I4" s="26">
+      <c r="I4" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A4,Tandas!$M:$M,"Baja")+COUNTIFS(Tandas!$B:$B,A4,Tandas!$M:$M,"Fuera")</f>
         <v/>
       </c>
@@ -8417,41 +8776,41 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="20">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>F1C</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Correcciones que cambian el proceso</t>
         </is>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="33">
         <f>COUNTIF(Tandas!$B:$B,A5)</f>
         <v/>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A5,Tandas!$K:$K,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A5,Tandas!$K:$K,"Sí")</f>
         <v/>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A5,Tandas!$K:$K,"Con cambios")+COUNTIFS(Tandas!$B:$B,A5,Tandas!$K:$K,"Duda")</f>
         <v/>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A5,Tandas!$K:$K,"No")</f>
         <v/>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A5,Tandas!$M:$M,"Sube")</f>
         <v/>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A5,Tandas!$M:$M,"Baja")+COUNTIFS(Tandas!$B:$B,A5,Tandas!$M:$M,"Fuera")</f>
         <v/>
       </c>
@@ -8461,41 +8820,41 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="20">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>F1D</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Diagnóstico protocolizado con checklist dinámico</t>
         </is>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="33">
         <f>COUNTIF(Tandas!$B:$B,A6)</f>
         <v/>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A6,Tandas!$K:$K,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A6,Tandas!$K:$K,"Sí")</f>
         <v/>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A6,Tandas!$K:$K,"Con cambios")+COUNTIFS(Tandas!$B:$B,A6,Tandas!$K:$K,"Duda")</f>
         <v/>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A6,Tandas!$K:$K,"No")</f>
         <v/>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A6,Tandas!$M:$M,"Sube")</f>
         <v/>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A6,Tandas!$M:$M,"Baja")+COUNTIFS(Tandas!$B:$B,A6,Tandas!$M:$M,"Fuera")</f>
         <v/>
       </c>
@@ -8505,41 +8864,41 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="20">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>F1E</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Módulo de informes</t>
         </is>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="33">
         <f>COUNTIF(Tandas!$B:$B,A7)</f>
         <v/>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A7,Tandas!$K:$K,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A7,Tandas!$K:$K,"Sí")</f>
         <v/>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A7,Tandas!$K:$K,"Con cambios")+COUNTIFS(Tandas!$B:$B,A7,Tandas!$K:$K,"Duda")</f>
         <v/>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A7,Tandas!$K:$K,"No")</f>
         <v/>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A7,Tandas!$M:$M,"Sube")</f>
         <v/>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A7,Tandas!$M:$M,"Baja")+COUNTIFS(Tandas!$B:$B,A7,Tandas!$M:$M,"Fuera")</f>
         <v/>
       </c>
@@ -8549,41 +8908,41 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="20">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>F1F</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Puesta en producción</t>
         </is>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="33">
         <f>COUNTIF(Tandas!$B:$B,A8)</f>
         <v/>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A8,Tandas!$K:$K,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A8,Tandas!$K:$K,"Sí")</f>
         <v/>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A8,Tandas!$K:$K,"Con cambios")+COUNTIFS(Tandas!$B:$B,A8,Tandas!$K:$K,"Duda")</f>
         <v/>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A8,Tandas!$K:$K,"No")</f>
         <v/>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A8,Tandas!$M:$M,"Sube")</f>
         <v/>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A8,Tandas!$M:$M,"Baja")+COUNTIFS(Tandas!$B:$B,A8,Tandas!$M:$M,"Fuera")</f>
         <v/>
       </c>
@@ -8593,41 +8952,41 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="20">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Operación interna completa</t>
         </is>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="33">
         <f>COUNTIF(Tandas!$B:$B,A9)</f>
         <v/>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A9,Tandas!$K:$K,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A9,Tandas!$K:$K,"Sí")</f>
         <v/>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A9,Tandas!$K:$K,"Con cambios")+COUNTIFS(Tandas!$B:$B,A9,Tandas!$K:$K,"Duda")</f>
         <v/>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A9,Tandas!$K:$K,"No")</f>
         <v/>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A9,Tandas!$M:$M,"Sube")</f>
         <v/>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A9,Tandas!$M:$M,"Baja")+COUNTIFS(Tandas!$B:$B,A9,Tandas!$M:$M,"Fuera")</f>
         <v/>
       </c>
@@ -8637,41 +8996,41 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="20">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>Área de cliente y seguridad</t>
         </is>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="33">
         <f>COUNTIF(Tandas!$B:$B,A10)</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A10,Tandas!$K:$K,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A10,Tandas!$K:$K,"Sí")</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A10,Tandas!$K:$K,"Con cambios")+COUNTIFS(Tandas!$B:$B,A10,Tandas!$K:$K,"Duda")</f>
         <v/>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A10,Tandas!$K:$K,"No")</f>
         <v/>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A10,Tandas!$M:$M,"Sube")</f>
         <v/>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A10,Tandas!$M:$M,"Baja")+COUNTIFS(Tandas!$B:$B,A10,Tandas!$M:$M,"Fuera")</f>
         <v/>
       </c>
@@ -8681,41 +9040,41 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="20">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Eficiencia, capacidad y conocimiento</t>
         </is>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="33">
         <f>COUNTIF(Tandas!$B:$B,A11)</f>
         <v/>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A11,Tandas!$K:$K,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A11,Tandas!$K:$K,"Sí")</f>
         <v/>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A11,Tandas!$K:$K,"Con cambios")+COUNTIFS(Tandas!$B:$B,A11,Tandas!$K:$K,"Duda")</f>
         <v/>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A11,Tandas!$K:$K,"No")</f>
         <v/>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A11,Tandas!$M:$M,"Sube")</f>
         <v/>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A11,Tandas!$M:$M,"Baja")+COUNTIFS(Tandas!$B:$B,A11,Tandas!$M:$M,"Fuera")</f>
         <v/>
       </c>
@@ -8725,41 +9084,41 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="20">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>F5</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>Promesa, predicción y ecosistema</t>
         </is>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="33">
         <f>COUNTIF(Tandas!$B:$B,A12)</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A12,Tandas!$K:$K,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A12,Tandas!$K:$K,"Sí")</f>
         <v/>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A12,Tandas!$K:$K,"Con cambios")+COUNTIFS(Tandas!$B:$B,A12,Tandas!$K:$K,"Duda")</f>
         <v/>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A12,Tandas!$K:$K,"No")</f>
         <v/>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A12,Tandas!$M:$M,"Sube")</f>
         <v/>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="33">
         <f>COUNTIFS(Tandas!$B:$B,A12,Tandas!$M:$M,"Baja")+COUNTIFS(Tandas!$B:$B,A12,Tandas!$M:$M,"Fuera")</f>
         <v/>
       </c>
